--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281BFFA2-8DE8-4E04-B019-F755DCC38ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FFFBFD-A9E6-41D9-B3A4-5DE59FB2A3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JNV_STUDENT-MARKS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="173">
   <si>
     <t>Class</t>
   </si>
@@ -67,41 +78,485 @@
     <t>10A</t>
   </si>
   <si>
-    <t>Suresh Patel</t>
-  </si>
-  <si>
     <t>PWT-1</t>
   </si>
   <si>
-    <t>TERM END EXAM</t>
-  </si>
-  <si>
     <t>Anil kumar</t>
   </si>
   <si>
-    <t>9845-5645-1012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIYA PANCHAL </t>
-  </si>
-  <si>
-    <t>DIYAPANCHAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URVASHI RATHVA </t>
-  </si>
-  <si>
-    <t>Suresh RATHVA</t>
+    <t>TAKSH SINGHAL</t>
+  </si>
+  <si>
+    <t>RATHVA AASTHABEN JITENDRABHAI</t>
+  </si>
+  <si>
+    <t>BARIA AYUSHKUMAR</t>
+  </si>
+  <si>
+    <t>RATHVA BHAVYA</t>
+  </si>
+  <si>
+    <t>RATHVA DHRUVIBEN</t>
+  </si>
+  <si>
+    <t>BARIYA DIYA DINESHBHAI</t>
+  </si>
+  <si>
+    <t>RATHVA DRASHTIBEN</t>
+  </si>
+  <si>
+    <t>BARIYA GAURAVKUMAR</t>
+  </si>
+  <si>
+    <t>VANKAR HARDIKKUMAR</t>
+  </si>
+  <si>
+    <t>RATHWA HARDIKABEN FATUBHAI</t>
+  </si>
+  <si>
+    <t>PARMAR HARSH</t>
+  </si>
+  <si>
+    <t>PATEL HARSHIL</t>
+  </si>
+  <si>
+    <t>PARMAR HARSHRAJ</t>
+  </si>
+  <si>
+    <t>RATHVA HITARTH</t>
+  </si>
+  <si>
+    <t>JAYSVAL INJOLINA</t>
+  </si>
+  <si>
+    <t>RATHVA JAIMINKUMAR</t>
+  </si>
+  <si>
+    <t>DABGAR JIYA KETANKUMAR</t>
+  </si>
+  <si>
+    <t>RATHVA KHUSHIBEN MANKARBHAI</t>
+  </si>
+  <si>
+    <t>GAMI KRISA</t>
+  </si>
+  <si>
+    <t>PARMAR KRUPANSHKUMAR</t>
+  </si>
+  <si>
+    <t>VANKAR KRUSHANKKUMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATHWA MAHI </t>
+  </si>
+  <si>
+    <t>VANKAR MEGHABEN PRAFULBHAI</t>
+  </si>
+  <si>
+    <t>MAHERIA MOUSAM</t>
+  </si>
+  <si>
+    <t>BARIA NIDHIBEN</t>
+  </si>
+  <si>
+    <t>PARMAR NIYATIBEN HARSHADBHAI</t>
+  </si>
+  <si>
+    <t>PANDYA PAVAN</t>
+  </si>
+  <si>
+    <t>RATHVA PRACHIBEN</t>
+  </si>
+  <si>
+    <t>BARIA PREM</t>
+  </si>
+  <si>
+    <t>RATHVA PRIYANSHI</t>
+  </si>
+  <si>
+    <t>RATHORE PURV ANTIM</t>
+  </si>
+  <si>
+    <t>BARIYA SHIVANIBEN</t>
+  </si>
+  <si>
+    <t>SHIVRAJBHAI</t>
+  </si>
+  <si>
+    <t>VANKAR SHYAMKUMAR</t>
+  </si>
+  <si>
+    <t>JAISWAL SUJALKUMAR</t>
+  </si>
+  <si>
+    <t>TARABADA TIRTHKUMAR</t>
+  </si>
+  <si>
+    <t>RATHVA USHABEN</t>
+  </si>
+  <si>
+    <t>RATHVA VAISHVIBEN</t>
+  </si>
+  <si>
+    <t>RATHVA YUVRAJSINH</t>
+  </si>
+  <si>
+    <t>RATHVA JITENDRABHAI SENGABHAI</t>
+  </si>
+  <si>
+    <t>BARIA ALPESHBHAI</t>
+  </si>
+  <si>
+    <t>NAVALSINGBHAI</t>
+  </si>
+  <si>
+    <t>RATHVA PARAMSINH</t>
+  </si>
+  <si>
+    <t>BARIYA DINESHBHAI</t>
+  </si>
+  <si>
+    <t>RATHVA HASMUKHBHAI</t>
+  </si>
+  <si>
+    <t>BARIYA BHUPENDRABHAI</t>
+  </si>
+  <si>
+    <t>VANKAR ARVINDBHAI</t>
+  </si>
+  <si>
+    <t>RATHWA FATUBHAI</t>
+  </si>
+  <si>
+    <t>PARMAR JAGDISHBHAI</t>
+  </si>
+  <si>
+    <t>PATEL AJITBHAI</t>
+  </si>
+  <si>
+    <t>PIYUSHBHAI</t>
+  </si>
+  <si>
+    <t>RATHVA JAYRAMBHAI</t>
+  </si>
+  <si>
+    <t>JAYSVAL AKLESHBHAI</t>
+  </si>
+  <si>
+    <t>RATHVA LAXMANBHAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KETANKUMAR </t>
+  </si>
+  <si>
+    <t>MANKARBHAI</t>
+  </si>
+  <si>
+    <t>GAMI SANJAYBHAI</t>
+  </si>
+  <si>
+    <t>PARMAR CHETANBHAI</t>
+  </si>
+  <si>
+    <t>VANKAR DINESHBHAI</t>
+  </si>
+  <si>
+    <t>RATHWA SANJAYBHAI</t>
+  </si>
+  <si>
+    <t>VANKAR PRAFULBHAI ARVINDBHAI</t>
+  </si>
+  <si>
+    <t>MAHERIA HARSHADBHAI</t>
+  </si>
+  <si>
+    <t>BARIA SANATBHAI</t>
+  </si>
+  <si>
+    <t>PARMAR HARSHADBHAI</t>
+  </si>
+  <si>
+    <t>PANDYA MAULINKUMAR</t>
+  </si>
+  <si>
+    <t>RATHVA IKRAMBHAI</t>
+  </si>
+  <si>
+    <t>BARIA CHARANKUMAR</t>
+  </si>
+  <si>
+    <t>RATHVA NARANBHAI</t>
+  </si>
+  <si>
+    <t>ANTIM</t>
+  </si>
+  <si>
+    <t>BARIYA RAMANBHAI</t>
+  </si>
+  <si>
+    <t>VINUBHAI</t>
+  </si>
+  <si>
+    <t>VANKAR DHARMENDRABHAI</t>
+  </si>
+  <si>
+    <t>JAISWAL DHARMRAJBHAI</t>
+  </si>
+  <si>
+    <t>PARMAR KALPESHBHAI</t>
+  </si>
+  <si>
+    <t>TARABADA JAYESHBHAI</t>
+  </si>
+  <si>
+    <t>RATHVA NARSINGBHAI</t>
+  </si>
+  <si>
+    <t>RATHVA BALVANTSINH</t>
+  </si>
+  <si>
+    <t>RATHVA DINESHBHAI</t>
+  </si>
+  <si>
+    <t>25.03.2012</t>
+  </si>
+  <si>
+    <t>24.07.2011</t>
+  </si>
+  <si>
+    <t>06.09.2011</t>
+  </si>
+  <si>
+    <t>26.12.2011</t>
+  </si>
+  <si>
+    <t>25.06.2011</t>
+  </si>
+  <si>
+    <t>19.08.2011</t>
+  </si>
+  <si>
+    <t>22.02.2012</t>
+  </si>
+  <si>
+    <t>22.10.2011</t>
+  </si>
+  <si>
+    <t>21.10.2011</t>
+  </si>
+  <si>
+    <t>16.02.2011</t>
+  </si>
+  <si>
+    <t>01.07.2010</t>
+  </si>
+  <si>
+    <t>02.04.2012</t>
+  </si>
+  <si>
+    <t>05.03.2012</t>
+  </si>
+  <si>
+    <t>28.10.2010</t>
+  </si>
+  <si>
+    <t>28.03.2011</t>
+  </si>
+  <si>
+    <t>14.04.2012</t>
+  </si>
+  <si>
+    <t>27.12.2011</t>
+  </si>
+  <si>
+    <t>14.11.2011</t>
+  </si>
+  <si>
+    <t>14.02.2011</t>
+  </si>
+  <si>
+    <t>18.10.2011</t>
+  </si>
+  <si>
+    <t>06.07.2011</t>
+  </si>
+  <si>
+    <t>30.08.2011</t>
+  </si>
+  <si>
+    <t>05.07.2011</t>
+  </si>
+  <si>
+    <t>24.12.2011</t>
+  </si>
+  <si>
+    <t>10.04.2012</t>
+  </si>
+  <si>
+    <t>22.11.2011</t>
+  </si>
+  <si>
+    <t>31.08.2011</t>
+  </si>
+  <si>
+    <t>26.10.2011</t>
+  </si>
+  <si>
+    <t>02.08.2011</t>
+  </si>
+  <si>
+    <t>02.12.2010</t>
+  </si>
+  <si>
+    <t>27.05.2011</t>
+  </si>
+  <si>
+    <t>21.07.2010</t>
+  </si>
+  <si>
+    <t>18.01.2010</t>
+  </si>
+  <si>
+    <t>13.06.2011</t>
+  </si>
+  <si>
+    <t>03.09.2011</t>
+  </si>
+  <si>
+    <t>06.08.2011</t>
+  </si>
+  <si>
+    <t>29.06.2011</t>
+  </si>
+  <si>
+    <t>31.05.2011</t>
+  </si>
+  <si>
+    <t>08.07.2010</t>
+  </si>
+  <si>
+    <t>574747014578</t>
+  </si>
+  <si>
+    <t>354010122443</t>
+  </si>
+  <si>
+    <t>936965078119</t>
+  </si>
+  <si>
+    <t>884051508443</t>
+  </si>
+  <si>
+    <t>893929190667</t>
+  </si>
+  <si>
+    <t>504736254868</t>
+  </si>
+  <si>
+    <t>802926956319</t>
+  </si>
+  <si>
+    <t>605112212584</t>
+  </si>
+  <si>
+    <t>526838229660</t>
+  </si>
+  <si>
+    <t>665572733862</t>
+  </si>
+  <si>
+    <t>994767977359</t>
+  </si>
+  <si>
+    <t>996366608635</t>
+  </si>
+  <si>
+    <t>605212626665</t>
+  </si>
+  <si>
+    <t>870324081975</t>
+  </si>
+  <si>
+    <t>818431602673</t>
+  </si>
+  <si>
+    <t>789507337345</t>
+  </si>
+  <si>
+    <t>365132741276</t>
+  </si>
+  <si>
+    <t>761938810531</t>
+  </si>
+  <si>
+    <t>809474748055</t>
+  </si>
+  <si>
+    <t>582919923933</t>
+  </si>
+  <si>
+    <t>908280526372</t>
+  </si>
+  <si>
+    <t>343267182819</t>
+  </si>
+  <si>
+    <t>347349816287</t>
+  </si>
+  <si>
+    <t>403744121028</t>
+  </si>
+  <si>
+    <t>436994918268</t>
+  </si>
+  <si>
+    <t>208709609783</t>
+  </si>
+  <si>
+    <t>918875799047</t>
+  </si>
+  <si>
+    <t>959758095720</t>
+  </si>
+  <si>
+    <t>740101830529</t>
+  </si>
+  <si>
+    <t>308378004990</t>
+  </si>
+  <si>
+    <t>405078356753</t>
+  </si>
+  <si>
+    <t>615438942416</t>
+  </si>
+  <si>
+    <t>370327117925</t>
+  </si>
+  <si>
+    <t>902033479293</t>
+  </si>
+  <si>
+    <t>278985535108</t>
+  </si>
+  <si>
+    <t>439529811732</t>
+  </si>
+  <si>
+    <t>623393076093</t>
+  </si>
+  <si>
+    <t>754773060352</t>
+  </si>
+  <si>
+    <t>884313537373</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -111,6 +566,17 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -132,20 +598,43 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{72D0AE27-16F0-437C-A5A7-BA403358CA3A}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -363,17 +852,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.140625" customWidth="1"/>
     <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -417,92 +907,92 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="1">
-        <v>101</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>1001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1">
-        <v>15082008</v>
-      </c>
-      <c r="F2" s="4">
-        <v>984556451012</v>
+        <v>56</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1">
+        <v>28</v>
+      </c>
+      <c r="I2" s="1">
+        <v>39</v>
+      </c>
+      <c r="J2" s="1">
+        <v>26</v>
+      </c>
+      <c r="K2" s="1">
         <v>22</v>
       </c>
-      <c r="I2" s="1">
-        <v>23</v>
-      </c>
-      <c r="J2" s="1">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1">
-        <v>21</v>
-      </c>
       <c r="L2" s="1">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="M2" s="1">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1">
+        <v>33</v>
+      </c>
+      <c r="J3" s="1">
+        <v>14</v>
+      </c>
+      <c r="K3" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1">
-        <v>101</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2">
-        <v>39675</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1">
-        <v>88</v>
-      </c>
-      <c r="I3" s="1">
-        <v>90</v>
-      </c>
-      <c r="J3" s="1">
-        <v>85</v>
-      </c>
-      <c r="K3" s="1">
-        <v>89</v>
-      </c>
       <c r="L3" s="1">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="M3" s="1">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -510,46 +1000,1634 @@
         <v>14</v>
       </c>
       <c r="B4">
+        <v>1003</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4">
+        <v>23</v>
+      </c>
+      <c r="I4">
+        <v>40</v>
+      </c>
+      <c r="J4">
+        <v>21</v>
+      </c>
+      <c r="K4">
+        <v>14</v>
+      </c>
+      <c r="L4">
+        <v>38</v>
+      </c>
+      <c r="M4">
+        <v>37</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>33</v>
+      </c>
+      <c r="I5">
+        <v>40</v>
+      </c>
+      <c r="J5">
+        <v>39</v>
+      </c>
+      <c r="K5">
+        <v>34</v>
+      </c>
+      <c r="L5">
+        <v>38</v>
+      </c>
+      <c r="M5">
+        <v>39</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1005</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>39</v>
+      </c>
+      <c r="J6">
+        <v>33</v>
+      </c>
+      <c r="K6">
+        <v>30</v>
+      </c>
+      <c r="L6">
+        <v>35</v>
+      </c>
+      <c r="M6">
+        <v>39</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>1006</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>23</v>
+      </c>
+      <c r="L7">
+        <v>26</v>
+      </c>
+      <c r="M7">
+        <v>39</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1007</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>37</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>35</v>
+      </c>
+      <c r="M8">
+        <v>36</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1008</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F9" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>23</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>1009</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10">
         <v>22</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="I10">
+        <v>36</v>
+      </c>
+      <c r="J10">
+        <v>17</v>
+      </c>
+      <c r="K10">
+        <v>25</v>
+      </c>
+      <c r="L10">
+        <v>34</v>
+      </c>
+      <c r="M10">
+        <v>36</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1010</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11">
+        <v>28</v>
+      </c>
+      <c r="I11">
+        <v>37</v>
+      </c>
+      <c r="J11">
+        <v>26</v>
+      </c>
+      <c r="K11">
+        <v>26</v>
+      </c>
+      <c r="L11">
+        <v>34</v>
+      </c>
+      <c r="M11">
+        <v>35</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1011</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12">
+        <v>27</v>
+      </c>
+      <c r="I12">
+        <v>38</v>
+      </c>
+      <c r="J12">
         <v>23</v>
       </c>
-      <c r="E4" s="3">
-        <v>39676</v>
-      </c>
-      <c r="F4" s="4">
-        <v>123456789012</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="K12">
+        <v>28</v>
+      </c>
+      <c r="L12">
+        <v>37</v>
+      </c>
+      <c r="M12">
+        <v>39</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>1012</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13">
+        <v>15</v>
+      </c>
+      <c r="I13">
+        <v>20</v>
+      </c>
+      <c r="J13">
+        <v>14</v>
+      </c>
+      <c r="K13">
+        <v>7</v>
+      </c>
+      <c r="L13">
+        <v>24</v>
+      </c>
+      <c r="M13">
+        <v>31</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14">
+        <v>35</v>
+      </c>
+      <c r="I14">
+        <v>40</v>
+      </c>
+      <c r="J14">
+        <v>35</v>
+      </c>
+      <c r="K14">
+        <v>29</v>
+      </c>
+      <c r="L14">
+        <v>37</v>
+      </c>
+      <c r="M14">
+        <v>37</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15">
+        <v>31</v>
+      </c>
+      <c r="I15">
+        <v>40</v>
+      </c>
+      <c r="J15">
+        <v>35</v>
+      </c>
+      <c r="K15">
+        <v>30</v>
+      </c>
+      <c r="L15">
+        <v>38</v>
+      </c>
+      <c r="M15">
+        <v>39</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>1015</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16">
+        <v>28</v>
+      </c>
+      <c r="I16">
+        <v>40</v>
+      </c>
+      <c r="J16">
+        <v>29</v>
+      </c>
+      <c r="K16">
+        <v>28</v>
+      </c>
+      <c r="L16">
+        <v>38</v>
+      </c>
+      <c r="M16">
+        <v>36</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1016</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17">
+        <v>30</v>
+      </c>
+      <c r="I17">
+        <v>40</v>
+      </c>
+      <c r="J17">
+        <v>20</v>
+      </c>
+      <c r="K17">
+        <v>30</v>
+      </c>
+      <c r="L17">
+        <v>28</v>
+      </c>
+      <c r="M17">
+        <v>37</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1017</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>36</v>
+      </c>
+      <c r="J18">
+        <v>32</v>
+      </c>
+      <c r="K18">
+        <v>25</v>
+      </c>
+      <c r="L18">
+        <v>31</v>
+      </c>
+      <c r="M18">
+        <v>35</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19">
+        <v>1018</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19">
+        <v>25</v>
+      </c>
+      <c r="I19">
+        <v>39</v>
+      </c>
+      <c r="J19">
         <v>17</v>
       </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>15</v>
-      </c>
-      <c r="K4">
-        <v>10</v>
-      </c>
-      <c r="L4">
+      <c r="K19">
+        <v>17</v>
+      </c>
+      <c r="L19">
+        <v>27</v>
+      </c>
+      <c r="M19">
+        <v>37</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1019</v>
+      </c>
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1020</v>
+      </c>
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21">
+        <v>23</v>
+      </c>
+      <c r="I21">
+        <v>37</v>
+      </c>
+      <c r="J21">
+        <v>18</v>
+      </c>
+      <c r="K21">
+        <v>22</v>
+      </c>
+      <c r="L21">
+        <v>32</v>
+      </c>
+      <c r="M21">
+        <v>36</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22">
+        <v>1021</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22">
+        <v>23</v>
+      </c>
+      <c r="I22">
+        <v>38</v>
+      </c>
+      <c r="J22">
+        <v>19</v>
+      </c>
+      <c r="K22">
         <v>20</v>
       </c>
-      <c r="M4">
+      <c r="L22">
+        <v>26</v>
+      </c>
+      <c r="M22">
+        <v>32</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1022</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23">
+        <v>22</v>
+      </c>
+      <c r="I23">
+        <v>38</v>
+      </c>
+      <c r="J23">
+        <v>14</v>
+      </c>
+      <c r="K23">
+        <v>14</v>
+      </c>
+      <c r="L23">
+        <v>29</v>
+      </c>
+      <c r="M23">
+        <v>37</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1023</v>
+      </c>
+      <c r="C24" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="D24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24">
+        <v>28</v>
+      </c>
+      <c r="I24">
+        <v>40</v>
+      </c>
+      <c r="J24">
+        <v>29</v>
+      </c>
+      <c r="K24">
         <v>18</v>
       </c>
+      <c r="L24">
+        <v>32</v>
+      </c>
+      <c r="M24">
+        <v>39</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25">
+        <v>1024</v>
+      </c>
+      <c r="C25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25">
+        <v>31</v>
+      </c>
+      <c r="I25">
+        <v>40</v>
+      </c>
+      <c r="J25">
+        <v>34</v>
+      </c>
+      <c r="K25">
+        <v>26</v>
+      </c>
+      <c r="L25">
+        <v>38</v>
+      </c>
+      <c r="M25">
+        <v>39</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1025</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26">
+        <v>21</v>
+      </c>
+      <c r="I26">
+        <v>39</v>
+      </c>
+      <c r="J26">
+        <v>20</v>
+      </c>
+      <c r="K26">
+        <v>23</v>
+      </c>
+      <c r="L26">
+        <v>29</v>
+      </c>
+      <c r="M26">
+        <v>39</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1026</v>
+      </c>
+      <c r="C27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27">
+        <v>30</v>
+      </c>
+      <c r="I27">
+        <v>40</v>
+      </c>
+      <c r="J27">
+        <v>31</v>
+      </c>
+      <c r="K27">
+        <v>28</v>
+      </c>
+      <c r="L27">
+        <v>40</v>
+      </c>
+      <c r="M27">
+        <v>38</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28">
+        <v>1027</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28">
+        <v>25</v>
+      </c>
+      <c r="I28">
+        <v>39</v>
+      </c>
+      <c r="J28">
+        <v>21</v>
+      </c>
+      <c r="K28">
+        <v>21</v>
+      </c>
+      <c r="L28">
+        <v>29</v>
+      </c>
+      <c r="M28">
+        <v>35</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1028</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29">
+        <v>26</v>
+      </c>
+      <c r="I29">
+        <v>36</v>
+      </c>
+      <c r="J29">
+        <v>33</v>
+      </c>
+      <c r="K29">
+        <v>28</v>
+      </c>
+      <c r="L29">
+        <v>34</v>
+      </c>
+      <c r="M29">
+        <v>33</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1029</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30">
+        <v>30</v>
+      </c>
+      <c r="I30">
+        <v>40</v>
+      </c>
+      <c r="J30">
+        <v>26</v>
+      </c>
+      <c r="K30">
+        <v>30</v>
+      </c>
+      <c r="L30">
+        <v>35</v>
+      </c>
+      <c r="M30">
+        <v>38</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31">
+        <v>1030</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31">
+        <v>36</v>
+      </c>
+      <c r="I31">
+        <v>38</v>
+      </c>
+      <c r="J31">
+        <v>38</v>
+      </c>
+      <c r="K31">
+        <v>37</v>
+      </c>
+      <c r="L31">
+        <v>37</v>
+      </c>
+      <c r="M31">
+        <v>36</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1031</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32">
+        <v>30</v>
+      </c>
+      <c r="I32">
+        <v>40</v>
+      </c>
+      <c r="J32">
+        <v>34</v>
+      </c>
+      <c r="K32">
+        <v>24</v>
+      </c>
+      <c r="L32">
+        <v>38</v>
+      </c>
+      <c r="M32">
+        <v>39</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1032</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33">
+        <v>24</v>
+      </c>
+      <c r="I33">
+        <v>37</v>
+      </c>
+      <c r="J33">
+        <v>24</v>
+      </c>
+      <c r="K33">
+        <v>24</v>
+      </c>
+      <c r="L33">
+        <v>34</v>
+      </c>
+      <c r="M33">
+        <v>39</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34">
+        <v>1033</v>
+      </c>
+      <c r="C34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34">
+        <v>24</v>
+      </c>
+      <c r="I34">
+        <v>37</v>
+      </c>
+      <c r="J34">
+        <v>28</v>
+      </c>
+      <c r="K34">
+        <v>26</v>
+      </c>
+      <c r="L34">
+        <v>30</v>
+      </c>
+      <c r="M34">
+        <v>38</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1034</v>
+      </c>
+      <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35">
+        <v>20</v>
+      </c>
+      <c r="I35">
+        <v>37</v>
+      </c>
+      <c r="J35">
+        <v>25</v>
+      </c>
+      <c r="K35">
+        <v>20</v>
+      </c>
+      <c r="L35">
+        <v>32</v>
+      </c>
+      <c r="M35">
+        <v>32</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1035</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36">
+        <v>23</v>
+      </c>
+      <c r="I36">
+        <v>38</v>
+      </c>
+      <c r="J36">
+        <v>19</v>
+      </c>
+      <c r="K36">
+        <v>26</v>
+      </c>
+      <c r="L36">
+        <v>34</v>
+      </c>
+      <c r="M36">
+        <v>39</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37">
+        <v>1036</v>
+      </c>
+      <c r="C37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1037</v>
+      </c>
+      <c r="C38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38">
+        <v>23</v>
+      </c>
+      <c r="I38">
+        <v>39</v>
+      </c>
+      <c r="J38">
+        <v>20</v>
+      </c>
+      <c r="K38">
+        <v>19</v>
+      </c>
+      <c r="L38">
+        <v>24</v>
+      </c>
+      <c r="M38">
+        <v>37</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1038</v>
+      </c>
+      <c r="C39" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39">
+        <v>28</v>
+      </c>
+      <c r="I39">
+        <v>37</v>
+      </c>
+      <c r="J39">
+        <v>30</v>
+      </c>
+      <c r="K39">
+        <v>29</v>
+      </c>
+      <c r="L39">
+        <v>37</v>
+      </c>
+      <c r="M39">
+        <v>38</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1039</v>
+      </c>
+      <c r="C40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" t="s">
+        <v>94</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40">
+        <v>30</v>
+      </c>
+      <c r="I40">
+        <v>40</v>
+      </c>
+      <c r="J40">
+        <v>22</v>
+      </c>
+      <c r="K40">
+        <v>28</v>
+      </c>
+      <c r="L40">
+        <v>33</v>
+      </c>
+      <c r="M40">
+        <v>37</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="F2:F40" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B75D2C-34B1-4211-9F80-C5FFE09C07A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACC0FB8-9C71-468C-A231-6DDA5A084C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13200" yWindow="60" windowWidth="15510" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="import streamlit as st_x000a_import p" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="175">
   <si>
     <t>Class</t>
   </si>
@@ -542,6 +542,9 @@
   </si>
   <si>
     <t>Anil kumar</t>
+  </si>
+  <si>
+    <t>PWT-1</t>
   </si>
 </sst>
 </file>
@@ -807,7 +810,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
@@ -815,7 +818,7 @@
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -862,7 +865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -909,7 +912,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -956,7 +959,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2693,6 +2696,1818 @@
       </c>
       <c r="O40" t="s">
         <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H41" s="1">
+        <v>240</v>
+      </c>
+      <c r="I41">
+        <v>30</v>
+      </c>
+      <c r="J41">
+        <v>31</v>
+      </c>
+      <c r="K41">
+        <v>32</v>
+      </c>
+      <c r="L41">
+        <v>30</v>
+      </c>
+      <c r="M41">
+        <v>30</v>
+      </c>
+      <c r="N41">
+        <v>33</v>
+      </c>
+      <c r="O41" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H42" s="1">
+        <v>240</v>
+      </c>
+      <c r="I42">
+        <v>23</v>
+      </c>
+      <c r="J42">
+        <v>32</v>
+      </c>
+      <c r="K42">
+        <v>25</v>
+      </c>
+      <c r="L42">
+        <v>33</v>
+      </c>
+      <c r="M42">
+        <v>33</v>
+      </c>
+      <c r="N42">
+        <v>33</v>
+      </c>
+      <c r="O42" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H43" s="1">
+        <v>240</v>
+      </c>
+      <c r="I43">
+        <v>28</v>
+      </c>
+      <c r="J43">
+        <v>34</v>
+      </c>
+      <c r="K43">
+        <v>34</v>
+      </c>
+      <c r="L43">
+        <v>24</v>
+      </c>
+      <c r="M43">
+        <v>33</v>
+      </c>
+      <c r="N43">
+        <v>32</v>
+      </c>
+      <c r="O43" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44">
+        <v>1004</v>
+      </c>
+      <c r="C44" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H44" s="1">
+        <v>240</v>
+      </c>
+      <c r="I44">
+        <v>14</v>
+      </c>
+      <c r="J44">
+        <v>22</v>
+      </c>
+      <c r="K44">
+        <v>14</v>
+      </c>
+      <c r="L44">
+        <v>17</v>
+      </c>
+      <c r="M44">
+        <v>20</v>
+      </c>
+      <c r="N44">
+        <v>25</v>
+      </c>
+      <c r="O44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45">
+        <v>1005</v>
+      </c>
+      <c r="C45" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" t="s">
+        <v>35</v>
+      </c>
+      <c r="F45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H45" s="1">
+        <v>240</v>
+      </c>
+      <c r="I45">
+        <v>31</v>
+      </c>
+      <c r="J45">
+        <v>30</v>
+      </c>
+      <c r="K45">
+        <v>15</v>
+      </c>
+      <c r="L45">
+        <v>23</v>
+      </c>
+      <c r="M45">
+        <v>30</v>
+      </c>
+      <c r="N45">
+        <v>35</v>
+      </c>
+      <c r="O45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46">
+        <v>1006</v>
+      </c>
+      <c r="C46" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46" t="s">
+        <v>40</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H46" s="1">
+        <v>240</v>
+      </c>
+      <c r="I46">
+        <v>29</v>
+      </c>
+      <c r="J46">
+        <v>29</v>
+      </c>
+      <c r="K46">
+        <v>27</v>
+      </c>
+      <c r="L46">
+        <v>22</v>
+      </c>
+      <c r="M46">
+        <v>30</v>
+      </c>
+      <c r="N46">
+        <v>28</v>
+      </c>
+      <c r="O46" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47">
+        <v>1007</v>
+      </c>
+      <c r="C47" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" t="s">
+        <v>42</v>
+      </c>
+      <c r="E47" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H47" s="1">
+        <v>240</v>
+      </c>
+      <c r="I47">
+        <v>24</v>
+      </c>
+      <c r="J47">
+        <v>27</v>
+      </c>
+      <c r="K47">
+        <v>16</v>
+      </c>
+      <c r="L47">
+        <v>23</v>
+      </c>
+      <c r="M47">
+        <v>23</v>
+      </c>
+      <c r="N47">
+        <v>33</v>
+      </c>
+      <c r="O47" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48">
+        <v>1008</v>
+      </c>
+      <c r="C48" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" t="s">
+        <v>48</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" s="1">
+        <v>240</v>
+      </c>
+      <c r="I48">
+        <v>20</v>
+      </c>
+      <c r="J48">
+        <v>33</v>
+      </c>
+      <c r="K48">
+        <v>37</v>
+      </c>
+      <c r="L48">
+        <v>17</v>
+      </c>
+      <c r="M48">
+        <v>32</v>
+      </c>
+      <c r="N48">
+        <v>30</v>
+      </c>
+      <c r="O48" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49">
+        <v>1009</v>
+      </c>
+      <c r="C49" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" t="s">
+        <v>50</v>
+      </c>
+      <c r="E49" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" t="s">
+        <v>52</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H49" s="1">
+        <v>240</v>
+      </c>
+      <c r="I49">
+        <v>35</v>
+      </c>
+      <c r="J49">
+        <v>36</v>
+      </c>
+      <c r="K49">
+        <v>27</v>
+      </c>
+      <c r="L49">
+        <v>38</v>
+      </c>
+      <c r="M49">
+        <v>36</v>
+      </c>
+      <c r="N49">
+        <v>39</v>
+      </c>
+      <c r="O49" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50">
+        <v>1010</v>
+      </c>
+      <c r="C50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H50" s="1">
+        <v>240</v>
+      </c>
+      <c r="I50">
+        <v>24</v>
+      </c>
+      <c r="J50">
+        <v>35</v>
+      </c>
+      <c r="K50">
+        <v>26</v>
+      </c>
+      <c r="L50">
+        <v>28</v>
+      </c>
+      <c r="M50">
+        <v>36</v>
+      </c>
+      <c r="N50">
+        <v>31</v>
+      </c>
+      <c r="O50" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51">
+        <v>1011</v>
+      </c>
+      <c r="C51" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" t="s">
+        <v>60</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H51" s="1">
+        <v>240</v>
+      </c>
+      <c r="I51">
+        <v>31</v>
+      </c>
+      <c r="J51">
+        <v>35</v>
+      </c>
+      <c r="K51">
+        <v>33</v>
+      </c>
+      <c r="L51">
+        <v>29</v>
+      </c>
+      <c r="M51">
+        <v>36</v>
+      </c>
+      <c r="N51">
+        <v>31</v>
+      </c>
+      <c r="O51" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52">
+        <v>1012</v>
+      </c>
+      <c r="C52" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" t="s">
+        <v>64</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H52" s="1">
+        <v>240</v>
+      </c>
+      <c r="I52">
+        <v>17</v>
+      </c>
+      <c r="J52">
+        <v>26</v>
+      </c>
+      <c r="K52">
+        <v>15</v>
+      </c>
+      <c r="L52">
+        <v>17</v>
+      </c>
+      <c r="M52">
+        <v>23</v>
+      </c>
+      <c r="N52">
+        <v>31</v>
+      </c>
+      <c r="O52" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53">
+        <v>1013</v>
+      </c>
+      <c r="C53" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" t="s">
+        <v>66</v>
+      </c>
+      <c r="E53" t="s">
+        <v>67</v>
+      </c>
+      <c r="F53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H53" s="1">
+        <v>240</v>
+      </c>
+      <c r="I53">
+        <v>14</v>
+      </c>
+      <c r="J53">
+        <v>29</v>
+      </c>
+      <c r="K53">
+        <v>14</v>
+      </c>
+      <c r="L53">
+        <v>18</v>
+      </c>
+      <c r="M53">
+        <v>28</v>
+      </c>
+      <c r="N53">
+        <v>31</v>
+      </c>
+      <c r="O53" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54">
+        <v>1014</v>
+      </c>
+      <c r="C54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" t="s">
+        <v>70</v>
+      </c>
+      <c r="E54" t="s">
+        <v>71</v>
+      </c>
+      <c r="F54" t="s">
+        <v>72</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H54" s="1">
+        <v>240</v>
+      </c>
+      <c r="I54">
+        <v>33</v>
+      </c>
+      <c r="J54">
+        <v>35</v>
+      </c>
+      <c r="K54">
+        <v>20</v>
+      </c>
+      <c r="L54">
+        <v>27</v>
+      </c>
+      <c r="M54">
+        <v>35</v>
+      </c>
+      <c r="N54">
+        <v>39</v>
+      </c>
+      <c r="O54" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55">
+        <v>1015</v>
+      </c>
+      <c r="C55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55" t="s">
+        <v>75</v>
+      </c>
+      <c r="F55" t="s">
+        <v>76</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H55" s="1">
+        <v>240</v>
+      </c>
+      <c r="I55">
+        <v>35</v>
+      </c>
+      <c r="J55">
+        <v>37</v>
+      </c>
+      <c r="K55">
+        <v>24</v>
+      </c>
+      <c r="L55">
+        <v>34</v>
+      </c>
+      <c r="M55">
+        <v>38</v>
+      </c>
+      <c r="N55">
+        <v>38</v>
+      </c>
+      <c r="O55" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56">
+        <v>1016</v>
+      </c>
+      <c r="C56" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56" t="s">
+        <v>80</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H56" s="1">
+        <v>240</v>
+      </c>
+      <c r="I56">
+        <v>34</v>
+      </c>
+      <c r="J56">
+        <v>33</v>
+      </c>
+      <c r="K56">
+        <v>24</v>
+      </c>
+      <c r="L56">
+        <v>30</v>
+      </c>
+      <c r="M56">
+        <v>34</v>
+      </c>
+      <c r="N56">
+        <v>33</v>
+      </c>
+      <c r="O56" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57">
+        <v>1017</v>
+      </c>
+      <c r="C57" t="s">
+        <v>81</v>
+      </c>
+      <c r="D57" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" t="s">
+        <v>83</v>
+      </c>
+      <c r="F57" t="s">
+        <v>84</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H57" s="1">
+        <v>240</v>
+      </c>
+      <c r="I57">
+        <v>27</v>
+      </c>
+      <c r="J57">
+        <v>27</v>
+      </c>
+      <c r="K57">
+        <v>19</v>
+      </c>
+      <c r="L57">
+        <v>18</v>
+      </c>
+      <c r="M57">
+        <v>25</v>
+      </c>
+      <c r="N57">
+        <v>36</v>
+      </c>
+      <c r="O57" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58">
+        <v>1018</v>
+      </c>
+      <c r="C58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D58" t="s">
+        <v>86</v>
+      </c>
+      <c r="E58" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58" t="s">
+        <v>88</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H58" s="1">
+        <v>240</v>
+      </c>
+      <c r="I58">
+        <v>20</v>
+      </c>
+      <c r="J58">
+        <v>25</v>
+      </c>
+      <c r="K58">
+        <v>18</v>
+      </c>
+      <c r="L58">
+        <v>18</v>
+      </c>
+      <c r="M58">
+        <v>23</v>
+      </c>
+      <c r="N58">
+        <v>29</v>
+      </c>
+      <c r="O58" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59">
+        <v>1019</v>
+      </c>
+      <c r="C59" t="s">
+        <v>89</v>
+      </c>
+      <c r="D59" t="s">
+        <v>90</v>
+      </c>
+      <c r="E59" t="s">
+        <v>91</v>
+      </c>
+      <c r="F59" t="s">
+        <v>92</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H59" s="1">
+        <v>240</v>
+      </c>
+      <c r="I59">
+        <v>22</v>
+      </c>
+      <c r="J59">
+        <v>27</v>
+      </c>
+      <c r="K59">
+        <v>15</v>
+      </c>
+      <c r="L59">
+        <v>17</v>
+      </c>
+      <c r="M59">
+        <v>26</v>
+      </c>
+      <c r="N59">
+        <v>25</v>
+      </c>
+      <c r="O59" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60">
+        <v>1020</v>
+      </c>
+      <c r="C60" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" t="s">
+        <v>94</v>
+      </c>
+      <c r="E60" t="s">
+        <v>95</v>
+      </c>
+      <c r="F60" t="s">
+        <v>96</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H60" s="1">
+        <v>240</v>
+      </c>
+      <c r="I60">
+        <v>20</v>
+      </c>
+      <c r="J60">
+        <v>28</v>
+      </c>
+      <c r="K60">
+        <v>18</v>
+      </c>
+      <c r="L60">
+        <v>20</v>
+      </c>
+      <c r="M60">
+        <v>26</v>
+      </c>
+      <c r="N60">
+        <v>32</v>
+      </c>
+      <c r="O60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61">
+        <v>1021</v>
+      </c>
+      <c r="C61" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61" t="s">
+        <v>98</v>
+      </c>
+      <c r="E61" t="s">
+        <v>99</v>
+      </c>
+      <c r="F61" t="s">
+        <v>100</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H61" s="1">
+        <v>240</v>
+      </c>
+      <c r="I61">
+        <v>33</v>
+      </c>
+      <c r="J61">
+        <v>39</v>
+      </c>
+      <c r="K61">
+        <v>32</v>
+      </c>
+      <c r="L61">
+        <v>35</v>
+      </c>
+      <c r="M61">
+        <v>40</v>
+      </c>
+      <c r="N61">
+        <v>34</v>
+      </c>
+      <c r="O61" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62">
+        <v>1022</v>
+      </c>
+      <c r="C62" t="s">
+        <v>101</v>
+      </c>
+      <c r="D62" t="s">
+        <v>102</v>
+      </c>
+      <c r="E62" t="s">
+        <v>103</v>
+      </c>
+      <c r="F62" t="s">
+        <v>104</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H62" s="1">
+        <v>240</v>
+      </c>
+      <c r="I62">
+        <v>30</v>
+      </c>
+      <c r="J62">
+        <v>31</v>
+      </c>
+      <c r="K62">
+        <v>31</v>
+      </c>
+      <c r="L62">
+        <v>29</v>
+      </c>
+      <c r="M62">
+        <v>31</v>
+      </c>
+      <c r="N62">
+        <v>34</v>
+      </c>
+      <c r="O62" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63">
+        <v>1023</v>
+      </c>
+      <c r="C63" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" t="s">
+        <v>106</v>
+      </c>
+      <c r="E63" t="s">
+        <v>107</v>
+      </c>
+      <c r="F63" t="s">
+        <v>108</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H63" s="1">
+        <v>240</v>
+      </c>
+      <c r="I63">
+        <v>19</v>
+      </c>
+      <c r="J63">
+        <v>29</v>
+      </c>
+      <c r="K63">
+        <v>30</v>
+      </c>
+      <c r="L63">
+        <v>35</v>
+      </c>
+      <c r="M63">
+        <v>30</v>
+      </c>
+      <c r="N63">
+        <v>26</v>
+      </c>
+      <c r="O63" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64">
+        <v>1024</v>
+      </c>
+      <c r="C64" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" t="s">
+        <v>110</v>
+      </c>
+      <c r="E64" t="s">
+        <v>111</v>
+      </c>
+      <c r="F64" t="s">
+        <v>112</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H64" s="1">
+        <v>240</v>
+      </c>
+      <c r="I64">
+        <v>16</v>
+      </c>
+      <c r="J64">
+        <v>34</v>
+      </c>
+      <c r="K64">
+        <v>25</v>
+      </c>
+      <c r="L64">
+        <v>28</v>
+      </c>
+      <c r="M64">
+        <v>35</v>
+      </c>
+      <c r="N64">
+        <v>32</v>
+      </c>
+      <c r="O64" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65">
+        <v>1025</v>
+      </c>
+      <c r="C65" t="s">
+        <v>113</v>
+      </c>
+      <c r="D65" t="s">
+        <v>114</v>
+      </c>
+      <c r="E65" t="s">
+        <v>115</v>
+      </c>
+      <c r="F65" t="s">
+        <v>116</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H65" s="1">
+        <v>240</v>
+      </c>
+      <c r="I65">
+        <v>32</v>
+      </c>
+      <c r="J65">
+        <v>33</v>
+      </c>
+      <c r="K65">
+        <v>29</v>
+      </c>
+      <c r="L65">
+        <v>34</v>
+      </c>
+      <c r="M65">
+        <v>33</v>
+      </c>
+      <c r="N65">
+        <v>32</v>
+      </c>
+      <c r="O65" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66">
+        <v>1026</v>
+      </c>
+      <c r="C66" t="s">
+        <v>117</v>
+      </c>
+      <c r="D66" t="s">
+        <v>118</v>
+      </c>
+      <c r="E66" t="s">
+        <v>119</v>
+      </c>
+      <c r="F66" t="s">
+        <v>120</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H66" s="1">
+        <v>240</v>
+      </c>
+      <c r="I66">
+        <v>27</v>
+      </c>
+      <c r="J66">
+        <v>32</v>
+      </c>
+      <c r="K66">
+        <v>33</v>
+      </c>
+      <c r="L66">
+        <v>25</v>
+      </c>
+      <c r="M66">
+        <v>33</v>
+      </c>
+      <c r="N66">
+        <v>27</v>
+      </c>
+      <c r="O66" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67">
+        <v>1027</v>
+      </c>
+      <c r="C67" t="s">
+        <v>121</v>
+      </c>
+      <c r="D67" t="s">
+        <v>122</v>
+      </c>
+      <c r="E67" t="s">
+        <v>123</v>
+      </c>
+      <c r="F67" t="s">
+        <v>124</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H67" s="1">
+        <v>240</v>
+      </c>
+      <c r="I67">
+        <v>33</v>
+      </c>
+      <c r="J67">
+        <v>34</v>
+      </c>
+      <c r="K67">
+        <v>31</v>
+      </c>
+      <c r="L67">
+        <v>33</v>
+      </c>
+      <c r="M67">
+        <v>37</v>
+      </c>
+      <c r="N67">
+        <v>35</v>
+      </c>
+      <c r="O67" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68">
+        <v>1028</v>
+      </c>
+      <c r="C68" t="s">
+        <v>125</v>
+      </c>
+      <c r="D68" t="s">
+        <v>126</v>
+      </c>
+      <c r="E68" t="s">
+        <v>127</v>
+      </c>
+      <c r="F68" t="s">
+        <v>128</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H68" s="1">
+        <v>240</v>
+      </c>
+      <c r="I68">
+        <v>36</v>
+      </c>
+      <c r="J68">
+        <v>38</v>
+      </c>
+      <c r="K68">
+        <v>36</v>
+      </c>
+      <c r="L68">
+        <v>38</v>
+      </c>
+      <c r="M68">
+        <v>40</v>
+      </c>
+      <c r="N68">
+        <v>40</v>
+      </c>
+      <c r="O68" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69">
+        <v>1029</v>
+      </c>
+      <c r="C69" t="s">
+        <v>129</v>
+      </c>
+      <c r="D69" t="s">
+        <v>130</v>
+      </c>
+      <c r="E69" t="s">
+        <v>131</v>
+      </c>
+      <c r="F69" t="s">
+        <v>132</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H69" s="1">
+        <v>240</v>
+      </c>
+      <c r="I69">
+        <v>17</v>
+      </c>
+      <c r="J69">
+        <v>37</v>
+      </c>
+      <c r="K69">
+        <v>14</v>
+      </c>
+      <c r="L69">
+        <v>25</v>
+      </c>
+      <c r="M69">
+        <v>37</v>
+      </c>
+      <c r="N69">
+        <v>31</v>
+      </c>
+      <c r="O69" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70">
+        <v>1030</v>
+      </c>
+      <c r="C70" t="s">
+        <v>133</v>
+      </c>
+      <c r="D70" t="s">
+        <v>134</v>
+      </c>
+      <c r="E70" t="s">
+        <v>135</v>
+      </c>
+      <c r="F70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H70" s="1">
+        <v>240</v>
+      </c>
+      <c r="I70">
+        <v>16</v>
+      </c>
+      <c r="J70">
+        <v>30</v>
+      </c>
+      <c r="K70">
+        <v>16</v>
+      </c>
+      <c r="L70">
+        <v>18</v>
+      </c>
+      <c r="M70">
+        <v>29</v>
+      </c>
+      <c r="N70">
+        <v>25</v>
+      </c>
+      <c r="O70" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71">
+        <v>1031</v>
+      </c>
+      <c r="C71" t="s">
+        <v>137</v>
+      </c>
+      <c r="D71" t="s">
+        <v>138</v>
+      </c>
+      <c r="E71" t="s">
+        <v>139</v>
+      </c>
+      <c r="F71" t="s">
+        <v>140</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H71" s="1">
+        <v>240</v>
+      </c>
+      <c r="I71">
+        <v>14</v>
+      </c>
+      <c r="J71">
+        <v>23</v>
+      </c>
+      <c r="K71">
+        <v>14</v>
+      </c>
+      <c r="L71">
+        <v>17</v>
+      </c>
+      <c r="M71">
+        <v>20</v>
+      </c>
+      <c r="N71">
+        <v>27</v>
+      </c>
+      <c r="O71" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72">
+        <v>1032</v>
+      </c>
+      <c r="C72" t="s">
+        <v>141</v>
+      </c>
+      <c r="D72" t="s">
+        <v>142</v>
+      </c>
+      <c r="E72" t="s">
+        <v>143</v>
+      </c>
+      <c r="F72" t="s">
+        <v>144</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H72" s="1">
+        <v>240</v>
+      </c>
+      <c r="I72">
+        <v>15</v>
+      </c>
+      <c r="J72">
+        <v>36</v>
+      </c>
+      <c r="K72">
+        <v>14</v>
+      </c>
+      <c r="L72">
+        <v>19</v>
+      </c>
+      <c r="M72">
+        <v>37</v>
+      </c>
+      <c r="N72">
+        <v>31</v>
+      </c>
+      <c r="O72" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73">
+        <v>1033</v>
+      </c>
+      <c r="C73" t="s">
+        <v>145</v>
+      </c>
+      <c r="D73" t="s">
+        <v>146</v>
+      </c>
+      <c r="E73" t="s">
+        <v>147</v>
+      </c>
+      <c r="F73" t="s">
+        <v>148</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H73" s="1">
+        <v>240</v>
+      </c>
+      <c r="I73">
+        <v>14</v>
+      </c>
+      <c r="J73">
+        <v>34</v>
+      </c>
+      <c r="K73">
+        <v>26</v>
+      </c>
+      <c r="L73">
+        <v>23</v>
+      </c>
+      <c r="M73">
+        <v>39</v>
+      </c>
+      <c r="N73">
+        <v>28</v>
+      </c>
+      <c r="O73" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74">
+        <v>1034</v>
+      </c>
+      <c r="C74" t="s">
+        <v>149</v>
+      </c>
+      <c r="D74" t="s">
+        <v>150</v>
+      </c>
+      <c r="E74" t="s">
+        <v>151</v>
+      </c>
+      <c r="F74" t="s">
+        <v>152</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H74" s="1">
+        <v>240</v>
+      </c>
+      <c r="I74">
+        <v>29</v>
+      </c>
+      <c r="J74">
+        <v>32</v>
+      </c>
+      <c r="K74">
+        <v>22</v>
+      </c>
+      <c r="L74">
+        <v>28</v>
+      </c>
+      <c r="M74">
+        <v>34</v>
+      </c>
+      <c r="N74">
+        <v>23</v>
+      </c>
+      <c r="O74" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75">
+        <v>1035</v>
+      </c>
+      <c r="C75" t="s">
+        <v>153</v>
+      </c>
+      <c r="D75" t="s">
+        <v>154</v>
+      </c>
+      <c r="E75" t="s">
+        <v>155</v>
+      </c>
+      <c r="F75" t="s">
+        <v>156</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H75" s="1">
+        <v>240</v>
+      </c>
+      <c r="I75">
+        <v>33</v>
+      </c>
+      <c r="J75">
+        <v>36</v>
+      </c>
+      <c r="K75">
+        <v>34</v>
+      </c>
+      <c r="L75">
+        <v>37</v>
+      </c>
+      <c r="M75">
+        <v>36</v>
+      </c>
+      <c r="N75">
+        <v>34</v>
+      </c>
+      <c r="O75" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76">
+        <v>1036</v>
+      </c>
+      <c r="C76" t="s">
+        <v>157</v>
+      </c>
+      <c r="D76" t="s">
+        <v>158</v>
+      </c>
+      <c r="E76" t="s">
+        <v>159</v>
+      </c>
+      <c r="F76" t="s">
+        <v>160</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H76" s="1">
+        <v>240</v>
+      </c>
+      <c r="I76">
+        <v>33</v>
+      </c>
+      <c r="J76">
+        <v>35</v>
+      </c>
+      <c r="K76">
+        <v>34</v>
+      </c>
+      <c r="L76">
+        <v>38</v>
+      </c>
+      <c r="M76">
+        <v>34</v>
+      </c>
+      <c r="N76">
+        <v>32</v>
+      </c>
+      <c r="O76" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77">
+        <v>1037</v>
+      </c>
+      <c r="C77" t="s">
+        <v>161</v>
+      </c>
+      <c r="D77" t="s">
+        <v>162</v>
+      </c>
+      <c r="E77" t="s">
+        <v>163</v>
+      </c>
+      <c r="F77" t="s">
+        <v>164</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H77" s="1">
+        <v>240</v>
+      </c>
+      <c r="I77">
+        <v>32</v>
+      </c>
+      <c r="J77">
+        <v>39</v>
+      </c>
+      <c r="K77">
+        <v>40</v>
+      </c>
+      <c r="L77">
+        <v>38</v>
+      </c>
+      <c r="M77">
+        <v>40</v>
+      </c>
+      <c r="N77">
+        <v>34</v>
+      </c>
+      <c r="O77" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78">
+        <v>1038</v>
+      </c>
+      <c r="C78" t="s">
+        <v>165</v>
+      </c>
+      <c r="D78" t="s">
+        <v>166</v>
+      </c>
+      <c r="E78" t="s">
+        <v>167</v>
+      </c>
+      <c r="F78" t="s">
+        <v>168</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H78" s="1">
+        <v>240</v>
+      </c>
+      <c r="I78">
+        <v>37</v>
+      </c>
+      <c r="J78">
+        <v>35</v>
+      </c>
+      <c r="K78">
+        <v>36</v>
+      </c>
+      <c r="L78">
+        <v>36</v>
+      </c>
+      <c r="M78">
+        <v>36</v>
+      </c>
+      <c r="N78">
+        <v>39</v>
+      </c>
+      <c r="O78" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79">
+        <v>1039</v>
+      </c>
+      <c r="C79" t="s">
+        <v>169</v>
+      </c>
+      <c r="D79" t="s">
+        <v>170</v>
+      </c>
+      <c r="E79" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79" t="s">
+        <v>172</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H79" s="1">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACC0FB8-9C71-468C-A231-6DDA5A084C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF05BA2-3183-4A8F-B380-A3CA7F5E5962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13200" yWindow="60" windowWidth="15510" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="import streamlit as st_x000a_import p" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="175">
   <si>
     <t>Class</t>
   </si>
@@ -2724,22 +2735,22 @@
         <v>240</v>
       </c>
       <c r="I41">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J41">
+        <v>35</v>
+      </c>
+      <c r="K41">
+        <v>35</v>
+      </c>
+      <c r="L41">
         <v>31</v>
       </c>
-      <c r="K41">
-        <v>32</v>
-      </c>
-      <c r="L41">
-        <v>30</v>
-      </c>
       <c r="M41">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N41">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O41" t="s">
         <v>173</v>
@@ -2774,19 +2785,19 @@
         <v>23</v>
       </c>
       <c r="J42">
+        <v>29</v>
+      </c>
+      <c r="K42">
+        <v>15</v>
+      </c>
+      <c r="L42">
+        <v>20</v>
+      </c>
+      <c r="M42">
+        <v>29</v>
+      </c>
+      <c r="N42">
         <v>32</v>
-      </c>
-      <c r="K42">
-        <v>25</v>
-      </c>
-      <c r="L42">
-        <v>33</v>
-      </c>
-      <c r="M42">
-        <v>33</v>
-      </c>
-      <c r="N42">
-        <v>33</v>
       </c>
       <c r="O42" t="s">
         <v>173</v>
@@ -2818,22 +2829,22 @@
         <v>240</v>
       </c>
       <c r="I43">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J43">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K43">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L43">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="M43">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N43">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="O43" t="s">
         <v>173</v>
@@ -2865,22 +2876,22 @@
         <v>240</v>
       </c>
       <c r="I44">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="J44">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K44">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L44">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="M44">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="N44">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="O44" t="s">
         <v>173</v>
@@ -2912,22 +2923,22 @@
         <v>240</v>
       </c>
       <c r="I45">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J45">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K45">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L45">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="M45">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="N45">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O45" t="s">
         <v>173</v>
@@ -2959,22 +2970,22 @@
         <v>240</v>
       </c>
       <c r="I46">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J46">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K46">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L46">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M46">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N46">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O46" t="s">
         <v>173</v>
@@ -3006,22 +3017,22 @@
         <v>240</v>
       </c>
       <c r="I47">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J47">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K47">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L47">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M47">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="N47">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O47" t="s">
         <v>173</v>
@@ -3053,22 +3064,22 @@
         <v>240</v>
       </c>
       <c r="I48">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J48">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K48">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L48">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="M48">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="N48">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="O48" t="s">
         <v>173</v>
@@ -3100,22 +3111,22 @@
         <v>240</v>
       </c>
       <c r="I49">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J49">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K49">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L49">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="M49">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="N49">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O49" t="s">
         <v>173</v>
@@ -3147,22 +3158,22 @@
         <v>240</v>
       </c>
       <c r="I50">
+        <v>25</v>
+      </c>
+      <c r="J50">
+        <v>34</v>
+      </c>
+      <c r="K50">
         <v>24</v>
       </c>
-      <c r="J50">
+      <c r="L50">
+        <v>25</v>
+      </c>
+      <c r="M50">
         <v>35</v>
       </c>
-      <c r="K50">
-        <v>26</v>
-      </c>
-      <c r="L50">
-        <v>28</v>
-      </c>
-      <c r="M50">
-        <v>36</v>
-      </c>
       <c r="N50">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O50" t="s">
         <v>173</v>
@@ -3194,22 +3205,22 @@
         <v>240</v>
       </c>
       <c r="I51">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J51">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K51">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L51">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M51">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="N51">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="O51" t="s">
         <v>173</v>
@@ -3241,22 +3252,22 @@
         <v>240</v>
       </c>
       <c r="I52">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J52">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K52">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L52">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M52">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N52">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O52" t="s">
         <v>173</v>
@@ -3288,22 +3299,22 @@
         <v>240</v>
       </c>
       <c r="I53">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J53">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K53">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="L53">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="M53">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N53">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O53" t="s">
         <v>173</v>
@@ -3335,22 +3346,22 @@
         <v>240</v>
       </c>
       <c r="I54">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J54">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K54">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="L54">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M54">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N54">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O54" t="s">
         <v>173</v>
@@ -3382,22 +3393,22 @@
         <v>240</v>
       </c>
       <c r="I55">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J55">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K55">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L55">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M55">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N55">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O55" t="s">
         <v>173</v>
@@ -3429,22 +3440,22 @@
         <v>240</v>
       </c>
       <c r="I56">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J56">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K56">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L56">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M56">
         <v>34</v>
       </c>
       <c r="N56">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O56" t="s">
         <v>173</v>
@@ -3476,22 +3487,22 @@
         <v>240</v>
       </c>
       <c r="I57">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J57">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K57">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L57">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="M57">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="N57">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O57" t="s">
         <v>173</v>
@@ -3523,22 +3534,22 @@
         <v>240</v>
       </c>
       <c r="I58">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J58">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K58">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L58">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M58">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="N58">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="O58" t="s">
         <v>173</v>
@@ -3573,19 +3584,19 @@
         <v>22</v>
       </c>
       <c r="J59">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K59">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L59">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M59">
         <v>26</v>
       </c>
       <c r="N59">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="O59" t="s">
         <v>173</v>
@@ -3620,19 +3631,19 @@
         <v>20</v>
       </c>
       <c r="J60">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K60">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L60">
         <v>20</v>
       </c>
       <c r="M60">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N60">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O60" t="s">
         <v>173</v>
@@ -3664,22 +3675,22 @@
         <v>240</v>
       </c>
       <c r="I61">
+        <v>18</v>
+      </c>
+      <c r="J61">
+        <v>34</v>
+      </c>
+      <c r="K61">
+        <v>20</v>
+      </c>
+      <c r="L61">
+        <v>20</v>
+      </c>
+      <c r="M61">
+        <v>34</v>
+      </c>
+      <c r="N61">
         <v>33</v>
-      </c>
-      <c r="J61">
-        <v>39</v>
-      </c>
-      <c r="K61">
-        <v>32</v>
-      </c>
-      <c r="L61">
-        <v>35</v>
-      </c>
-      <c r="M61">
-        <v>40</v>
-      </c>
-      <c r="N61">
-        <v>34</v>
       </c>
       <c r="O61" t="s">
         <v>173</v>
@@ -3711,19 +3722,19 @@
         <v>240</v>
       </c>
       <c r="I62">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J62">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K62">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="L62">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M62">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N62">
         <v>34</v>
@@ -3758,22 +3769,22 @@
         <v>240</v>
       </c>
       <c r="I63">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J63">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K63">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L63">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M63">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N63">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O63" t="s">
         <v>173</v>
@@ -3805,22 +3816,22 @@
         <v>240</v>
       </c>
       <c r="I64">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="J64">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K64">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L64">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="M64">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N64">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O64" t="s">
         <v>173</v>
@@ -3852,22 +3863,22 @@
         <v>240</v>
       </c>
       <c r="I65">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J65">
         <v>33</v>
       </c>
       <c r="K65">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L65">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="M65">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N65">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="O65" t="s">
         <v>173</v>
@@ -3899,22 +3910,22 @@
         <v>240</v>
       </c>
       <c r="I66">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J66">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K66">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L66">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M66">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N66">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="O66" t="s">
         <v>173</v>
@@ -3946,22 +3957,22 @@
         <v>240</v>
       </c>
       <c r="I67">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J67">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K67">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L67">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M67">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="N67">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O67" t="s">
         <v>173</v>
@@ -3993,22 +4004,22 @@
         <v>240</v>
       </c>
       <c r="I68">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J68">
+        <v>30</v>
+      </c>
+      <c r="K68">
         <v>38</v>
       </c>
-      <c r="K68">
-        <v>36</v>
-      </c>
       <c r="L68">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M68">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N68">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="O68" t="s">
         <v>173</v>
@@ -4040,22 +4051,22 @@
         <v>240</v>
       </c>
       <c r="I69">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J69">
         <v>37</v>
       </c>
       <c r="K69">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="L69">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M69">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N69">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="O69" t="s">
         <v>173</v>
@@ -4087,22 +4098,22 @@
         <v>240</v>
       </c>
       <c r="I70">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J70">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K70">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L70">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M70">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N70">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O70" t="s">
         <v>173</v>
@@ -4134,22 +4145,22 @@
         <v>240</v>
       </c>
       <c r="I71">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="J71">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K71">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="L71">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="M71">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="N71">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="O71" t="s">
         <v>173</v>
@@ -4181,22 +4192,22 @@
         <v>240</v>
       </c>
       <c r="I72">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J72">
+        <v>33</v>
+      </c>
+      <c r="K72">
+        <v>32</v>
+      </c>
+      <c r="L72">
         <v>36</v>
       </c>
-      <c r="K72">
-        <v>14</v>
-      </c>
-      <c r="L72">
-        <v>19</v>
-      </c>
       <c r="M72">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N72">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O72" t="s">
         <v>173</v>
@@ -4228,22 +4239,22 @@
         <v>240</v>
       </c>
       <c r="I73">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J73">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K73">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L73">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M73">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N73">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O73" t="s">
         <v>173</v>
@@ -4275,22 +4286,22 @@
         <v>240</v>
       </c>
       <c r="I74">
+        <v>16</v>
+      </c>
+      <c r="J74">
         <v>29</v>
       </c>
-      <c r="J74">
+      <c r="K74">
+        <v>30</v>
+      </c>
+      <c r="L74">
+        <v>29</v>
+      </c>
+      <c r="M74">
+        <v>31</v>
+      </c>
+      <c r="N74">
         <v>32</v>
-      </c>
-      <c r="K74">
-        <v>22</v>
-      </c>
-      <c r="L74">
-        <v>28</v>
-      </c>
-      <c r="M74">
-        <v>34</v>
-      </c>
-      <c r="N74">
-        <v>23</v>
       </c>
       <c r="O74" t="s">
         <v>173</v>
@@ -4322,19 +4333,19 @@
         <v>240</v>
       </c>
       <c r="I75">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J75">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K75">
+        <v>18</v>
+      </c>
+      <c r="L75">
         <v>34</v>
       </c>
-      <c r="L75">
-        <v>37</v>
-      </c>
       <c r="M75">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="N75">
         <v>34</v>
@@ -4369,22 +4380,22 @@
         <v>240</v>
       </c>
       <c r="I76">
+        <v>28</v>
+      </c>
+      <c r="J76">
+        <v>32</v>
+      </c>
+      <c r="K76">
+        <v>22</v>
+      </c>
+      <c r="L76">
         <v>33</v>
       </c>
-      <c r="J76">
-        <v>35</v>
-      </c>
-      <c r="K76">
-        <v>34</v>
-      </c>
-      <c r="L76">
-        <v>38</v>
-      </c>
       <c r="M76">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N76">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="O76" t="s">
         <v>173</v>
@@ -4416,22 +4427,22 @@
         <v>240</v>
       </c>
       <c r="I77">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J77">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K77">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L77">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="M77">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N77">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O77" t="s">
         <v>173</v>
@@ -4463,22 +4474,22 @@
         <v>240</v>
       </c>
       <c r="I78">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J78">
+        <v>34</v>
+      </c>
+      <c r="K78">
+        <v>33</v>
+      </c>
+      <c r="L78">
         <v>35</v>
       </c>
-      <c r="K78">
-        <v>36</v>
-      </c>
-      <c r="L78">
-        <v>36</v>
-      </c>
       <c r="M78">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N78">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O78" t="s">
         <v>173</v>
@@ -4508,12 +4519,33 @@
       </c>
       <c r="H79" s="1">
         <v>240</v>
+      </c>
+      <c r="I79">
+        <v>27</v>
+      </c>
+      <c r="J79">
+        <v>36</v>
+      </c>
+      <c r="K79">
+        <v>26</v>
+      </c>
+      <c r="L79">
+        <v>33</v>
+      </c>
+      <c r="M79">
+        <v>36</v>
+      </c>
+      <c r="N79">
+        <v>39</v>
+      </c>
+      <c r="O79" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="F2:F40" numberStoredAsText="1"/>
+    <ignoredError sqref="F2:F40 F41:F79" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF05BA2-3183-4A8F-B380-A3CA7F5E5962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B98187-7B23-4E40-96D3-B4EB6FFEE41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,7 +876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -896,34 +896,34 @@
         <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="H2" s="1">
         <v>240</v>
       </c>
-      <c r="I2" s="1">
-        <v>28</v>
-      </c>
-      <c r="J2" s="1">
-        <v>39</v>
-      </c>
-      <c r="K2" s="1">
-        <v>26</v>
-      </c>
-      <c r="L2" s="1">
-        <v>22</v>
-      </c>
-      <c r="M2" s="1">
-        <v>33</v>
-      </c>
-      <c r="N2" s="1">
-        <v>39</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I2">
+        <v>29</v>
+      </c>
+      <c r="J2">
+        <v>35</v>
+      </c>
+      <c r="K2">
+        <v>35</v>
+      </c>
+      <c r="L2">
+        <v>31</v>
+      </c>
+      <c r="M2">
+        <v>38</v>
+      </c>
+      <c r="N2">
+        <v>38</v>
+      </c>
+      <c r="O2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -943,34 +943,34 @@
         <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="H3" s="1">
         <v>240</v>
       </c>
-      <c r="I3" s="1">
-        <v>17</v>
-      </c>
-      <c r="J3" s="1">
-        <v>33</v>
-      </c>
-      <c r="K3" s="1">
-        <v>14</v>
-      </c>
-      <c r="L3" s="1">
-        <v>18</v>
-      </c>
-      <c r="M3" s="1">
+      <c r="I3">
+        <v>23</v>
+      </c>
+      <c r="J3">
         <v>29</v>
       </c>
-      <c r="N3" s="1">
-        <v>33</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="K3">
+        <v>15</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
+      </c>
+      <c r="M3">
+        <v>29</v>
+      </c>
+      <c r="N3">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -990,30 +990,30 @@
         <v>28</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="H4" s="1">
         <v>240</v>
       </c>
-      <c r="I4" s="1">
-        <v>23</v>
-      </c>
-      <c r="J4" s="1">
-        <v>40</v>
-      </c>
-      <c r="K4" s="1">
-        <v>21</v>
-      </c>
-      <c r="L4" s="1">
-        <v>14</v>
-      </c>
-      <c r="M4" s="1">
+      <c r="I4">
+        <v>31</v>
+      </c>
+      <c r="J4">
+        <v>35</v>
+      </c>
+      <c r="K4">
+        <v>29</v>
+      </c>
+      <c r="L4">
+        <v>29</v>
+      </c>
+      <c r="M4">
         <v>38</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N4">
         <v>37</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1036,29 +1036,29 @@
       <c r="F5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" t="s">
-        <v>16</v>
+      <c r="G5" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H5" s="1">
         <v>240</v>
       </c>
       <c r="I5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J5">
+        <v>37</v>
+      </c>
+      <c r="K5">
+        <v>38</v>
+      </c>
+      <c r="L5">
+        <v>39</v>
+      </c>
+      <c r="M5">
+        <v>36</v>
+      </c>
+      <c r="N5">
         <v>40</v>
-      </c>
-      <c r="K5">
-        <v>39</v>
-      </c>
-      <c r="L5">
-        <v>34</v>
-      </c>
-      <c r="M5">
-        <v>38</v>
-      </c>
-      <c r="N5">
-        <v>39</v>
       </c>
       <c r="O5" t="s">
         <v>173</v>
@@ -1083,29 +1083,29 @@
       <c r="F6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" t="s">
-        <v>16</v>
+      <c r="G6" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H6" s="1">
         <v>240</v>
       </c>
       <c r="I6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J6">
+        <v>34</v>
+      </c>
+      <c r="K6">
+        <v>32</v>
+      </c>
+      <c r="L6">
         <v>39</v>
       </c>
-      <c r="K6">
-        <v>33</v>
-      </c>
-      <c r="L6">
-        <v>30</v>
-      </c>
       <c r="M6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" t="s">
         <v>173</v>
@@ -1130,29 +1130,29 @@
       <c r="F7" t="s">
         <v>40</v>
       </c>
-      <c r="G7" t="s">
-        <v>16</v>
+      <c r="G7" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H7" s="1">
         <v>240</v>
       </c>
       <c r="I7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M7">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N7">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="O7" t="s">
         <v>173</v>
@@ -1177,26 +1177,26 @@
       <c r="F8" t="s">
         <v>44</v>
       </c>
-      <c r="G8" t="s">
-        <v>16</v>
+      <c r="G8" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H8" s="1">
         <v>240</v>
       </c>
       <c r="I8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J8">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M8">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N8">
         <v>36</v>
@@ -1224,29 +1224,29 @@
       <c r="F9" t="s">
         <v>48</v>
       </c>
-      <c r="G9" t="s">
-        <v>16</v>
+      <c r="G9" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H9" s="1">
         <v>240</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K9">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O9" t="s">
         <v>173</v>
@@ -1271,29 +1271,29 @@
       <c r="F10" t="s">
         <v>52</v>
       </c>
-      <c r="G10" t="s">
-        <v>16</v>
+      <c r="G10" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H10" s="1">
         <v>240</v>
       </c>
       <c r="I10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J10">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L10">
+        <v>24</v>
+      </c>
+      <c r="M10">
         <v>25</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>34</v>
-      </c>
-      <c r="N10">
-        <v>36</v>
       </c>
       <c r="O10" t="s">
         <v>173</v>
@@ -1318,26 +1318,26 @@
       <c r="F11" t="s">
         <v>56</v>
       </c>
-      <c r="G11" t="s">
-        <v>16</v>
+      <c r="G11" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H11" s="1">
         <v>240</v>
       </c>
       <c r="I11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J11">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M11">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N11">
         <v>35</v>
@@ -1365,29 +1365,29 @@
       <c r="F12" t="s">
         <v>60</v>
       </c>
-      <c r="G12" t="s">
-        <v>16</v>
+      <c r="G12" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H12" s="1">
         <v>240</v>
       </c>
       <c r="I12">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J12">
+        <v>32</v>
+      </c>
+      <c r="K12">
+        <v>24</v>
+      </c>
+      <c r="L12">
+        <v>34</v>
+      </c>
+      <c r="M12">
+        <v>32</v>
+      </c>
+      <c r="N12">
         <v>38</v>
-      </c>
-      <c r="K12">
-        <v>23</v>
-      </c>
-      <c r="L12">
-        <v>28</v>
-      </c>
-      <c r="M12">
-        <v>37</v>
-      </c>
-      <c r="N12">
-        <v>39</v>
       </c>
       <c r="O12" t="s">
         <v>173</v>
@@ -1412,14 +1412,14 @@
       <c r="F13" t="s">
         <v>64</v>
       </c>
-      <c r="G13" t="s">
-        <v>16</v>
+      <c r="G13" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H13" s="1">
         <v>240</v>
       </c>
       <c r="I13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J13">
         <v>20</v>
@@ -1428,13 +1428,13 @@
         <v>14</v>
       </c>
       <c r="L13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N13">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O13" t="s">
         <v>173</v>
@@ -1459,29 +1459,29 @@
       <c r="F14" t="s">
         <v>68</v>
       </c>
-      <c r="G14" t="s">
-        <v>16</v>
+      <c r="G14" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H14" s="1">
         <v>240</v>
       </c>
       <c r="I14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J14">
+        <v>36</v>
+      </c>
+      <c r="K14">
+        <v>36</v>
+      </c>
+      <c r="L14">
+        <v>34</v>
+      </c>
+      <c r="M14">
         <v>40</v>
       </c>
-      <c r="K14">
-        <v>35</v>
-      </c>
-      <c r="L14">
-        <v>29</v>
-      </c>
-      <c r="M14">
-        <v>37</v>
-      </c>
       <c r="N14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O14" t="s">
         <v>173</v>
@@ -1506,29 +1506,29 @@
       <c r="F15" t="s">
         <v>72</v>
       </c>
-      <c r="G15" t="s">
-        <v>16</v>
+      <c r="G15" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H15" s="1">
         <v>240</v>
       </c>
       <c r="I15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J15">
+        <v>39</v>
+      </c>
+      <c r="K15">
+        <v>36</v>
+      </c>
+      <c r="L15">
+        <v>38</v>
+      </c>
+      <c r="M15">
+        <v>39</v>
+      </c>
+      <c r="N15">
         <v>40</v>
-      </c>
-      <c r="K15">
-        <v>35</v>
-      </c>
-      <c r="L15">
-        <v>30</v>
-      </c>
-      <c r="M15">
-        <v>38</v>
-      </c>
-      <c r="N15">
-        <v>39</v>
       </c>
       <c r="O15" t="s">
         <v>173</v>
@@ -1553,29 +1553,29 @@
       <c r="F16" t="s">
         <v>76</v>
       </c>
-      <c r="G16" t="s">
-        <v>16</v>
+      <c r="G16" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H16" s="1">
         <v>240</v>
       </c>
       <c r="I16">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J16">
+        <v>38</v>
+      </c>
+      <c r="K16">
+        <v>34</v>
+      </c>
+      <c r="L16">
+        <v>38</v>
+      </c>
+      <c r="M16">
         <v>40</v>
       </c>
-      <c r="K16">
-        <v>29</v>
-      </c>
-      <c r="L16">
-        <v>28</v>
-      </c>
-      <c r="M16">
-        <v>38</v>
-      </c>
       <c r="N16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O16" t="s">
         <v>173</v>
@@ -1600,29 +1600,29 @@
       <c r="F17" t="s">
         <v>80</v>
       </c>
-      <c r="G17" t="s">
-        <v>16</v>
+      <c r="G17" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H17" s="1">
         <v>240</v>
       </c>
       <c r="I17">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J17">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K17">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L17">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M17">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="N17">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O17" t="s">
         <v>173</v>
@@ -1647,29 +1647,29 @@
       <c r="F18" t="s">
         <v>84</v>
       </c>
-      <c r="G18" t="s">
-        <v>16</v>
+      <c r="G18" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H18" s="1">
         <v>240</v>
       </c>
       <c r="I18">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J18">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K18">
+        <v>31</v>
+      </c>
+      <c r="L18">
+        <v>38</v>
+      </c>
+      <c r="M18">
         <v>32</v>
       </c>
-      <c r="L18">
-        <v>25</v>
-      </c>
-      <c r="M18">
-        <v>31</v>
-      </c>
       <c r="N18">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O18" t="s">
         <v>173</v>
@@ -1694,29 +1694,29 @@
       <c r="F19" t="s">
         <v>88</v>
       </c>
-      <c r="G19" t="s">
-        <v>16</v>
+      <c r="G19" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H19" s="1">
         <v>240</v>
       </c>
       <c r="I19">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J19">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K19">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M19">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N19">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O19" t="s">
         <v>173</v>
@@ -1741,29 +1741,29 @@
       <c r="F20" t="s">
         <v>92</v>
       </c>
-      <c r="G20" t="s">
-        <v>16</v>
+      <c r="G20" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H20" s="1">
         <v>240</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O20" t="s">
         <v>173</v>
@@ -1788,29 +1788,29 @@
       <c r="F21" t="s">
         <v>96</v>
       </c>
-      <c r="G21" t="s">
-        <v>16</v>
+      <c r="G21" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H21" s="1">
         <v>240</v>
       </c>
       <c r="I21">
+        <v>20</v>
+      </c>
+      <c r="J21">
+        <v>27</v>
+      </c>
+      <c r="K21">
         <v>23</v>
       </c>
-      <c r="J21">
-        <v>37</v>
-      </c>
-      <c r="K21">
-        <v>18</v>
-      </c>
       <c r="L21">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M21">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O21" t="s">
         <v>173</v>
@@ -1835,29 +1835,29 @@
       <c r="F22" t="s">
         <v>100</v>
       </c>
-      <c r="G22" t="s">
-        <v>16</v>
+      <c r="G22" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H22" s="1">
         <v>240</v>
       </c>
       <c r="I22">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J22">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L22">
         <v>20</v>
       </c>
       <c r="M22">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N22">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O22" t="s">
         <v>173</v>
@@ -1882,29 +1882,29 @@
       <c r="F23" t="s">
         <v>104</v>
       </c>
-      <c r="G23" t="s">
-        <v>16</v>
+      <c r="G23" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H23" s="1">
         <v>240</v>
       </c>
       <c r="I23">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J23">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K23">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L23">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M23">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N23">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O23" t="s">
         <v>173</v>
@@ -1929,29 +1929,29 @@
       <c r="F24" t="s">
         <v>108</v>
       </c>
-      <c r="G24" t="s">
-        <v>16</v>
+      <c r="G24" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H24" s="1">
         <v>240</v>
       </c>
       <c r="I24">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J24">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="K24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L24">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="M24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N24">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O24" t="s">
         <v>173</v>
@@ -1976,29 +1976,29 @@
       <c r="F25" t="s">
         <v>112</v>
       </c>
-      <c r="G25" t="s">
-        <v>16</v>
+      <c r="G25" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H25" s="1">
         <v>240</v>
       </c>
       <c r="I25">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J25">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K25">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L25">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="M25">
         <v>38</v>
       </c>
       <c r="N25">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O25" t="s">
         <v>173</v>
@@ -2023,26 +2023,26 @@
       <c r="F26" t="s">
         <v>116</v>
       </c>
-      <c r="G26" t="s">
-        <v>16</v>
+      <c r="G26" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H26" s="1">
         <v>240</v>
       </c>
       <c r="I26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J26">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K26">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L26">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M26">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N26">
         <v>39</v>
@@ -2070,29 +2070,29 @@
       <c r="F27" t="s">
         <v>120</v>
       </c>
-      <c r="G27" t="s">
-        <v>16</v>
+      <c r="G27" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H27" s="1">
         <v>240</v>
       </c>
       <c r="I27">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J27">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K27">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L27">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M27">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N27">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O27" t="s">
         <v>173</v>
@@ -2117,29 +2117,29 @@
       <c r="F28" t="s">
         <v>124</v>
       </c>
-      <c r="G28" t="s">
-        <v>16</v>
+      <c r="G28" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H28" s="1">
         <v>240</v>
       </c>
       <c r="I28">
+        <v>26</v>
+      </c>
+      <c r="J28">
+        <v>30</v>
+      </c>
+      <c r="K28">
         <v>25</v>
       </c>
-      <c r="J28">
-        <v>39</v>
-      </c>
-      <c r="K28">
-        <v>21</v>
-      </c>
       <c r="L28">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M28">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N28">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O28" t="s">
         <v>173</v>
@@ -2164,8 +2164,8 @@
       <c r="F29" t="s">
         <v>128</v>
       </c>
-      <c r="G29" t="s">
-        <v>16</v>
+      <c r="G29" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H29" s="1">
         <v>240</v>
@@ -2174,19 +2174,19 @@
         <v>26</v>
       </c>
       <c r="J29">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K29">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L29">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="M29">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N29">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O29" t="s">
         <v>173</v>
@@ -2211,8 +2211,8 @@
       <c r="F30" t="s">
         <v>132</v>
       </c>
-      <c r="G30" t="s">
-        <v>16</v>
+      <c r="G30" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H30" s="1">
         <v>240</v>
@@ -2221,16 +2221,16 @@
         <v>30</v>
       </c>
       <c r="J30">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K30">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L30">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N30">
         <v>38</v>
@@ -2258,29 +2258,29 @@
       <c r="F31" t="s">
         <v>136</v>
       </c>
-      <c r="G31" t="s">
-        <v>16</v>
+      <c r="G31" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H31" s="1">
         <v>240</v>
       </c>
       <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
         <v>36</v>
       </c>
-      <c r="J31">
-        <v>38</v>
-      </c>
       <c r="K31">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N31">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O31" t="s">
         <v>173</v>
@@ -2305,26 +2305,26 @@
       <c r="F32" t="s">
         <v>140</v>
       </c>
-      <c r="G32" t="s">
-        <v>16</v>
+      <c r="G32" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H32" s="1">
         <v>240</v>
       </c>
       <c r="I32">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J32">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L32">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M32">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N32">
         <v>39</v>
@@ -2352,26 +2352,26 @@
       <c r="F33" t="s">
         <v>144</v>
       </c>
-      <c r="G33" t="s">
-        <v>16</v>
+      <c r="G33" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H33" s="1">
         <v>240</v>
       </c>
       <c r="I33">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J33">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K33">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L33">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M33">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N33">
         <v>39</v>
@@ -2399,29 +2399,29 @@
       <c r="F34" t="s">
         <v>148</v>
       </c>
-      <c r="G34" t="s">
-        <v>16</v>
+      <c r="G34" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H34" s="1">
         <v>240</v>
       </c>
       <c r="I34">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J34">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K34">
+        <v>30</v>
+      </c>
+      <c r="L34">
         <v>28</v>
       </c>
-      <c r="L34">
-        <v>26</v>
-      </c>
       <c r="M34">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="N34">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="O34" t="s">
         <v>173</v>
@@ -2446,26 +2446,26 @@
       <c r="F35" t="s">
         <v>152</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H35" s="1">
+        <v>240</v>
+      </c>
+      <c r="I35">
         <v>16</v>
       </c>
-      <c r="H35" s="1">
-        <v>240</v>
-      </c>
-      <c r="I35">
-        <v>20</v>
-      </c>
       <c r="J35">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="K35">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L35">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M35">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N35">
         <v>32</v>
@@ -2493,29 +2493,29 @@
       <c r="F36" t="s">
         <v>156</v>
       </c>
-      <c r="G36" t="s">
-        <v>16</v>
+      <c r="G36" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H36" s="1">
         <v>240</v>
       </c>
       <c r="I36">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J36">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K36">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L36">
+        <v>34</v>
+      </c>
+      <c r="M36">
         <v>26</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>34</v>
-      </c>
-      <c r="N36">
-        <v>39</v>
       </c>
       <c r="O36" t="s">
         <v>173</v>
@@ -2540,29 +2540,29 @@
       <c r="F37" t="s">
         <v>160</v>
       </c>
-      <c r="G37" t="s">
-        <v>16</v>
+      <c r="G37" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H37" s="1">
         <v>240</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="O37" t="s">
         <v>173</v>
@@ -2587,26 +2587,26 @@
       <c r="F38" t="s">
         <v>164</v>
       </c>
-      <c r="G38" t="s">
-        <v>16</v>
+      <c r="G38" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H38" s="1">
         <v>240</v>
       </c>
       <c r="I38">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J38">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K38">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L38">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M38">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="N38">
         <v>37</v>
@@ -2634,8 +2634,8 @@
       <c r="F39" t="s">
         <v>168</v>
       </c>
-      <c r="G39" t="s">
-        <v>16</v>
+      <c r="G39" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H39" s="1">
         <v>240</v>
@@ -2644,19 +2644,19 @@
         <v>28</v>
       </c>
       <c r="J39">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K39">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L39">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="M39">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N39">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O39" t="s">
         <v>173</v>
@@ -2681,29 +2681,29 @@
       <c r="F40" t="s">
         <v>172</v>
       </c>
-      <c r="G40" t="s">
-        <v>16</v>
+      <c r="G40" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H40" s="1">
         <v>240</v>
       </c>
       <c r="I40">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J40">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K40">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L40">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M40">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N40">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O40" t="s">
         <v>173</v>
@@ -2729,30 +2729,30 @@
         <v>20</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="H41" s="1">
         <v>240</v>
       </c>
-      <c r="I41">
-        <v>29</v>
-      </c>
-      <c r="J41">
-        <v>35</v>
-      </c>
-      <c r="K41">
-        <v>35</v>
-      </c>
-      <c r="L41">
-        <v>31</v>
-      </c>
-      <c r="M41">
-        <v>38</v>
-      </c>
-      <c r="N41">
-        <v>38</v>
-      </c>
-      <c r="O41" t="s">
+      <c r="I41" s="1">
+        <v>28</v>
+      </c>
+      <c r="J41" s="1">
+        <v>39</v>
+      </c>
+      <c r="K41" s="1">
+        <v>26</v>
+      </c>
+      <c r="L41" s="1">
+        <v>22</v>
+      </c>
+      <c r="M41" s="1">
+        <v>33</v>
+      </c>
+      <c r="N41" s="1">
+        <v>39</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2776,30 +2776,30 @@
         <v>24</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="H42" s="1">
         <v>240</v>
       </c>
-      <c r="I42">
-        <v>23</v>
-      </c>
-      <c r="J42">
+      <c r="I42" s="1">
+        <v>17</v>
+      </c>
+      <c r="J42" s="1">
+        <v>33</v>
+      </c>
+      <c r="K42" s="1">
+        <v>14</v>
+      </c>
+      <c r="L42" s="1">
+        <v>18</v>
+      </c>
+      <c r="M42" s="1">
         <v>29</v>
       </c>
-      <c r="K42">
-        <v>15</v>
-      </c>
-      <c r="L42">
-        <v>20</v>
-      </c>
-      <c r="M42">
-        <v>29</v>
-      </c>
-      <c r="N42">
-        <v>32</v>
-      </c>
-      <c r="O42" t="s">
+      <c r="N42" s="1">
+        <v>33</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2823,30 +2823,30 @@
         <v>28</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="H43" s="1">
         <v>240</v>
       </c>
-      <c r="I43">
-        <v>31</v>
-      </c>
-      <c r="J43">
-        <v>35</v>
-      </c>
-      <c r="K43">
-        <v>29</v>
-      </c>
-      <c r="L43">
-        <v>29</v>
-      </c>
-      <c r="M43">
+      <c r="I43" s="1">
+        <v>23</v>
+      </c>
+      <c r="J43" s="1">
+        <v>40</v>
+      </c>
+      <c r="K43" s="1">
+        <v>21</v>
+      </c>
+      <c r="L43" s="1">
+        <v>14</v>
+      </c>
+      <c r="M43" s="1">
         <v>38</v>
       </c>
-      <c r="N43">
+      <c r="N43" s="1">
         <v>37</v>
       </c>
-      <c r="O43" t="s">
+      <c r="O43" s="1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2869,29 +2869,29 @@
       <c r="F44" t="s">
         <v>32</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>174</v>
+      <c r="G44" t="s">
+        <v>16</v>
       </c>
       <c r="H44" s="1">
         <v>240</v>
       </c>
       <c r="I44">
+        <v>33</v>
+      </c>
+      <c r="J44">
+        <v>40</v>
+      </c>
+      <c r="K44">
+        <v>39</v>
+      </c>
+      <c r="L44">
         <v>34</v>
       </c>
-      <c r="J44">
-        <v>37</v>
-      </c>
-      <c r="K44">
+      <c r="M44">
         <v>38</v>
       </c>
-      <c r="L44">
+      <c r="N44">
         <v>39</v>
-      </c>
-      <c r="M44">
-        <v>36</v>
-      </c>
-      <c r="N44">
-        <v>40</v>
       </c>
       <c r="O44" t="s">
         <v>173</v>
@@ -2916,29 +2916,29 @@
       <c r="F45" t="s">
         <v>36</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>174</v>
+      <c r="G45" t="s">
+        <v>16</v>
       </c>
       <c r="H45" s="1">
         <v>240</v>
       </c>
       <c r="I45">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J45">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K45">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L45">
+        <v>30</v>
+      </c>
+      <c r="M45">
+        <v>35</v>
+      </c>
+      <c r="N45">
         <v>39</v>
-      </c>
-      <c r="M45">
-        <v>36</v>
-      </c>
-      <c r="N45">
-        <v>38</v>
       </c>
       <c r="O45" t="s">
         <v>173</v>
@@ -2963,29 +2963,29 @@
       <c r="F46" t="s">
         <v>40</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>174</v>
+      <c r="G46" t="s">
+        <v>16</v>
       </c>
       <c r="H46" s="1">
         <v>240</v>
       </c>
       <c r="I46">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J46">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K46">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L46">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M46">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N46">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="O46" t="s">
         <v>173</v>
@@ -3010,26 +3010,26 @@
       <c r="F47" t="s">
         <v>44</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>174</v>
+      <c r="G47" t="s">
+        <v>16</v>
       </c>
       <c r="H47" s="1">
         <v>240</v>
       </c>
       <c r="I47">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J47">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K47">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L47">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="M47">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N47">
         <v>36</v>
@@ -3057,29 +3057,29 @@
       <c r="F48" t="s">
         <v>48</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>174</v>
+      <c r="G48" t="s">
+        <v>16</v>
       </c>
       <c r="H48" s="1">
         <v>240</v>
       </c>
       <c r="I48">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J48">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="L48">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O48" t="s">
         <v>173</v>
@@ -3104,29 +3104,29 @@
       <c r="F49" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>174</v>
+      <c r="G49" t="s">
+        <v>16</v>
       </c>
       <c r="H49" s="1">
         <v>240</v>
       </c>
       <c r="I49">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J49">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K49">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L49">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M49">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="N49">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O49" t="s">
         <v>173</v>
@@ -3151,26 +3151,26 @@
       <c r="F50" t="s">
         <v>56</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>174</v>
+      <c r="G50" t="s">
+        <v>16</v>
       </c>
       <c r="H50" s="1">
         <v>240</v>
       </c>
       <c r="I50">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J50">
+        <v>37</v>
+      </c>
+      <c r="K50">
+        <v>26</v>
+      </c>
+      <c r="L50">
+        <v>26</v>
+      </c>
+      <c r="M50">
         <v>34</v>
-      </c>
-      <c r="K50">
-        <v>24</v>
-      </c>
-      <c r="L50">
-        <v>25</v>
-      </c>
-      <c r="M50">
-        <v>35</v>
       </c>
       <c r="N50">
         <v>35</v>
@@ -3198,29 +3198,29 @@
       <c r="F51" t="s">
         <v>60</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>174</v>
+      <c r="G51" t="s">
+        <v>16</v>
       </c>
       <c r="H51" s="1">
         <v>240</v>
       </c>
       <c r="I51">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J51">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K51">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L51">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M51">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N51">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O51" t="s">
         <v>173</v>
@@ -3245,14 +3245,14 @@
       <c r="F52" t="s">
         <v>64</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>174</v>
+      <c r="G52" t="s">
+        <v>16</v>
       </c>
       <c r="H52" s="1">
         <v>240</v>
       </c>
       <c r="I52">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J52">
         <v>20</v>
@@ -3261,13 +3261,13 @@
         <v>14</v>
       </c>
       <c r="L52">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M52">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N52">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O52" t="s">
         <v>173</v>
@@ -3292,29 +3292,29 @@
       <c r="F53" t="s">
         <v>68</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>174</v>
+      <c r="G53" t="s">
+        <v>16</v>
       </c>
       <c r="H53" s="1">
         <v>240</v>
       </c>
       <c r="I53">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J53">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K53">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L53">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M53">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N53">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O53" t="s">
         <v>173</v>
@@ -3339,29 +3339,29 @@
       <c r="F54" t="s">
         <v>72</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>174</v>
+      <c r="G54" t="s">
+        <v>16</v>
       </c>
       <c r="H54" s="1">
         <v>240</v>
       </c>
       <c r="I54">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J54">
+        <v>40</v>
+      </c>
+      <c r="K54">
+        <v>35</v>
+      </c>
+      <c r="L54">
+        <v>30</v>
+      </c>
+      <c r="M54">
+        <v>38</v>
+      </c>
+      <c r="N54">
         <v>39</v>
-      </c>
-      <c r="K54">
-        <v>36</v>
-      </c>
-      <c r="L54">
-        <v>38</v>
-      </c>
-      <c r="M54">
-        <v>39</v>
-      </c>
-      <c r="N54">
-        <v>40</v>
       </c>
       <c r="O54" t="s">
         <v>173</v>
@@ -3386,29 +3386,29 @@
       <c r="F55" t="s">
         <v>76</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>174</v>
+      <c r="G55" t="s">
+        <v>16</v>
       </c>
       <c r="H55" s="1">
         <v>240</v>
       </c>
       <c r="I55">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J55">
+        <v>40</v>
+      </c>
+      <c r="K55">
+        <v>29</v>
+      </c>
+      <c r="L55">
+        <v>28</v>
+      </c>
+      <c r="M55">
         <v>38</v>
       </c>
-      <c r="K55">
-        <v>34</v>
-      </c>
-      <c r="L55">
-        <v>38</v>
-      </c>
-      <c r="M55">
-        <v>40</v>
-      </c>
       <c r="N55">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O55" t="s">
         <v>173</v>
@@ -3433,29 +3433,29 @@
       <c r="F56" t="s">
         <v>80</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>174</v>
+      <c r="G56" t="s">
+        <v>16</v>
       </c>
       <c r="H56" s="1">
         <v>240</v>
       </c>
       <c r="I56">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J56">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K56">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="L56">
+        <v>30</v>
+      </c>
+      <c r="M56">
+        <v>28</v>
+      </c>
+      <c r="N56">
         <v>37</v>
-      </c>
-      <c r="M56">
-        <v>34</v>
-      </c>
-      <c r="N56">
-        <v>36</v>
       </c>
       <c r="O56" t="s">
         <v>173</v>
@@ -3480,29 +3480,29 @@
       <c r="F57" t="s">
         <v>84</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>174</v>
+      <c r="G57" t="s">
+        <v>16</v>
       </c>
       <c r="H57" s="1">
         <v>240</v>
       </c>
       <c r="I57">
+        <v>35</v>
+      </c>
+      <c r="J57">
+        <v>36</v>
+      </c>
+      <c r="K57">
+        <v>32</v>
+      </c>
+      <c r="L57">
         <v>25</v>
       </c>
-      <c r="J57">
-        <v>33</v>
-      </c>
-      <c r="K57">
+      <c r="M57">
         <v>31</v>
       </c>
-      <c r="L57">
-        <v>38</v>
-      </c>
-      <c r="M57">
-        <v>32</v>
-      </c>
       <c r="N57">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O57" t="s">
         <v>173</v>
@@ -3527,29 +3527,29 @@
       <c r="F58" t="s">
         <v>88</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>174</v>
+      <c r="G58" t="s">
+        <v>16</v>
       </c>
       <c r="H58" s="1">
         <v>240</v>
       </c>
       <c r="I58">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J58">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K58">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L58">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M58">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="N58">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O58" t="s">
         <v>173</v>
@@ -3574,29 +3574,29 @@
       <c r="F59" t="s">
         <v>92</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>174</v>
+      <c r="G59" t="s">
+        <v>16</v>
       </c>
       <c r="H59" s="1">
         <v>240</v>
       </c>
       <c r="I59">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L59">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O59" t="s">
         <v>173</v>
@@ -3621,29 +3621,29 @@
       <c r="F60" t="s">
         <v>96</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>174</v>
+      <c r="G60" t="s">
+        <v>16</v>
       </c>
       <c r="H60" s="1">
         <v>240</v>
       </c>
       <c r="I60">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J60">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K60">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L60">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M60">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="N60">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O60" t="s">
         <v>173</v>
@@ -3668,29 +3668,29 @@
       <c r="F61" t="s">
         <v>100</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>174</v>
+      <c r="G61" t="s">
+        <v>16</v>
       </c>
       <c r="H61" s="1">
         <v>240</v>
       </c>
       <c r="I61">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J61">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K61">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L61">
         <v>20</v>
       </c>
       <c r="M61">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N61">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O61" t="s">
         <v>173</v>
@@ -3715,29 +3715,29 @@
       <c r="F62" t="s">
         <v>104</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>174</v>
+      <c r="G62" t="s">
+        <v>16</v>
       </c>
       <c r="H62" s="1">
         <v>240</v>
       </c>
       <c r="I62">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J62">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K62">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L62">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M62">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N62">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O62" t="s">
         <v>173</v>
@@ -3762,29 +3762,29 @@
       <c r="F63" t="s">
         <v>108</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>174</v>
+      <c r="G63" t="s">
+        <v>16</v>
       </c>
       <c r="H63" s="1">
         <v>240</v>
       </c>
       <c r="I63">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J63">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K63">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L63">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M63">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N63">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O63" t="s">
         <v>173</v>
@@ -3809,29 +3809,29 @@
       <c r="F64" t="s">
         <v>112</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>174</v>
+      <c r="G64" t="s">
+        <v>16</v>
       </c>
       <c r="H64" s="1">
         <v>240</v>
       </c>
       <c r="I64">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J64">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K64">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L64">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="M64">
         <v>38</v>
       </c>
       <c r="N64">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O64" t="s">
         <v>173</v>
@@ -3856,26 +3856,26 @@
       <c r="F65" t="s">
         <v>116</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>174</v>
+      <c r="G65" t="s">
+        <v>16</v>
       </c>
       <c r="H65" s="1">
         <v>240</v>
       </c>
       <c r="I65">
+        <v>21</v>
+      </c>
+      <c r="J65">
+        <v>39</v>
+      </c>
+      <c r="K65">
         <v>20</v>
       </c>
-      <c r="J65">
-        <v>33</v>
-      </c>
-      <c r="K65">
+      <c r="L65">
         <v>23</v>
       </c>
-      <c r="L65">
-        <v>27</v>
-      </c>
       <c r="M65">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N65">
         <v>39</v>
@@ -3903,29 +3903,29 @@
       <c r="F66" t="s">
         <v>120</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>174</v>
+      <c r="G66" t="s">
+        <v>16</v>
       </c>
       <c r="H66" s="1">
         <v>240</v>
       </c>
       <c r="I66">
+        <v>30</v>
+      </c>
+      <c r="J66">
+        <v>40</v>
+      </c>
+      <c r="K66">
         <v>31</v>
       </c>
-      <c r="J66">
-        <v>37</v>
-      </c>
-      <c r="K66">
-        <v>35</v>
-      </c>
       <c r="L66">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M66">
+        <v>40</v>
+      </c>
+      <c r="N66">
         <v>38</v>
-      </c>
-      <c r="N66">
-        <v>39</v>
       </c>
       <c r="O66" t="s">
         <v>173</v>
@@ -3950,29 +3950,29 @@
       <c r="F67" t="s">
         <v>124</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>174</v>
+      <c r="G67" t="s">
+        <v>16</v>
       </c>
       <c r="H67" s="1">
         <v>240</v>
       </c>
       <c r="I67">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J67">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K67">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L67">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="M67">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N67">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O67" t="s">
         <v>173</v>
@@ -3997,8 +3997,8 @@
       <c r="F68" t="s">
         <v>128</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>174</v>
+      <c r="G68" t="s">
+        <v>16</v>
       </c>
       <c r="H68" s="1">
         <v>240</v>
@@ -4007,19 +4007,19 @@
         <v>26</v>
       </c>
       <c r="J68">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K68">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L68">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="M68">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N68">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O68" t="s">
         <v>173</v>
@@ -4044,8 +4044,8 @@
       <c r="F69" t="s">
         <v>132</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>174</v>
+      <c r="G69" t="s">
+        <v>16</v>
       </c>
       <c r="H69" s="1">
         <v>240</v>
@@ -4054,16 +4054,16 @@
         <v>30</v>
       </c>
       <c r="J69">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K69">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L69">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="M69">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N69">
         <v>38</v>
@@ -4091,29 +4091,29 @@
       <c r="F70" t="s">
         <v>136</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>174</v>
+      <c r="G70" t="s">
+        <v>16</v>
       </c>
       <c r="H70" s="1">
         <v>240</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J70">
+        <v>38</v>
+      </c>
+      <c r="K70">
+        <v>38</v>
+      </c>
+      <c r="L70">
+        <v>37</v>
+      </c>
+      <c r="M70">
+        <v>37</v>
+      </c>
+      <c r="N70">
         <v>36</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>36</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
       </c>
       <c r="O70" t="s">
         <v>173</v>
@@ -4138,26 +4138,26 @@
       <c r="F71" t="s">
         <v>140</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>174</v>
+      <c r="G71" t="s">
+        <v>16</v>
       </c>
       <c r="H71" s="1">
         <v>240</v>
       </c>
       <c r="I71">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J71">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K71">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L71">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="M71">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N71">
         <v>39</v>
@@ -4185,26 +4185,26 @@
       <c r="F72" t="s">
         <v>144</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>174</v>
+      <c r="G72" t="s">
+        <v>16</v>
       </c>
       <c r="H72" s="1">
         <v>240</v>
       </c>
       <c r="I72">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J72">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K72">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L72">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="M72">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N72">
         <v>39</v>
@@ -4232,29 +4232,29 @@
       <c r="F73" t="s">
         <v>148</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>174</v>
+      <c r="G73" t="s">
+        <v>16</v>
       </c>
       <c r="H73" s="1">
         <v>240</v>
       </c>
       <c r="I73">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J73">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K73">
+        <v>28</v>
+      </c>
+      <c r="L73">
+        <v>26</v>
+      </c>
+      <c r="M73">
         <v>30</v>
       </c>
-      <c r="L73">
-        <v>28</v>
-      </c>
-      <c r="M73">
-        <v>36</v>
-      </c>
       <c r="N73">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O73" t="s">
         <v>173</v>
@@ -4279,26 +4279,26 @@
       <c r="F74" t="s">
         <v>152</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>174</v>
+      <c r="G74" t="s">
+        <v>16</v>
       </c>
       <c r="H74" s="1">
         <v>240</v>
       </c>
       <c r="I74">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J74">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K74">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L74">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="M74">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N74">
         <v>32</v>
@@ -4326,29 +4326,29 @@
       <c r="F75" t="s">
         <v>156</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>174</v>
+      <c r="G75" t="s">
+        <v>16</v>
       </c>
       <c r="H75" s="1">
         <v>240</v>
       </c>
       <c r="I75">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J75">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K75">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L75">
+        <v>26</v>
+      </c>
+      <c r="M75">
         <v>34</v>
       </c>
-      <c r="M75">
-        <v>26</v>
-      </c>
       <c r="N75">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="O75" t="s">
         <v>173</v>
@@ -4373,29 +4373,29 @@
       <c r="F76" t="s">
         <v>160</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>174</v>
+      <c r="G76" t="s">
+        <v>16</v>
       </c>
       <c r="H76" s="1">
         <v>240</v>
       </c>
       <c r="I76">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J76">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K76">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L76">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M76">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N76">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="O76" t="s">
         <v>173</v>
@@ -4420,26 +4420,26 @@
       <c r="F77" t="s">
         <v>164</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>174</v>
+      <c r="G77" t="s">
+        <v>16</v>
       </c>
       <c r="H77" s="1">
         <v>240</v>
       </c>
       <c r="I77">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J77">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K77">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L77">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M77">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="N77">
         <v>37</v>
@@ -4467,8 +4467,8 @@
       <c r="F78" t="s">
         <v>168</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>174</v>
+      <c r="G78" t="s">
+        <v>16</v>
       </c>
       <c r="H78" s="1">
         <v>240</v>
@@ -4477,19 +4477,19 @@
         <v>28</v>
       </c>
       <c r="J78">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K78">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L78">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M78">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N78">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O78" t="s">
         <v>173</v>
@@ -4514,29 +4514,29 @@
       <c r="F79" t="s">
         <v>172</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>174</v>
+      <c r="G79" t="s">
+        <v>16</v>
       </c>
       <c r="H79" s="1">
         <v>240</v>
       </c>
       <c r="I79">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J79">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K79">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L79">
+        <v>28</v>
+      </c>
+      <c r="M79">
         <v>33</v>
       </c>
-      <c r="M79">
-        <v>36</v>
-      </c>
       <c r="N79">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O79" t="s">
         <v>173</v>
@@ -4545,7 +4545,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="F2:F40 F41:F79" numberStoredAsText="1"/>
+    <ignoredError sqref="F2:F40" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26503584-559D-40F7-88AE-73E9A7B827B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D48659-1ECD-4230-B18D-49FCBFCCB49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="184">
   <si>
     <t>Roll_No</t>
   </si>
@@ -580,6 +580,15 @@
   </si>
   <si>
     <t>PWT-2</t>
+  </si>
+  <si>
+    <t>01.01.2000</t>
+  </si>
+  <si>
+    <t>11A</t>
+  </si>
+  <si>
+    <t>MALKHAN MEENA</t>
   </si>
 </sst>
 </file>
@@ -638,21 +647,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFC4C7C5"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -667,36 +661,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1019,1182 +1031,1190 @@
     <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="6">
         <v>1001</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="2">
         <v>6353423130</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G2" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="6">
         <v>1002</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="2">
         <v>9925636156</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="6">
         <v>1003</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="3">
         <v>7861847673</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G4" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="7">
         <v>1004</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="2">
         <v>9727883707</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G5" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="7">
         <v>1005</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="3">
         <v>9925520169</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="G6" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="7">
         <v>1006</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="2">
         <v>9313643310</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="G7" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="7">
         <v>1007</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="2">
         <v>9825938737</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="G8" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="7">
         <v>1008</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="2">
         <v>8980177520</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="G9" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="7">
         <v>1009</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="2">
         <v>9537598991</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="G10" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="7">
         <v>1010</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="2">
         <v>9712863175</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="G11" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="7">
         <v>1011</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="2">
         <v>7567358072</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="G12" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="7">
         <v>1012</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="3">
         <v>8141828290</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="G13" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="7">
         <v>1013</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="2">
         <v>9974704919</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="G14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="7">
         <v>1014</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="2">
         <v>9913943175</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="G15" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="7">
         <v>1015</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="2">
         <v>9978463169</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="G16" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="7">
         <v>1016</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="3">
         <v>9925251723</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="G17" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="7">
         <v>1017</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="2">
         <v>9712972430</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="G18" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="7">
         <v>1018</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="4">
         <v>9925260543</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="G19" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="7">
         <v>1019</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="2">
         <v>6340300055</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="G20" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="7">
         <v>1020</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="2">
         <v>6354598416</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="G21" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="A22" s="7">
         <v>1021</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="2">
         <v>9537854070</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="G22" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="7">
         <v>1022</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="3">
         <v>9726573288</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="G23" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="A24" s="7">
         <v>1023</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="2">
         <v>6340300195</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="G24" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="7">
         <v>1024</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="3">
         <v>9879769465</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="G25" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H25" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="A26" s="7">
         <v>1025</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="3">
         <v>8780316912</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="G26" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="7">
         <v>1026</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="4">
         <v>9723255189</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="G27" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="A28" s="7">
         <v>1027</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="2">
         <v>8141284920</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="G28" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="A29" s="7">
         <v>1028</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="2">
         <v>9825512456</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="G29" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H29" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="A30" s="7">
         <v>1029</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="4">
         <v>9001844668</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="G30" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="7">
         <v>1030</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="2">
         <v>9574632300</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="G31" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="A32" s="7">
         <v>1031</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="2">
         <v>9727926762</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="G32" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H32" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="A33" s="7">
         <v>1032</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="3">
         <v>6354922106</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="G33" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H33" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="A34" s="7">
         <v>1033</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="3">
         <v>6352551344</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="G34" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="A35" s="7">
         <v>1034</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="3">
         <v>9427075491</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="G35" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="A36" s="7">
         <v>1035</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="3">
         <v>9687168715</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="G36" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="A37" s="7">
         <v>1036</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="2">
         <v>9099247253</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="G37" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H37" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="A38" s="7">
         <v>1037</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="2">
         <v>9726658420</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H38" t="s">
+      <c r="G38" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H38" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="A39" s="7">
         <v>1038</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="3">
         <v>9316586342</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H39" t="s">
+      <c r="G39" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H39" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="A40" s="7">
         <v>1039</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="3">
         <v>9909233642</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H40" t="s">
+      <c r="G40" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H40" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
+      <c r="A41" s="6">
+        <v>1101</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41" s="12">
+        <v>884813537312</v>
+      </c>
+      <c r="F41" s="3">
+        <v>9909233641</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G44" s="3"/>
+      <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G45" s="3"/>
+      <c r="G45" s="1"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G46" s="3"/>
+      <c r="G46" s="1"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G47" s="3"/>
+      <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G48" s="3"/>
+      <c r="G48" s="1"/>
     </row>
     <row r="49" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G49" s="3"/>
+      <c r="G49" s="1"/>
     </row>
     <row r="50" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G50" s="3"/>
+      <c r="G50" s="1"/>
     </row>
     <row r="51" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G51" s="3"/>
+      <c r="G51" s="1"/>
     </row>
     <row r="52" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G52" s="3"/>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G53" s="3"/>
+      <c r="G53" s="1"/>
     </row>
     <row r="54" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G54" s="3"/>
+      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G55" s="3"/>
+      <c r="G55" s="1"/>
     </row>
     <row r="56" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G56" s="3"/>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G57" s="3"/>
+      <c r="G57" s="1"/>
     </row>
     <row r="58" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G58" s="3"/>
+      <c r="G58" s="1"/>
     </row>
     <row r="59" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G59" s="3"/>
+      <c r="G59" s="1"/>
     </row>
     <row r="60" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G60" s="3"/>
+      <c r="G60" s="1"/>
     </row>
     <row r="61" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G61" s="3"/>
+      <c r="G61" s="1"/>
     </row>
     <row r="62" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G62" s="3"/>
+      <c r="G62" s="1"/>
     </row>
     <row r="63" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G63" s="3"/>
+      <c r="G63" s="1"/>
     </row>
     <row r="64" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G64" s="3"/>
+      <c r="G64" s="1"/>
     </row>
     <row r="65" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G65" s="3"/>
+      <c r="G65" s="1"/>
     </row>
     <row r="66" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G66" s="3"/>
+      <c r="G66" s="1"/>
     </row>
     <row r="67" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G67" s="3"/>
+      <c r="G67" s="1"/>
     </row>
     <row r="68" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G68" s="3"/>
+      <c r="G68" s="1"/>
     </row>
     <row r="69" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G69" s="3"/>
+      <c r="G69" s="1"/>
     </row>
     <row r="70" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G70" s="3"/>
+      <c r="G70" s="1"/>
     </row>
     <row r="71" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G71" s="3"/>
+      <c r="G71" s="1"/>
     </row>
     <row r="72" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G72" s="3"/>
+      <c r="G72" s="1"/>
     </row>
     <row r="73" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G73" s="3"/>
+      <c r="G73" s="1"/>
     </row>
     <row r="74" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G74" s="3"/>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G75" s="3"/>
+      <c r="G75" s="1"/>
     </row>
     <row r="76" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G76" s="3"/>
+      <c r="G76" s="1"/>
     </row>
     <row r="77" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G77" s="3"/>
+      <c r="G77" s="1"/>
     </row>
     <row r="78" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G78" s="3"/>
+      <c r="G78" s="1"/>
     </row>
     <row r="79" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G79" s="3"/>
+      <c r="G79" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2206,2539 +2226,2551 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D043D23-75C9-4A79-B369-DB03044E1B80}">
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>1001</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="2">
-        <v>240</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="B2" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="8">
+        <v>240</v>
+      </c>
+      <c r="E2" s="9">
         <v>38</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="10">
         <v>35</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="9">
         <v>29</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="9">
         <v>35</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="9">
         <v>31</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
         <v>1002</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2">
-        <v>240</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="B3" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="8">
+        <v>240</v>
+      </c>
+      <c r="E3" s="9">
         <v>32</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="10">
         <v>29</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="9">
         <v>23</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="9">
         <v>15</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="9">
         <v>20</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="9">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
         <v>1003</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2">
-        <v>240</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="B4" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="8">
+        <v>240</v>
+      </c>
+      <c r="E4" s="9">
         <v>37</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="9">
         <v>35</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="9">
         <v>31</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="9">
         <v>29</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="9">
         <v>29</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
         <v>1004</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2">
-        <v>240</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="B5" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="8">
+        <v>240</v>
+      </c>
+      <c r="E5" s="9">
         <v>40</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="9">
         <v>37</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="9">
         <v>34</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="9">
         <v>38</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="9">
         <v>39</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="9">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
         <v>1005</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2">
-        <v>240</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="B6" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="8">
+        <v>240</v>
+      </c>
+      <c r="E6" s="9">
         <v>38</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="9">
         <v>34</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="9">
         <v>24</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="9">
         <v>32</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="9">
         <v>39</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="9">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
         <v>1006</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2">
-        <v>240</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="B7" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="8">
+        <v>240</v>
+      </c>
+      <c r="E7" s="9">
         <v>32</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="9">
         <v>34</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="9">
         <v>22</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="9">
         <v>22</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="9">
         <v>21</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
         <v>1007</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="2">
-        <v>240</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="B8" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="8">
+        <v>240</v>
+      </c>
+      <c r="E8" s="9">
         <v>36</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="9">
         <v>32</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="9">
         <v>26</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="9">
         <v>20</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="9">
         <v>22</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="9">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
         <v>1008</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="2">
-        <v>240</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="B9" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="8">
+        <v>240</v>
+      </c>
+      <c r="E9" s="9">
         <v>38</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="9">
         <v>37</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="9">
         <v>32</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="9">
         <v>34</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="9">
         <v>35</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
         <v>1009</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="2">
-        <v>240</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="B10" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="8">
+        <v>240</v>
+      </c>
+      <c r="E10" s="9">
         <v>34</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="9">
         <v>29</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="9">
         <v>26</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="9">
         <v>19</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="9">
         <v>24</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="9">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
         <v>1010</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="2">
-        <v>240</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="B11" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="8">
+        <v>240</v>
+      </c>
+      <c r="E11" s="9">
         <v>35</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="9">
         <v>34</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="9">
         <v>25</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="9">
         <v>24</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="9">
         <v>25</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="9">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
         <v>1011</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="2">
-        <v>240</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="B12" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="8">
+        <v>240</v>
+      </c>
+      <c r="E12" s="9">
         <v>38</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="9">
         <v>32</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="9">
         <v>24</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="9">
         <v>24</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="9">
         <v>34</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="9">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
         <v>1012</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="2">
-        <v>240</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="B13" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="8">
+        <v>240</v>
+      </c>
+      <c r="E13" s="9">
         <v>33</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="9">
         <v>20</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="9">
         <v>14</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="9">
         <v>14</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="9">
         <v>9</v>
       </c>
-      <c r="J13" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="J13" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
         <v>1013</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="2">
-        <v>240</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="B14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="8">
+        <v>240</v>
+      </c>
+      <c r="E14" s="9">
         <v>39</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="9">
         <v>36</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="9">
         <v>30</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="9">
         <v>36</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="9">
         <v>34</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="9">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
         <v>1014</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="2">
-        <v>240</v>
-      </c>
-      <c r="E15" s="5">
+      <c r="B15" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="8">
+        <v>240</v>
+      </c>
+      <c r="E15" s="9">
         <v>40</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="9">
         <v>39</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="9">
         <v>34</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="9">
         <v>36</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="9">
         <v>38</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="9">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
         <v>1015</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="2">
-        <v>240</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="B16" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="8">
+        <v>240</v>
+      </c>
+      <c r="E16" s="9">
         <v>39</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="9">
         <v>38</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="9">
         <v>30</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="9">
         <v>34</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="9">
         <v>38</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="9">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
         <v>1016</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="2">
-        <v>240</v>
-      </c>
-      <c r="E17" s="5">
+      <c r="B17" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="8">
+        <v>240</v>
+      </c>
+      <c r="E17" s="9">
         <v>36</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="9">
         <v>35</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="9">
         <v>27</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="9">
         <v>29</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="9">
         <v>37</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
         <v>1017</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="2">
-        <v>240</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="B18" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="8">
+        <v>240</v>
+      </c>
+      <c r="E18" s="9">
         <v>38</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="9">
         <v>33</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="9">
         <v>25</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="9">
         <v>31</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="9">
         <v>38</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="9">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
         <v>1018</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="2">
-        <v>240</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="B19" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="8">
+        <v>240</v>
+      </c>
+      <c r="E19" s="9">
         <v>38</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="9">
         <v>36</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="9">
         <v>26</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="9">
         <v>24</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="9">
         <v>21</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="9">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
         <v>1019</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="2">
-        <v>240</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="B20" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="8">
+        <v>240</v>
+      </c>
+      <c r="E20" s="9">
         <v>35</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="9">
         <v>29</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="9">
         <v>22</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="9">
         <v>14</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="9">
         <v>8</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="9">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
         <v>1020</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="2">
-        <v>240</v>
-      </c>
-      <c r="E21" s="5">
+      <c r="B21" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="8">
+        <v>240</v>
+      </c>
+      <c r="E21" s="9">
         <v>34</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="9">
         <v>27</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="9">
         <v>20</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="9">
         <v>23</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="9">
         <v>20</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="9">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
         <v>1021</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="2">
-        <v>240</v>
-      </c>
-      <c r="E22" s="5">
+      <c r="B22" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="8">
+        <v>240</v>
+      </c>
+      <c r="E22" s="9">
         <v>33</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="9">
         <v>34</v>
       </c>
-      <c r="G22" s="5">
-        <v>18</v>
-      </c>
-      <c r="H22" s="5">
+      <c r="G22" s="9">
+        <v>18</v>
+      </c>
+      <c r="H22" s="9">
         <v>20</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="9">
         <v>20</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
         <v>1022</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="2">
-        <v>240</v>
-      </c>
-      <c r="E23" s="5">
+      <c r="B23" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="8">
+        <v>240</v>
+      </c>
+      <c r="E23" s="9">
         <v>34</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="9">
         <v>33</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="9">
         <v>26</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="9">
         <v>17</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="9">
         <v>21</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J23" s="9">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
         <v>1023</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="2">
-        <v>240</v>
-      </c>
-      <c r="E24" s="5">
+      <c r="B24" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="8">
+        <v>240</v>
+      </c>
+      <c r="E24" s="9">
         <v>38</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="9">
         <v>34</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="9">
         <v>24</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="9">
         <v>31</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="9">
         <v>31</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
         <v>1024</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="2">
-        <v>240</v>
-      </c>
-      <c r="E25" s="5">
+      <c r="B25" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="8">
+        <v>240</v>
+      </c>
+      <c r="E25" s="9">
         <v>40</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="9">
         <v>36</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="9">
         <v>33</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="9">
         <v>38</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="9">
         <v>37</v>
       </c>
-      <c r="J25" s="5">
+      <c r="J25" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
         <v>1025</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="2">
-        <v>240</v>
-      </c>
-      <c r="E26" s="5">
+      <c r="B26" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="8">
+        <v>240</v>
+      </c>
+      <c r="E26" s="9">
         <v>39</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="9">
         <v>33</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="9">
         <v>20</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="9">
         <v>23</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="9">
         <v>27</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J26" s="9">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
         <v>1026</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="2">
-        <v>240</v>
-      </c>
-      <c r="E27" s="5">
+      <c r="B27" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="8">
+        <v>240</v>
+      </c>
+      <c r="E27" s="9">
         <v>39</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="9">
         <v>37</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="9">
         <v>31</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="9">
         <v>35</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="9">
         <v>36</v>
       </c>
-      <c r="J27" s="5">
+      <c r="J27" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
         <v>1027</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="2">
-        <v>240</v>
-      </c>
-      <c r="E28" s="5">
+      <c r="B28" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="8">
+        <v>240</v>
+      </c>
+      <c r="E28" s="9">
         <v>38</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="9">
         <v>30</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="9">
         <v>26</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="9">
         <v>25</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="9">
         <v>30</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J28" s="9">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
         <v>1028</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="2">
-        <v>240</v>
-      </c>
-      <c r="E29" s="5">
+      <c r="B29" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="8">
+        <v>240</v>
+      </c>
+      <c r="E29" s="9">
         <v>35</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="9">
         <v>30</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="9">
         <v>26</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="9">
         <v>38</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="9">
         <v>35</v>
       </c>
-      <c r="J29" s="5">
+      <c r="J29" s="9">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
         <v>1029</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="2">
-        <v>240</v>
-      </c>
-      <c r="E30" s="5">
+      <c r="B30" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="8">
+        <v>240</v>
+      </c>
+      <c r="E30" s="9">
         <v>38</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="9">
         <v>37</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="9">
         <v>30</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="9">
         <v>34</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="9">
         <v>36</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J30" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
         <v>1030</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="2">
-        <v>240</v>
-      </c>
-      <c r="E31" s="5">
+      <c r="B31" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="8">
+        <v>240</v>
+      </c>
+      <c r="E31" s="9">
         <v>0</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="9">
         <v>36</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="9">
         <v>0</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="9">
         <v>0</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="9">
         <v>0</v>
       </c>
-      <c r="J31" s="5">
+      <c r="J31" s="9">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
         <v>1031</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="2">
-        <v>240</v>
-      </c>
-      <c r="E32" s="5">
+      <c r="B32" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="8">
+        <v>240</v>
+      </c>
+      <c r="E32" s="9">
         <v>39</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="9">
         <v>35</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="9">
         <v>33</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="9">
         <v>32</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="9">
         <v>36</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J32" s="9">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
         <v>1032</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="2">
-        <v>240</v>
-      </c>
-      <c r="E33" s="5">
+      <c r="B33" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="8">
+        <v>240</v>
+      </c>
+      <c r="E33" s="9">
         <v>39</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="9">
         <v>33</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="9">
         <v>22</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="9">
         <v>32</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="9">
         <v>36</v>
       </c>
-      <c r="J33" s="5">
+      <c r="J33" s="9">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
         <v>1033</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="2">
-        <v>240</v>
-      </c>
-      <c r="E34" s="5">
+      <c r="B34" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="8">
+        <v>240</v>
+      </c>
+      <c r="E34" s="9">
         <v>36</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="9">
         <v>32</v>
       </c>
-      <c r="G34" s="5">
-        <v>18</v>
-      </c>
-      <c r="H34" s="5">
+      <c r="G34" s="9">
+        <v>18</v>
+      </c>
+      <c r="H34" s="9">
         <v>30</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="9">
         <v>28</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J34" s="9">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
         <v>1034</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" s="2">
-        <v>240</v>
-      </c>
-      <c r="E35" s="5">
+      <c r="B35" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="8">
+        <v>240</v>
+      </c>
+      <c r="E35" s="9">
         <v>32</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="9">
         <v>29</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="9">
         <v>16</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="9">
         <v>30</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="9">
         <v>29</v>
       </c>
-      <c r="J35" s="5">
+      <c r="J35" s="9">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
         <v>1035</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36" s="2">
-        <v>240</v>
-      </c>
-      <c r="E36" s="5">
+      <c r="B36" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="8">
+        <v>240</v>
+      </c>
+      <c r="E36" s="9">
         <v>34</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="9">
         <v>29</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="9">
         <v>22</v>
       </c>
-      <c r="H36" s="5">
-        <v>18</v>
-      </c>
-      <c r="I36" s="5">
+      <c r="H36" s="9">
+        <v>18</v>
+      </c>
+      <c r="I36" s="9">
         <v>34</v>
       </c>
-      <c r="J36" s="5">
+      <c r="J36" s="9">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
         <v>1036</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="2">
-        <v>240</v>
-      </c>
-      <c r="E37" s="5">
+      <c r="B37" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="8">
+        <v>240</v>
+      </c>
+      <c r="E37" s="9">
         <v>37</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="9">
         <v>32</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="9">
         <v>28</v>
       </c>
-      <c r="H37" s="5">
+      <c r="H37" s="9">
         <v>22</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="9">
         <v>33</v>
       </c>
-      <c r="J37" s="5">
+      <c r="J37" s="9">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
         <v>1037</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" s="2">
-        <v>240</v>
-      </c>
-      <c r="E38" s="5">
+      <c r="B38" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="8">
+        <v>240</v>
+      </c>
+      <c r="E38" s="9">
         <v>37</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="9">
         <v>31</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="9">
         <v>22</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="9">
         <v>25</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="9">
         <v>21</v>
       </c>
-      <c r="J38" s="5">
+      <c r="J38" s="9">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
         <v>1038</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="2">
-        <v>240</v>
-      </c>
-      <c r="E39" s="5">
+      <c r="B39" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="8">
+        <v>240</v>
+      </c>
+      <c r="E39" s="9">
         <v>40</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="9">
         <v>34</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="9">
         <v>28</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="9">
         <v>33</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="9">
         <v>35</v>
       </c>
-      <c r="J39" s="5">
+      <c r="J39" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
         <v>1039</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="2">
-        <v>240</v>
-      </c>
-      <c r="E40" s="5">
+      <c r="B40" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="8">
+        <v>240</v>
+      </c>
+      <c r="E40" s="9">
         <v>39</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="9">
         <v>36</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="9">
         <v>27</v>
       </c>
-      <c r="H40" s="5">
+      <c r="H40" s="9">
         <v>26</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="9">
         <v>33</v>
       </c>
-      <c r="J40" s="5">
+      <c r="J40" s="9">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
         <v>1001</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="B41" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D41" s="2">
-        <v>240</v>
-      </c>
-      <c r="E41" s="6">
+      <c r="D41" s="8">
+        <v>240</v>
+      </c>
+      <c r="E41" s="11">
         <v>39</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="9">
         <v>39</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="11">
         <v>28</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="11">
         <v>26</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="11">
         <v>22</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="11">
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
         <v>1002</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="B42" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D42" s="2">
-        <v>240</v>
-      </c>
-      <c r="E42" s="6">
+      <c r="D42" s="8">
+        <v>240</v>
+      </c>
+      <c r="E42" s="11">
         <v>33</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="9">
         <v>33</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42" s="11">
         <v>17</v>
       </c>
-      <c r="H42" s="6">
+      <c r="H42" s="11">
         <v>14</v>
       </c>
-      <c r="I42" s="6">
-        <v>18</v>
-      </c>
-      <c r="J42" s="6">
+      <c r="I42" s="11">
+        <v>18</v>
+      </c>
+      <c r="J42" s="11">
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
         <v>1003</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="B43" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D43" s="2">
-        <v>240</v>
-      </c>
-      <c r="E43" s="6">
+      <c r="D43" s="8">
+        <v>240</v>
+      </c>
+      <c r="E43" s="11">
         <v>37</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="9">
         <v>40</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="11">
         <v>23</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H43" s="11">
         <v>21</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I43" s="11">
         <v>14</v>
       </c>
-      <c r="J43" s="6">
+      <c r="J43" s="11">
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
         <v>1004</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="B44" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D44" s="2">
-        <v>240</v>
-      </c>
-      <c r="E44" s="5">
+      <c r="D44" s="8">
+        <v>240</v>
+      </c>
+      <c r="E44" s="9">
         <v>39</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="9">
         <v>40</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="9">
         <v>33</v>
       </c>
-      <c r="H44" s="5">
+      <c r="H44" s="9">
         <v>39</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="9">
         <v>34</v>
       </c>
-      <c r="J44" s="5">
+      <c r="J44" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
         <v>1005</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="B45" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D45" s="2">
-        <v>240</v>
-      </c>
-      <c r="E45" s="5">
+      <c r="D45" s="8">
+        <v>240</v>
+      </c>
+      <c r="E45" s="9">
         <v>39</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="9">
         <v>39</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="9">
         <v>27</v>
       </c>
-      <c r="H45" s="5">
+      <c r="H45" s="9">
         <v>33</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="9">
         <v>30</v>
       </c>
-      <c r="J45" s="5">
+      <c r="J45" s="9">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
         <v>1006</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="B46" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D46" s="2">
-        <v>240</v>
-      </c>
-      <c r="E46" s="5">
+      <c r="D46" s="8">
+        <v>240</v>
+      </c>
+      <c r="E46" s="9">
         <v>39</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="9">
         <v>39</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="9">
         <v>23</v>
       </c>
-      <c r="H46" s="5">
+      <c r="H46" s="9">
         <v>15</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="9">
         <v>23</v>
       </c>
-      <c r="J46" s="5">
+      <c r="J46" s="9">
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
         <v>1007</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="B47" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D47" s="2">
-        <v>240</v>
-      </c>
-      <c r="E47" s="5">
+      <c r="D47" s="8">
+        <v>240</v>
+      </c>
+      <c r="E47" s="9">
         <v>36</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="9">
         <v>37</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="9">
         <v>25</v>
       </c>
-      <c r="H47" s="5">
+      <c r="H47" s="9">
         <v>15</v>
       </c>
-      <c r="I47" s="5">
-        <v>18</v>
-      </c>
-      <c r="J47" s="5">
+      <c r="I47" s="9">
+        <v>18</v>
+      </c>
+      <c r="J47" s="9">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
         <v>1008</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="B48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D48" s="2">
-        <v>240</v>
-      </c>
-      <c r="E48" s="5">
+      <c r="D48" s="8">
+        <v>240</v>
+      </c>
+      <c r="E48" s="9">
         <v>0</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="9">
         <v>0</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="9">
         <v>0</v>
       </c>
-      <c r="H48" s="5">
+      <c r="H48" s="9">
         <v>23</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="9">
         <v>0</v>
       </c>
-      <c r="J48" s="5">
+      <c r="J48" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
         <v>1009</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="B49" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D49" s="2">
-        <v>240</v>
-      </c>
-      <c r="E49" s="5">
+      <c r="D49" s="8">
+        <v>240</v>
+      </c>
+      <c r="E49" s="9">
         <v>36</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="9">
         <v>36</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="9">
         <v>22</v>
       </c>
-      <c r="H49" s="5">
+      <c r="H49" s="9">
         <v>17</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I49" s="9">
         <v>25</v>
       </c>
-      <c r="J49" s="5">
+      <c r="J49" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
         <v>1010</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="B50" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D50" s="2">
-        <v>240</v>
-      </c>
-      <c r="E50" s="5">
+      <c r="D50" s="8">
+        <v>240</v>
+      </c>
+      <c r="E50" s="9">
         <v>35</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="9">
         <v>37</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="9">
         <v>28</v>
       </c>
-      <c r="H50" s="5">
+      <c r="H50" s="9">
         <v>26</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="9">
         <v>26</v>
       </c>
-      <c r="J50" s="5">
+      <c r="J50" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
         <v>1011</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="B51" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="2">
-        <v>240</v>
-      </c>
-      <c r="E51" s="5">
+      <c r="D51" s="8">
+        <v>240</v>
+      </c>
+      <c r="E51" s="9">
         <v>39</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="9">
         <v>38</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="9">
         <v>27</v>
       </c>
-      <c r="H51" s="5">
+      <c r="H51" s="9">
         <v>23</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="9">
         <v>28</v>
       </c>
-      <c r="J51" s="5">
+      <c r="J51" s="9">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
         <v>1012</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="B52" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D52" s="2">
-        <v>240</v>
-      </c>
-      <c r="E52" s="5">
+      <c r="D52" s="8">
+        <v>240</v>
+      </c>
+      <c r="E52" s="9">
         <v>31</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="9">
         <v>20</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52" s="9">
         <v>15</v>
       </c>
-      <c r="H52" s="5">
+      <c r="H52" s="9">
         <v>14</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="9">
         <v>7</v>
       </c>
-      <c r="J52" s="5">
+      <c r="J52" s="9">
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
         <v>1013</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="B53" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C53" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D53" s="2">
-        <v>240</v>
-      </c>
-      <c r="E53" s="5">
+      <c r="D53" s="8">
+        <v>240</v>
+      </c>
+      <c r="E53" s="9">
         <v>37</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="9">
         <v>40</v>
       </c>
-      <c r="G53" s="5">
+      <c r="G53" s="9">
         <v>35</v>
       </c>
-      <c r="H53" s="5">
+      <c r="H53" s="9">
         <v>35</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="9">
         <v>29</v>
       </c>
-      <c r="J53" s="5">
+      <c r="J53" s="9">
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="7">
         <v>1014</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="B54" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D54" s="2">
-        <v>240</v>
-      </c>
-      <c r="E54" s="5">
+      <c r="D54" s="8">
+        <v>240</v>
+      </c>
+      <c r="E54" s="9">
         <v>39</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="9">
         <v>40</v>
       </c>
-      <c r="G54" s="5">
+      <c r="G54" s="9">
         <v>31</v>
       </c>
-      <c r="H54" s="5">
+      <c r="H54" s="9">
         <v>35</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="9">
         <v>30</v>
       </c>
-      <c r="J54" s="5">
+      <c r="J54" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
         <v>1015</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="B55" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D55" s="2">
-        <v>240</v>
-      </c>
-      <c r="E55" s="5">
+      <c r="D55" s="8">
+        <v>240</v>
+      </c>
+      <c r="E55" s="9">
         <v>36</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55" s="9">
         <v>40</v>
       </c>
-      <c r="G55" s="5">
+      <c r="G55" s="9">
         <v>28</v>
       </c>
-      <c r="H55" s="5">
+      <c r="H55" s="9">
         <v>29</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="9">
         <v>28</v>
       </c>
-      <c r="J55" s="5">
+      <c r="J55" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="7">
         <v>1016</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="B56" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D56" s="2">
-        <v>240</v>
-      </c>
-      <c r="E56" s="5">
+      <c r="D56" s="8">
+        <v>240</v>
+      </c>
+      <c r="E56" s="9">
         <v>37</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="9">
         <v>40</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G56" s="9">
         <v>30</v>
       </c>
-      <c r="H56" s="5">
+      <c r="H56" s="9">
         <v>20</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="9">
         <v>30</v>
       </c>
-      <c r="J56" s="5">
+      <c r="J56" s="9">
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="7">
         <v>1017</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="B57" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C57" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D57" s="2">
-        <v>240</v>
-      </c>
-      <c r="E57" s="5">
+      <c r="D57" s="8">
+        <v>240</v>
+      </c>
+      <c r="E57" s="9">
         <v>35</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57" s="9">
         <v>36</v>
       </c>
-      <c r="G57" s="5">
+      <c r="G57" s="9">
         <v>35</v>
       </c>
-      <c r="H57" s="5">
+      <c r="H57" s="9">
         <v>32</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I57" s="9">
         <v>25</v>
       </c>
-      <c r="J57" s="5">
+      <c r="J57" s="9">
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="7">
         <v>1018</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="B58" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C58" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D58" s="2">
-        <v>240</v>
-      </c>
-      <c r="E58" s="5">
+      <c r="D58" s="8">
+        <v>240</v>
+      </c>
+      <c r="E58" s="9">
         <v>37</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="9">
         <v>39</v>
       </c>
-      <c r="G58" s="5">
+      <c r="G58" s="9">
         <v>25</v>
       </c>
-      <c r="H58" s="5">
+      <c r="H58" s="9">
         <v>17</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I58" s="9">
         <v>17</v>
       </c>
-      <c r="J58" s="5">
+      <c r="J58" s="9">
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="7">
         <v>1019</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="B59" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D59" s="2">
-        <v>240</v>
-      </c>
-      <c r="E59" s="5">
+      <c r="D59" s="8">
+        <v>240</v>
+      </c>
+      <c r="E59" s="9">
         <v>0</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="9">
         <v>0</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="9">
         <v>0</v>
       </c>
-      <c r="H59" s="5">
+      <c r="H59" s="9">
         <v>0</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="9">
         <v>0</v>
       </c>
-      <c r="J59" s="5">
+      <c r="J59" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="7">
         <v>1020</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="B60" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D60" s="2">
-        <v>240</v>
-      </c>
-      <c r="E60" s="5">
+      <c r="D60" s="8">
+        <v>240</v>
+      </c>
+      <c r="E60" s="9">
         <v>36</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="9">
         <v>37</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="9">
         <v>23</v>
       </c>
-      <c r="H60" s="5">
-        <v>18</v>
-      </c>
-      <c r="I60" s="5">
+      <c r="H60" s="9">
+        <v>18</v>
+      </c>
+      <c r="I60" s="9">
         <v>22</v>
       </c>
-      <c r="J60" s="5">
+      <c r="J60" s="9">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="7">
         <v>1021</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="B61" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D61" s="2">
-        <v>240</v>
-      </c>
-      <c r="E61" s="5">
+      <c r="D61" s="8">
+        <v>240</v>
+      </c>
+      <c r="E61" s="9">
         <v>32</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="9">
         <v>38</v>
       </c>
-      <c r="G61" s="5">
+      <c r="G61" s="9">
         <v>23</v>
       </c>
-      <c r="H61" s="5">
+      <c r="H61" s="9">
         <v>19</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I61" s="9">
         <v>20</v>
       </c>
-      <c r="J61" s="5">
+      <c r="J61" s="9">
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="7">
         <v>1022</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="B62" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D62" s="2">
-        <v>240</v>
-      </c>
-      <c r="E62" s="5">
+      <c r="D62" s="8">
+        <v>240</v>
+      </c>
+      <c r="E62" s="9">
         <v>37</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F62" s="9">
         <v>38</v>
       </c>
-      <c r="G62" s="5">
+      <c r="G62" s="9">
         <v>22</v>
       </c>
-      <c r="H62" s="5">
+      <c r="H62" s="9">
         <v>14</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="9">
         <v>14</v>
       </c>
-      <c r="J62" s="5">
+      <c r="J62" s="9">
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
         <v>1023</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="B63" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D63" s="2">
-        <v>240</v>
-      </c>
-      <c r="E63" s="5">
+      <c r="D63" s="8">
+        <v>240</v>
+      </c>
+      <c r="E63" s="9">
         <v>39</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F63" s="9">
         <v>40</v>
       </c>
-      <c r="G63" s="5">
+      <c r="G63" s="9">
         <v>28</v>
       </c>
-      <c r="H63" s="5">
+      <c r="H63" s="9">
         <v>29</v>
       </c>
-      <c r="I63" s="5">
-        <v>18</v>
-      </c>
-      <c r="J63" s="5">
+      <c r="I63" s="9">
+        <v>18</v>
+      </c>
+      <c r="J63" s="9">
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="7">
         <v>1024</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="B64" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D64" s="2">
-        <v>240</v>
-      </c>
-      <c r="E64" s="5">
+      <c r="D64" s="8">
+        <v>240</v>
+      </c>
+      <c r="E64" s="9">
         <v>39</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="9">
         <v>40</v>
       </c>
-      <c r="G64" s="5">
+      <c r="G64" s="9">
         <v>31</v>
       </c>
-      <c r="H64" s="5">
+      <c r="H64" s="9">
         <v>34</v>
       </c>
-      <c r="I64" s="5">
+      <c r="I64" s="9">
         <v>26</v>
       </c>
-      <c r="J64" s="5">
+      <c r="J64" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
         <v>1025</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C65" s="2" t="s">
+      <c r="B65" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D65" s="2">
-        <v>240</v>
-      </c>
-      <c r="E65" s="5">
+      <c r="D65" s="8">
+        <v>240</v>
+      </c>
+      <c r="E65" s="9">
         <v>39</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="9">
         <v>39</v>
       </c>
-      <c r="G65" s="5">
+      <c r="G65" s="9">
         <v>21</v>
       </c>
-      <c r="H65" s="5">
+      <c r="H65" s="9">
         <v>20</v>
       </c>
-      <c r="I65" s="5">
+      <c r="I65" s="9">
         <v>23</v>
       </c>
-      <c r="J65" s="5">
+      <c r="J65" s="9">
         <v>29</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="7">
         <v>1026</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C66" s="2" t="s">
+      <c r="B66" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C66" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D66" s="2">
-        <v>240</v>
-      </c>
-      <c r="E66" s="5">
+      <c r="D66" s="8">
+        <v>240</v>
+      </c>
+      <c r="E66" s="9">
         <v>38</v>
       </c>
-      <c r="F66" s="5">
+      <c r="F66" s="9">
         <v>40</v>
       </c>
-      <c r="G66" s="5">
+      <c r="G66" s="9">
         <v>30</v>
       </c>
-      <c r="H66" s="5">
+      <c r="H66" s="9">
         <v>31</v>
       </c>
-      <c r="I66" s="5">
+      <c r="I66" s="9">
         <v>28</v>
       </c>
-      <c r="J66" s="5">
+      <c r="J66" s="9">
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
         <v>1027</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C67" s="2" t="s">
+      <c r="B67" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C67" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D67" s="2">
-        <v>240</v>
-      </c>
-      <c r="E67" s="5">
+      <c r="D67" s="8">
+        <v>240</v>
+      </c>
+      <c r="E67" s="9">
         <v>35</v>
       </c>
-      <c r="F67" s="5">
+      <c r="F67" s="9">
         <v>39</v>
       </c>
-      <c r="G67" s="5">
+      <c r="G67" s="9">
         <v>25</v>
       </c>
-      <c r="H67" s="5">
+      <c r="H67" s="9">
         <v>21</v>
       </c>
-      <c r="I67" s="5">
+      <c r="I67" s="9">
         <v>21</v>
       </c>
-      <c r="J67" s="5">
+      <c r="J67" s="9">
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="7">
         <v>1028</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C68" s="2" t="s">
+      <c r="B68" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D68" s="2">
-        <v>240</v>
-      </c>
-      <c r="E68" s="5">
+      <c r="D68" s="8">
+        <v>240</v>
+      </c>
+      <c r="E68" s="9">
         <v>33</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="9">
         <v>36</v>
       </c>
-      <c r="G68" s="5">
+      <c r="G68" s="9">
         <v>26</v>
       </c>
-      <c r="H68" s="5">
+      <c r="H68" s="9">
         <v>33</v>
       </c>
-      <c r="I68" s="5">
+      <c r="I68" s="9">
         <v>28</v>
       </c>
-      <c r="J68" s="5">
+      <c r="J68" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="7">
         <v>1029</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C69" s="2" t="s">
+      <c r="B69" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D69" s="2">
-        <v>240</v>
-      </c>
-      <c r="E69" s="5">
+      <c r="D69" s="8">
+        <v>240</v>
+      </c>
+      <c r="E69" s="9">
         <v>38</v>
       </c>
-      <c r="F69" s="5">
+      <c r="F69" s="9">
         <v>40</v>
       </c>
-      <c r="G69" s="5">
+      <c r="G69" s="9">
         <v>30</v>
       </c>
-      <c r="H69" s="5">
+      <c r="H69" s="9">
         <v>26</v>
       </c>
-      <c r="I69" s="5">
+      <c r="I69" s="9">
         <v>30</v>
       </c>
-      <c r="J69" s="5">
+      <c r="J69" s="9">
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="7">
         <v>1030</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="B70" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C70" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D70" s="2">
-        <v>240</v>
-      </c>
-      <c r="E70" s="5">
+      <c r="D70" s="8">
+        <v>240</v>
+      </c>
+      <c r="E70" s="9">
         <v>36</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="9">
         <v>38</v>
       </c>
-      <c r="G70" s="5">
+      <c r="G70" s="9">
         <v>36</v>
       </c>
-      <c r="H70" s="5">
+      <c r="H70" s="9">
         <v>38</v>
       </c>
-      <c r="I70" s="5">
+      <c r="I70" s="9">
         <v>37</v>
       </c>
-      <c r="J70" s="5">
+      <c r="J70" s="9">
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="7">
         <v>1031</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C71" s="2" t="s">
+      <c r="B71" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C71" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D71" s="2">
-        <v>240</v>
-      </c>
-      <c r="E71" s="5">
+      <c r="D71" s="8">
+        <v>240</v>
+      </c>
+      <c r="E71" s="9">
         <v>39</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F71" s="9">
         <v>40</v>
       </c>
-      <c r="G71" s="5">
+      <c r="G71" s="9">
         <v>30</v>
       </c>
-      <c r="H71" s="5">
+      <c r="H71" s="9">
         <v>34</v>
       </c>
-      <c r="I71" s="5">
+      <c r="I71" s="9">
         <v>24</v>
       </c>
-      <c r="J71" s="5">
+      <c r="J71" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="7">
         <v>1032</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C72" s="2" t="s">
+      <c r="B72" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C72" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D72" s="2">
-        <v>240</v>
-      </c>
-      <c r="E72" s="5">
+      <c r="D72" s="8">
+        <v>240</v>
+      </c>
+      <c r="E72" s="9">
         <v>39</v>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="9">
         <v>37</v>
       </c>
-      <c r="G72" s="5">
+      <c r="G72" s="9">
         <v>24</v>
       </c>
-      <c r="H72" s="5">
+      <c r="H72" s="9">
         <v>24</v>
       </c>
-      <c r="I72" s="5">
+      <c r="I72" s="9">
         <v>24</v>
       </c>
-      <c r="J72" s="5">
+      <c r="J72" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="7">
         <v>1033</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="B73" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C73" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D73" s="2">
-        <v>240</v>
-      </c>
-      <c r="E73" s="5">
+      <c r="D73" s="8">
+        <v>240</v>
+      </c>
+      <c r="E73" s="9">
         <v>38</v>
       </c>
-      <c r="F73" s="5">
+      <c r="F73" s="9">
         <v>37</v>
       </c>
-      <c r="G73" s="5">
+      <c r="G73" s="9">
         <v>24</v>
       </c>
-      <c r="H73" s="5">
+      <c r="H73" s="9">
         <v>28</v>
       </c>
-      <c r="I73" s="5">
+      <c r="I73" s="9">
         <v>26</v>
       </c>
-      <c r="J73" s="5">
+      <c r="J73" s="9">
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="7">
         <v>1034</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="B74" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C74" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D74" s="2">
-        <v>240</v>
-      </c>
-      <c r="E74" s="5">
+      <c r="D74" s="8">
+        <v>240</v>
+      </c>
+      <c r="E74" s="9">
         <v>32</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="9">
         <v>37</v>
       </c>
-      <c r="G74" s="5">
+      <c r="G74" s="9">
         <v>20</v>
       </c>
-      <c r="H74" s="5">
+      <c r="H74" s="9">
         <v>25</v>
       </c>
-      <c r="I74" s="5">
+      <c r="I74" s="9">
         <v>20</v>
       </c>
-      <c r="J74" s="5">
+      <c r="J74" s="9">
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="7">
         <v>1035</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="B75" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C75" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="2">
-        <v>240</v>
-      </c>
-      <c r="E75" s="5">
+      <c r="D75" s="8">
+        <v>240</v>
+      </c>
+      <c r="E75" s="9">
         <v>39</v>
       </c>
-      <c r="F75" s="5">
+      <c r="F75" s="9">
         <v>38</v>
       </c>
-      <c r="G75" s="5">
+      <c r="G75" s="9">
         <v>23</v>
       </c>
-      <c r="H75" s="5">
+      <c r="H75" s="9">
         <v>19</v>
       </c>
-      <c r="I75" s="5">
+      <c r="I75" s="9">
         <v>26</v>
       </c>
-      <c r="J75" s="5">
+      <c r="J75" s="9">
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="7">
         <v>1036</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C76" s="2" t="s">
+      <c r="B76" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C76" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D76" s="2">
-        <v>240</v>
-      </c>
-      <c r="E76" s="5">
+      <c r="D76" s="8">
+        <v>240</v>
+      </c>
+      <c r="E76" s="9">
         <v>0</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="9">
         <v>0</v>
       </c>
-      <c r="G76" s="5">
+      <c r="G76" s="9">
         <v>0</v>
       </c>
-      <c r="H76" s="5">
+      <c r="H76" s="9">
         <v>0</v>
       </c>
-      <c r="I76" s="5">
+      <c r="I76" s="9">
         <v>0</v>
       </c>
-      <c r="J76" s="5">
+      <c r="J76" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="7">
         <v>1037</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C77" s="2" t="s">
+      <c r="B77" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C77" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D77" s="2">
-        <v>240</v>
-      </c>
-      <c r="E77" s="5">
+      <c r="D77" s="8">
+        <v>240</v>
+      </c>
+      <c r="E77" s="9">
         <v>37</v>
       </c>
-      <c r="F77" s="5">
+      <c r="F77" s="9">
         <v>39</v>
       </c>
-      <c r="G77" s="5">
+      <c r="G77" s="9">
         <v>23</v>
       </c>
-      <c r="H77" s="5">
+      <c r="H77" s="9">
         <v>20</v>
       </c>
-      <c r="I77" s="5">
+      <c r="I77" s="9">
         <v>19</v>
       </c>
-      <c r="J77" s="5">
+      <c r="J77" s="9">
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="7">
         <v>1038</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C78" s="2" t="s">
+      <c r="B78" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C78" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D78" s="2">
-        <v>240</v>
-      </c>
-      <c r="E78" s="5">
+      <c r="D78" s="8">
+        <v>240</v>
+      </c>
+      <c r="E78" s="9">
         <v>38</v>
       </c>
-      <c r="F78" s="5">
+      <c r="F78" s="9">
         <v>37</v>
       </c>
-      <c r="G78" s="5">
+      <c r="G78" s="9">
         <v>28</v>
       </c>
-      <c r="H78" s="5">
+      <c r="H78" s="9">
         <v>30</v>
       </c>
-      <c r="I78" s="5">
+      <c r="I78" s="9">
         <v>29</v>
       </c>
-      <c r="J78" s="5">
+      <c r="J78" s="9">
         <v>37</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="7">
         <v>1039</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C79" s="2" t="s">
+      <c r="B79" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D79" s="2">
-        <v>240</v>
-      </c>
-      <c r="E79" s="5">
+      <c r="D79" s="8">
+        <v>240</v>
+      </c>
+      <c r="E79" s="9">
         <v>37</v>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="9">
         <v>40</v>
       </c>
-      <c r="G79" s="5">
+      <c r="G79" s="9">
         <v>30</v>
       </c>
-      <c r="H79" s="5">
+      <c r="H79" s="9">
         <v>22</v>
       </c>
-      <c r="I79" s="5">
+      <c r="I79" s="9">
         <v>28</v>
       </c>
-      <c r="J79" s="5">
+      <c r="J79" s="9">
         <v>33</v>
       </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4753,92 +4785,97 @@
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
         <v>1101</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="2">
-        <v>240</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="C2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="8">
+        <v>240</v>
+      </c>
+      <c r="E2" s="8">
         <v>20</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="8">
         <v>20</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="8">
         <v>20</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="8">
         <v>20</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="8">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
         <v>1102</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2">
-        <v>240</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="C3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="8">
+        <v>240</v>
+      </c>
+      <c r="E3" s="8">
         <v>20</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="8">
         <v>20</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="8">
         <v>20</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="8">
         <v>20</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="8">
         <v>20</v>
       </c>
     </row>
@@ -4854,93 +4891,98 @@
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>1103</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="8">
+        <v>240</v>
+      </c>
+      <c r="E2" s="8">
+        <v>21</v>
+      </c>
+      <c r="F2" s="8">
+        <v>20</v>
+      </c>
+      <c r="G2" s="8">
+        <v>22</v>
+      </c>
+      <c r="H2" s="8">
+        <v>23</v>
+      </c>
+      <c r="I2" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
         <v>1104</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="2">
-        <v>240</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="C3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="8">
+        <v>240</v>
+      </c>
+      <c r="E3" s="8">
         <v>21</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F3" s="8">
         <v>20</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G3" s="8">
         <v>22</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H3" s="8">
         <v>23</v>
       </c>
-      <c r="I2" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>1105</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2">
-        <v>240</v>
-      </c>
-      <c r="E3" s="2">
-        <v>21</v>
-      </c>
-      <c r="F3" s="2">
-        <v>20</v>
-      </c>
-      <c r="G3" s="2">
-        <v>22</v>
-      </c>
-      <c r="H3" s="2">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="I3" s="8">
         <v>20</v>
       </c>
     </row>

--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D48659-1ECD-4230-B18D-49FCBFCCB49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4BCD15-0286-40E8-8CEE-ABF58509968E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="184">
   <si>
     <t>Roll_No</t>
   </si>
@@ -678,7 +678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -709,6 +709,12 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4761,16 +4767,34 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
+      <c r="A80" s="8">
+        <v>1101</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D80" s="8">
+        <v>240</v>
+      </c>
+      <c r="E80" s="10">
+        <v>20</v>
+      </c>
+      <c r="F80" s="10">
+        <v>20</v>
+      </c>
+      <c r="G80" s="10">
+        <v>20</v>
+      </c>
+      <c r="H80" s="10">
+        <v>20</v>
+      </c>
+      <c r="I80" s="10">
+        <v>20</v>
+      </c>
+      <c r="J80" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4BCD15-0286-40E8-8CEE-ABF58509968E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C3A123-1111-4D87-B631-705705FA5246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="184">
   <si>
     <t>Roll_No</t>
   </si>
@@ -2232,13 +2232,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D043D23-75C9-4A79-B369-DB03044E1B80}">
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2269,8 +2269,20 @@
       <c r="J1" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1001</v>
       </c>
@@ -2302,7 +2314,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1002</v>
       </c>
@@ -2334,7 +2346,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1003</v>
       </c>
@@ -2366,7 +2378,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>1004</v>
       </c>
@@ -2398,7 +2410,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>1005</v>
       </c>
@@ -2430,7 +2442,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>1006</v>
       </c>
@@ -2462,7 +2474,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>1007</v>
       </c>
@@ -2494,7 +2506,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>1008</v>
       </c>
@@ -2526,7 +2538,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>1009</v>
       </c>
@@ -2558,7 +2570,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>1010</v>
       </c>
@@ -2590,7 +2602,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>1011</v>
       </c>
@@ -2622,7 +2634,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>1012</v>
       </c>
@@ -2654,7 +2666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>1013</v>
       </c>
@@ -2686,7 +2698,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>1014</v>
       </c>
@@ -2718,7 +2730,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>1015</v>
       </c>
@@ -4286,7 +4298,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>1025</v>
       </c>
@@ -4318,7 +4330,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>1026</v>
       </c>
@@ -4350,7 +4362,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>1027</v>
       </c>
@@ -4382,7 +4394,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>1028</v>
       </c>
@@ -4414,7 +4426,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>1029</v>
       </c>
@@ -4446,7 +4458,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>1030</v>
       </c>
@@ -4478,7 +4490,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>1031</v>
       </c>
@@ -4510,7 +4522,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>1032</v>
       </c>
@@ -4542,7 +4554,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>1033</v>
       </c>
@@ -4574,7 +4586,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>1034</v>
       </c>
@@ -4606,7 +4618,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>1035</v>
       </c>
@@ -4638,7 +4650,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>1036</v>
       </c>
@@ -4670,7 +4682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>1037</v>
       </c>
@@ -4702,7 +4714,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>1038</v>
       </c>
@@ -4734,7 +4746,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>1039</v>
       </c>
@@ -4766,8 +4778,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="8">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="7">
         <v>1101</v>
       </c>
       <c r="B80" s="13" t="s">
@@ -4779,22 +4791,25 @@
       <c r="D80" s="8">
         <v>240</v>
       </c>
-      <c r="E80" s="10">
-        <v>20</v>
-      </c>
+      <c r="E80" s="10"/>
       <c r="F80" s="10">
         <v>20</v>
       </c>
       <c r="G80" s="10">
         <v>20</v>
       </c>
-      <c r="H80" s="10">
+      <c r="H80" s="10"/>
+      <c r="I80" s="10"/>
+      <c r="J80" s="14"/>
+      <c r="K80">
         <v>20</v>
       </c>
-      <c r="I80" s="10">
+      <c r="L80">
+        <v>12</v>
+      </c>
+      <c r="N80">
         <v>20</v>
       </c>
-      <c r="J80" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C3A123-1111-4D87-B631-705705FA5246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C2C928-A86E-4AB5-B687-A90735434D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="183">
   <si>
     <t>Roll_No</t>
   </si>
@@ -583,9 +583,6 @@
   </si>
   <si>
     <t>01.01.2000</t>
-  </si>
-  <si>
-    <t>11A</t>
   </si>
   <si>
     <t>MALKHAN MEENA</t>
@@ -2099,11 +2096,11 @@
       <c r="F41" s="3">
         <v>9909233641</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">

--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C2C928-A86E-4AB5-B687-A90735434D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB48587-A3EC-43F5-9187-B2749234C1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="183">
   <si>
     <t>Roll_No</t>
   </si>
@@ -635,7 +635,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -671,11 +671,115 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -710,9 +814,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2229,13 +2351,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D043D23-75C9-4A79-B369-DB03044E1B80}">
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2263,23 +2385,20 @@
       <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="N1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1001</v>
       </c>
@@ -2307,11 +2426,14 @@
       <c r="I2" s="9">
         <v>31</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K2" s="21"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="23"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1002</v>
       </c>
@@ -2339,11 +2461,14 @@
       <c r="I3" s="9">
         <v>20</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="15">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K3" s="21"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="23"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1003</v>
       </c>
@@ -2371,11 +2496,14 @@
       <c r="I4" s="9">
         <v>29</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K4" s="21"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="23"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>1004</v>
       </c>
@@ -2403,11 +2531,14 @@
       <c r="I5" s="9">
         <v>39</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="15">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K5" s="21"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="23"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>1005</v>
       </c>
@@ -2435,11 +2566,14 @@
       <c r="I6" s="9">
         <v>39</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="15">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K6" s="21"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="23"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>1006</v>
       </c>
@@ -2467,11 +2601,14 @@
       <c r="I7" s="9">
         <v>21</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="15">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K7" s="21"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="23"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>1007</v>
       </c>
@@ -2499,11 +2636,14 @@
       <c r="I8" s="9">
         <v>22</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="15">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K8" s="21"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="23"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>1008</v>
       </c>
@@ -2531,11 +2671,14 @@
       <c r="I9" s="9">
         <v>35</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K9" s="21"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="23"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>1009</v>
       </c>
@@ -2563,11 +2706,14 @@
       <c r="I10" s="9">
         <v>24</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="15">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K10" s="21"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="23"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>1010</v>
       </c>
@@ -2595,11 +2741,14 @@
       <c r="I11" s="9">
         <v>25</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="15">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K11" s="21"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="23"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>1011</v>
       </c>
@@ -2627,11 +2776,14 @@
       <c r="I12" s="9">
         <v>34</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="15">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K12" s="21"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="23"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>1012</v>
       </c>
@@ -2659,11 +2811,14 @@
       <c r="I13" s="9">
         <v>9</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="15">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K13" s="21"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="23"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>1013</v>
       </c>
@@ -2691,11 +2846,14 @@
       <c r="I14" s="9">
         <v>34</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="15">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K14" s="21"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="23"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>1014</v>
       </c>
@@ -2723,11 +2881,14 @@
       <c r="I15" s="9">
         <v>38</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="15">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K15" s="21"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="23"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>1015</v>
       </c>
@@ -2755,11 +2916,14 @@
       <c r="I16" s="9">
         <v>38</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="15">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="21"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="23"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>1016</v>
       </c>
@@ -2787,11 +2951,14 @@
       <c r="I17" s="9">
         <v>37</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="15">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="21"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="23"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>1017</v>
       </c>
@@ -2819,11 +2986,14 @@
       <c r="I18" s="9">
         <v>38</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="15">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18" s="21"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="23"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>1018</v>
       </c>
@@ -2851,11 +3021,14 @@
       <c r="I19" s="9">
         <v>21</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="15">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="21"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="23"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>1019</v>
       </c>
@@ -2883,11 +3056,14 @@
       <c r="I20" s="9">
         <v>8</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="15">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="21"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="23"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>1020</v>
       </c>
@@ -2915,11 +3091,14 @@
       <c r="I21" s="9">
         <v>20</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="15">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="21"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="23"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>1021</v>
       </c>
@@ -2947,11 +3126,14 @@
       <c r="I22" s="9">
         <v>20</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="15">
         <v>34</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22" s="21"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="23"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>1022</v>
       </c>
@@ -2979,11 +3161,14 @@
       <c r="I23" s="9">
         <v>21</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="15">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" s="21"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="23"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>1023</v>
       </c>
@@ -3011,11 +3196,14 @@
       <c r="I24" s="9">
         <v>31</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="15">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K24" s="21"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="23"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>1024</v>
       </c>
@@ -3043,11 +3231,14 @@
       <c r="I25" s="9">
         <v>37</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K25" s="21"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="23"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>1025</v>
       </c>
@@ -3075,11 +3266,14 @@
       <c r="I26" s="9">
         <v>27</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="15">
         <v>30</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26" s="21"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="23"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>1026</v>
       </c>
@@ -3107,11 +3301,14 @@
       <c r="I27" s="9">
         <v>36</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="21"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="23"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>1027</v>
       </c>
@@ -3139,11 +3336,14 @@
       <c r="I28" s="9">
         <v>30</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="15">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="21"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="23"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>1028</v>
       </c>
@@ -3171,11 +3371,14 @@
       <c r="I29" s="9">
         <v>35</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="15">
         <v>37</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="21"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="23"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>1029</v>
       </c>
@@ -3203,11 +3406,14 @@
       <c r="I30" s="9">
         <v>36</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="21"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="23"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>1030</v>
       </c>
@@ -3235,11 +3441,14 @@
       <c r="I31" s="9">
         <v>0</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="15">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="21"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="23"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>1031</v>
       </c>
@@ -3267,11 +3476,14 @@
       <c r="I32" s="9">
         <v>36</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="15">
         <v>37</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="21"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="23"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>1032</v>
       </c>
@@ -3299,11 +3511,14 @@
       <c r="I33" s="9">
         <v>36</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="15">
         <v>35</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="21"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="23"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>1033</v>
       </c>
@@ -3331,11 +3546,14 @@
       <c r="I34" s="9">
         <v>28</v>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="15">
         <v>36</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="21"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="23"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>1034</v>
       </c>
@@ -3363,11 +3581,14 @@
       <c r="I35" s="9">
         <v>29</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="15">
         <v>31</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K35" s="21"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="23"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>1035</v>
       </c>
@@ -3395,11 +3616,14 @@
       <c r="I36" s="9">
         <v>34</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="15">
         <v>26</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K36" s="21"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="23"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>1036</v>
       </c>
@@ -3427,11 +3651,14 @@
       <c r="I37" s="9">
         <v>33</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="15">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K37" s="21"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="23"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>1037</v>
       </c>
@@ -3459,11 +3686,14 @@
       <c r="I38" s="9">
         <v>21</v>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="15">
         <v>31</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K38" s="21"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="23"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>1038</v>
       </c>
@@ -3491,11 +3721,14 @@
       <c r="I39" s="9">
         <v>35</v>
       </c>
-      <c r="J39" s="9">
+      <c r="J39" s="15">
         <v>34</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K39" s="21"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="23"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>1039</v>
       </c>
@@ -3523,11 +3756,14 @@
       <c r="I40" s="9">
         <v>33</v>
       </c>
-      <c r="J40" s="9">
+      <c r="J40" s="15">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K40" s="21"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="23"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>1001</v>
       </c>
@@ -3555,11 +3791,14 @@
       <c r="I41" s="11">
         <v>22</v>
       </c>
-      <c r="J41" s="11">
+      <c r="J41" s="16">
         <v>33</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K41" s="21"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="23"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>1002</v>
       </c>
@@ -3587,11 +3826,14 @@
       <c r="I42" s="11">
         <v>18</v>
       </c>
-      <c r="J42" s="11">
+      <c r="J42" s="16">
         <v>29</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K42" s="21"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="23"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>1003</v>
       </c>
@@ -3619,11 +3861,14 @@
       <c r="I43" s="11">
         <v>14</v>
       </c>
-      <c r="J43" s="11">
+      <c r="J43" s="16">
         <v>38</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K43" s="21"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="23"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>1004</v>
       </c>
@@ -3651,11 +3896,14 @@
       <c r="I44" s="9">
         <v>34</v>
       </c>
-      <c r="J44" s="9">
+      <c r="J44" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K44" s="21"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="23"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>1005</v>
       </c>
@@ -3683,11 +3931,14 @@
       <c r="I45" s="9">
         <v>30</v>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="15">
         <v>35</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K45" s="21"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="23"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>1006</v>
       </c>
@@ -3715,11 +3966,14 @@
       <c r="I46" s="9">
         <v>23</v>
       </c>
-      <c r="J46" s="9">
+      <c r="J46" s="15">
         <v>26</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K46" s="21"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="23"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>1007</v>
       </c>
@@ -3747,11 +4001,14 @@
       <c r="I47" s="9">
         <v>18</v>
       </c>
-      <c r="J47" s="9">
+      <c r="J47" s="15">
         <v>35</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K47" s="21"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="23"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>1008</v>
       </c>
@@ -3779,11 +4036,14 @@
       <c r="I48" s="9">
         <v>0</v>
       </c>
-      <c r="J48" s="9">
+      <c r="J48" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K48" s="21"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="23"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>1009</v>
       </c>
@@ -3811,11 +4071,14 @@
       <c r="I49" s="9">
         <v>25</v>
       </c>
-      <c r="J49" s="9">
+      <c r="J49" s="15">
         <v>34</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K49" s="21"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="23"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>1010</v>
       </c>
@@ -3843,11 +4106,14 @@
       <c r="I50" s="9">
         <v>26</v>
       </c>
-      <c r="J50" s="9">
+      <c r="J50" s="15">
         <v>34</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K50" s="21"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="23"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>1011</v>
       </c>
@@ -3875,11 +4141,14 @@
       <c r="I51" s="9">
         <v>28</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="15">
         <v>37</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K51" s="21"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="23"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>1012</v>
       </c>
@@ -3907,11 +4176,14 @@
       <c r="I52" s="9">
         <v>7</v>
       </c>
-      <c r="J52" s="9">
+      <c r="J52" s="15">
         <v>24</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K52" s="21"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="23"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>1013</v>
       </c>
@@ -3939,11 +4211,14 @@
       <c r="I53" s="9">
         <v>29</v>
       </c>
-      <c r="J53" s="9">
+      <c r="J53" s="15">
         <v>37</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K53" s="21"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="23"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>1014</v>
       </c>
@@ -3971,11 +4246,14 @@
       <c r="I54" s="9">
         <v>30</v>
       </c>
-      <c r="J54" s="9">
+      <c r="J54" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K54" s="21"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="23"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>1015</v>
       </c>
@@ -4003,11 +4281,14 @@
       <c r="I55" s="9">
         <v>28</v>
       </c>
-      <c r="J55" s="9">
+      <c r="J55" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K55" s="21"/>
+      <c r="L55" s="22"/>
+      <c r="M55" s="23"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>1016</v>
       </c>
@@ -4035,11 +4316,14 @@
       <c r="I56" s="9">
         <v>30</v>
       </c>
-      <c r="J56" s="9">
+      <c r="J56" s="15">
         <v>28</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K56" s="21"/>
+      <c r="L56" s="22"/>
+      <c r="M56" s="23"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>1017</v>
       </c>
@@ -4067,11 +4351,14 @@
       <c r="I57" s="9">
         <v>25</v>
       </c>
-      <c r="J57" s="9">
+      <c r="J57" s="15">
         <v>31</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K57" s="21"/>
+      <c r="L57" s="22"/>
+      <c r="M57" s="23"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>1018</v>
       </c>
@@ -4099,11 +4386,14 @@
       <c r="I58" s="9">
         <v>17</v>
       </c>
-      <c r="J58" s="9">
+      <c r="J58" s="15">
         <v>27</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K58" s="21"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="23"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>1019</v>
       </c>
@@ -4131,11 +4421,14 @@
       <c r="I59" s="9">
         <v>0</v>
       </c>
-      <c r="J59" s="9">
+      <c r="J59" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K59" s="21"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="23"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>1020</v>
       </c>
@@ -4163,11 +4456,14 @@
       <c r="I60" s="9">
         <v>22</v>
       </c>
-      <c r="J60" s="9">
+      <c r="J60" s="15">
         <v>32</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K60" s="21"/>
+      <c r="L60" s="22"/>
+      <c r="M60" s="23"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>1021</v>
       </c>
@@ -4195,11 +4491,14 @@
       <c r="I61" s="9">
         <v>20</v>
       </c>
-      <c r="J61" s="9">
+      <c r="J61" s="15">
         <v>26</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K61" s="21"/>
+      <c r="L61" s="22"/>
+      <c r="M61" s="23"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>1022</v>
       </c>
@@ -4227,11 +4526,14 @@
       <c r="I62" s="9">
         <v>14</v>
       </c>
-      <c r="J62" s="9">
+      <c r="J62" s="15">
         <v>29</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K62" s="21"/>
+      <c r="L62" s="22"/>
+      <c r="M62" s="23"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>1023</v>
       </c>
@@ -4259,11 +4561,14 @@
       <c r="I63" s="9">
         <v>18</v>
       </c>
-      <c r="J63" s="9">
+      <c r="J63" s="15">
         <v>32</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K63" s="21"/>
+      <c r="L63" s="22"/>
+      <c r="M63" s="23"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>1024</v>
       </c>
@@ -4291,11 +4596,14 @@
       <c r="I64" s="9">
         <v>26</v>
       </c>
-      <c r="J64" s="9">
+      <c r="J64" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K64" s="21"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="23"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>1025</v>
       </c>
@@ -4323,11 +4631,14 @@
       <c r="I65" s="9">
         <v>23</v>
       </c>
-      <c r="J65" s="9">
+      <c r="J65" s="15">
         <v>29</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K65" s="21"/>
+      <c r="L65" s="22"/>
+      <c r="M65" s="23"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>1026</v>
       </c>
@@ -4355,11 +4666,14 @@
       <c r="I66" s="9">
         <v>28</v>
       </c>
-      <c r="J66" s="9">
+      <c r="J66" s="15">
         <v>40</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K66" s="21"/>
+      <c r="L66" s="22"/>
+      <c r="M66" s="23"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>1027</v>
       </c>
@@ -4387,11 +4701,14 @@
       <c r="I67" s="9">
         <v>21</v>
       </c>
-      <c r="J67" s="9">
+      <c r="J67" s="15">
         <v>29</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K67" s="21"/>
+      <c r="L67" s="22"/>
+      <c r="M67" s="23"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>1028</v>
       </c>
@@ -4419,11 +4736,14 @@
       <c r="I68" s="9">
         <v>28</v>
       </c>
-      <c r="J68" s="9">
+      <c r="J68" s="15">
         <v>34</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K68" s="21"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="23"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>1029</v>
       </c>
@@ -4451,11 +4771,14 @@
       <c r="I69" s="9">
         <v>30</v>
       </c>
-      <c r="J69" s="9">
+      <c r="J69" s="15">
         <v>35</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K69" s="21"/>
+      <c r="L69" s="22"/>
+      <c r="M69" s="23"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>1030</v>
       </c>
@@ -4483,11 +4806,14 @@
       <c r="I70" s="9">
         <v>37</v>
       </c>
-      <c r="J70" s="9">
+      <c r="J70" s="15">
         <v>37</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K70" s="21"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="23"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>1031</v>
       </c>
@@ -4515,11 +4841,14 @@
       <c r="I71" s="9">
         <v>24</v>
       </c>
-      <c r="J71" s="9">
+      <c r="J71" s="15">
         <v>38</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K71" s="21"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="23"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>1032</v>
       </c>
@@ -4547,11 +4876,14 @@
       <c r="I72" s="9">
         <v>24</v>
       </c>
-      <c r="J72" s="9">
+      <c r="J72" s="15">
         <v>34</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K72" s="21"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="23"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>1033</v>
       </c>
@@ -4579,11 +4911,14 @@
       <c r="I73" s="9">
         <v>26</v>
       </c>
-      <c r="J73" s="9">
+      <c r="J73" s="15">
         <v>30</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K73" s="21"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="23"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>1034</v>
       </c>
@@ -4611,11 +4946,14 @@
       <c r="I74" s="9">
         <v>20</v>
       </c>
-      <c r="J74" s="9">
+      <c r="J74" s="15">
         <v>32</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K74" s="21"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="23"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>1035</v>
       </c>
@@ -4643,11 +4981,14 @@
       <c r="I75" s="9">
         <v>26</v>
       </c>
-      <c r="J75" s="9">
+      <c r="J75" s="15">
         <v>34</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K75" s="21"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="23"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>1036</v>
       </c>
@@ -4675,11 +5016,14 @@
       <c r="I76" s="9">
         <v>0</v>
       </c>
-      <c r="J76" s="9">
+      <c r="J76" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K76" s="21"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="23"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>1037</v>
       </c>
@@ -4707,11 +5051,14 @@
       <c r="I77" s="9">
         <v>19</v>
       </c>
-      <c r="J77" s="9">
+      <c r="J77" s="15">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K77" s="21"/>
+      <c r="L77" s="22"/>
+      <c r="M77" s="23"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>1038</v>
       </c>
@@ -4739,11 +5086,14 @@
       <c r="I78" s="9">
         <v>29</v>
       </c>
-      <c r="J78" s="9">
+      <c r="J78" s="15">
         <v>37</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K78" s="21"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="23"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>1039</v>
       </c>
@@ -4771,11 +5121,14 @@
       <c r="I79" s="9">
         <v>28</v>
       </c>
-      <c r="J79" s="9">
+      <c r="J79" s="15">
         <v>33</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K79" s="21"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="23"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="7">
         <v>1101</v>
       </c>
@@ -4795,18 +5148,18 @@
       <c r="G80" s="10">
         <v>20</v>
       </c>
-      <c r="H80" s="10"/>
+      <c r="H80" s="10">
+        <v>30</v>
+      </c>
       <c r="I80" s="10"/>
-      <c r="J80" s="14"/>
-      <c r="K80">
+      <c r="J80" s="17"/>
+      <c r="K80" s="24">
         <v>20</v>
       </c>
-      <c r="L80">
+      <c r="L80" s="25">
         <v>12</v>
       </c>
-      <c r="N80">
-        <v>20</v>
-      </c>
+      <c r="M80" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB48587-A3EC-43F5-9187-B2749234C1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A2E9BF-3622-4B56-AA70-AFF7F45F89D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="264">
   <si>
     <t>Roll_No</t>
   </si>
@@ -582,17 +582,260 @@
     <t>PWT-2</t>
   </si>
   <si>
-    <t>01.01.2000</t>
-  </si>
-  <si>
-    <t>MALKHAN MEENA</t>
+    <t>TADVI AYUSHIBEN ARVINDBHAI</t>
+  </si>
+  <si>
+    <t>GURJAR DIVYA HOSHIYARSINGH</t>
+  </si>
+  <si>
+    <t>HARESH BARIA</t>
+  </si>
+  <si>
+    <t>PATHAN HUSEN ALLAHRAKHA</t>
+  </si>
+  <si>
+    <t>VASAVA JINALBEN JALARAMBHAI</t>
+  </si>
+  <si>
+    <t>MEET BARIA</t>
+  </si>
+  <si>
+    <t>NIRAV RATHVA</t>
+  </si>
+  <si>
+    <t>TAVIYAD RIYABEN PARESHKUMAR</t>
+  </si>
+  <si>
+    <t>SACHIN RATHVA</t>
+  </si>
+  <si>
+    <t>SNEHABEN PANCHOLI</t>
+  </si>
+  <si>
+    <t>SUMIT RATHVA</t>
+  </si>
+  <si>
+    <t>TANVIBEN RATHVA</t>
+  </si>
+  <si>
+    <t>TEJASVINIBEN PARMAR</t>
+  </si>
+  <si>
+    <t>URVASHIBEN ASANBHAI</t>
+  </si>
+  <si>
+    <t>ZALAK RATHWA</t>
+  </si>
+  <si>
+    <t>GAURANGBHAI NARESHBHAI RATHWA</t>
+  </si>
+  <si>
+    <t>NISHABEN DILIPBHAI TADVI</t>
+  </si>
+  <si>
+    <t>AKSHARA IRFAN PATHAN</t>
+  </si>
+  <si>
+    <t>RATHVA RITABEN KANUBHAI</t>
+  </si>
+  <si>
+    <t>JANVI KANTIBHAI RATHVA</t>
+  </si>
+  <si>
+    <t>BHILALA TEJALBEN KUKANIYABHAI</t>
+  </si>
+  <si>
+    <t>ARYA RATHVA</t>
+  </si>
+  <si>
+    <t>DIXANTKUMAR CHAUHAN</t>
+  </si>
+  <si>
+    <t>DIYA PANCHAL</t>
+  </si>
+  <si>
+    <t>KHATRI FARHANA ABDUL SATTAR</t>
+  </si>
+  <si>
+    <t>PATHAR JAYKUMAR PALABHAI</t>
+  </si>
+  <si>
+    <t>JYOTIKABEN TADVI</t>
+  </si>
+  <si>
+    <t>KRISH DER</t>
+  </si>
+  <si>
+    <t>NIKHIL RATHVA</t>
+  </si>
+  <si>
+    <t>SVARKUMAR RATHWA</t>
+  </si>
+  <si>
+    <t>YUG BARIA</t>
+  </si>
+  <si>
+    <t>ALISHA MOHSINBHAI MAKRANI</t>
+  </si>
+  <si>
+    <t>BHAGYASHREE PARMAR</t>
+  </si>
+  <si>
+    <t>VASAVA TEJASVIKUMARI HARESHBHAI</t>
+  </si>
+  <si>
+    <t>TADVI ARVINDBHAI</t>
+  </si>
+  <si>
+    <t>GURJAR HOSHIYARSINGH</t>
+  </si>
+  <si>
+    <t>BHOPATSINH</t>
+  </si>
+  <si>
+    <t>PATHAN ALLAHRAKHA</t>
+  </si>
+  <si>
+    <t>VASAVA JALARAMBHAI</t>
+  </si>
+  <si>
+    <t>RAJENDRABHAI</t>
+  </si>
+  <si>
+    <t>RANGESHBHAI</t>
+  </si>
+  <si>
+    <t>TAVIYAD PARESHBHAI</t>
+  </si>
+  <si>
+    <t>ISHWARBHAI</t>
+  </si>
+  <si>
+    <t>SHANABHAI</t>
+  </si>
+  <si>
+    <t>RAJUBHAI</t>
+  </si>
+  <si>
+    <t>DINESHBHAI</t>
+  </si>
+  <si>
+    <t>VINODBHAI</t>
+  </si>
+  <si>
+    <t>VASAVA HARESHBHAI</t>
+  </si>
+  <si>
+    <t>ASANBHAI</t>
+  </si>
+  <si>
+    <t>MURSINGBHAI</t>
+  </si>
+  <si>
+    <t>NARESHBHAI</t>
+  </si>
+  <si>
+    <t>DILIPBHAI TADVI</t>
+  </si>
+  <si>
+    <t>IRFANBHAI</t>
+  </si>
+  <si>
+    <t>KANUBHAI</t>
+  </si>
+  <si>
+    <t>KANTIBHAI RATHVA</t>
+  </si>
+  <si>
+    <t>KUKANIYABHAI</t>
+  </si>
+  <si>
+    <t>RIKESHKUMAR</t>
+  </si>
+  <si>
+    <t>GULABSINH</t>
+  </si>
+  <si>
+    <t>CHANDRAKANT</t>
+  </si>
+  <si>
+    <t>ABDUL SATTAR</t>
+  </si>
+  <si>
+    <t>PATHAR PALABHAI</t>
+  </si>
+  <si>
+    <t>HARISHBHAI</t>
+  </si>
+  <si>
+    <t>BHARATBHAI</t>
+  </si>
+  <si>
+    <t>KAMLESHBHAI</t>
+  </si>
+  <si>
+    <t>ASHOKBHAI</t>
+  </si>
+  <si>
+    <t>MOHSINBHAI</t>
+  </si>
+  <si>
+    <t>SHAILESHKUMAR</t>
+  </si>
+  <si>
+    <t>562114325626</t>
+  </si>
+  <si>
+    <t>313028784157</t>
+  </si>
+  <si>
+    <t>982555489859</t>
+  </si>
+  <si>
+    <t>873277459691</t>
+  </si>
+  <si>
+    <t>776844204534</t>
+  </si>
+  <si>
+    <t>366718397233</t>
+  </si>
+  <si>
+    <t>03.03.2010</t>
+  </si>
+  <si>
+    <t>24.11.2009</t>
+  </si>
+  <si>
+    <t>21.03.2009</t>
+  </si>
+  <si>
+    <t>22.06.2009</t>
+  </si>
+  <si>
+    <t>31.08.2009</t>
+  </si>
+  <si>
+    <t>12-PCB</t>
+  </si>
+  <si>
+    <t>12-PCM</t>
+  </si>
+  <si>
+    <t>DINESH RATHOD</t>
+  </si>
+  <si>
+    <t>OD</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -626,16 +869,75 @@
       <name val="Cambria"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -707,26 +1009,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -748,20 +1030,24 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
+      <left style="thin">
         <color indexed="64"/>
-      </bottom>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -769,17 +1055,21 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -808,9 +1098,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -826,20 +1113,192 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1149,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542F166A-4256-4AA6-A03A-29FB16EA9D15}">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -2201,157 +2660,914 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>1101</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41" s="6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B41" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="E41" s="12">
-        <v>884813537312</v>
-      </c>
-      <c r="F41" s="3">
-        <v>9909233641</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>13</v>
+      <c r="C41" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D41" s="32">
+        <v>40147</v>
+      </c>
+      <c r="E41" s="27">
+        <v>629725429548</v>
+      </c>
+      <c r="F41" s="2">
+        <v>7874735374</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>259</v>
       </c>
       <c r="H41" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="19">
+        <v>1202</v>
+      </c>
+      <c r="B42" s="20" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
+      <c r="C42" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D42" s="32">
+        <v>40431</v>
+      </c>
+      <c r="E42" s="27">
+        <v>868784631083</v>
+      </c>
+      <c r="F42" s="35">
+        <v>9624104337</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
+      <c r="A43" s="6">
+        <v>1203</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D43" s="32">
+        <v>39743</v>
+      </c>
+      <c r="E43" s="27">
+        <v>861502383654</v>
+      </c>
+      <c r="F43" s="35">
+        <v>8141169136</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G44" s="1"/>
+      <c r="A44" s="19">
+        <v>1204</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D44" s="32">
+        <v>39823</v>
+      </c>
+      <c r="E44" s="27">
+        <v>523235907356</v>
+      </c>
+      <c r="F44" s="2">
+        <v>9737392469</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G45" s="1"/>
+      <c r="A45" s="6">
+        <v>1205</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D45" s="32">
+        <v>40078</v>
+      </c>
+      <c r="E45" s="27">
+        <v>892372104796</v>
+      </c>
+      <c r="F45" s="35">
+        <v>9265841928</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G46" s="1"/>
+      <c r="A46" s="19">
+        <v>1206</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D46" s="32">
+        <v>39991</v>
+      </c>
+      <c r="E46" s="27">
+        <v>412140699697</v>
+      </c>
+      <c r="F46" s="35">
+        <v>9725282548</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G47" s="1"/>
+      <c r="A47" s="6">
+        <v>1207</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D47" s="32">
+        <v>40163</v>
+      </c>
+      <c r="E47" s="27">
+        <v>240156702958</v>
+      </c>
+      <c r="F47" s="35">
+        <v>9687875011</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G51" s="1"/>
-    </row>
-    <row r="52" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G52" s="1"/>
-    </row>
-    <row r="53" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G53" s="1"/>
-    </row>
-    <row r="54" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G54" s="1"/>
-    </row>
-    <row r="55" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G55" s="1"/>
-    </row>
-    <row r="56" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G56" s="1"/>
-    </row>
-    <row r="57" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G57" s="1"/>
-    </row>
-    <row r="58" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G58" s="1"/>
-    </row>
-    <row r="59" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G59" s="1"/>
-    </row>
-    <row r="60" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G60" s="1"/>
-    </row>
-    <row r="61" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G61" s="1"/>
-    </row>
-    <row r="62" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G62" s="1"/>
-    </row>
-    <row r="63" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G63" s="1"/>
-    </row>
-    <row r="64" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G64" s="1"/>
-    </row>
-    <row r="65" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G65" s="1"/>
-    </row>
-    <row r="66" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G66" s="1"/>
-    </row>
-    <row r="67" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G67" s="1"/>
-    </row>
-    <row r="68" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G68" s="1"/>
-    </row>
-    <row r="69" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G69" s="1"/>
-    </row>
-    <row r="70" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G70" s="1"/>
-    </row>
-    <row r="71" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G71" s="1"/>
-    </row>
-    <row r="72" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G72" s="1"/>
-    </row>
-    <row r="73" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G73" s="1"/>
-    </row>
-    <row r="74" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G74" s="1"/>
-    </row>
-    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G75" s="1"/>
-    </row>
-    <row r="76" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="19">
+        <v>1208</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D48" s="32">
+        <v>40215</v>
+      </c>
+      <c r="E48" s="27">
+        <v>279595726744</v>
+      </c>
+      <c r="F48" s="35">
+        <v>9879537857</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>1209</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D49" s="32">
+        <v>39731</v>
+      </c>
+      <c r="E49" s="27">
+        <v>916336765264</v>
+      </c>
+      <c r="F49" s="2">
+        <v>9537575058</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="19">
+        <v>1210</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D50" s="32">
+        <v>40301</v>
+      </c>
+      <c r="E50" s="27">
+        <v>705953487400</v>
+      </c>
+      <c r="F50" s="35">
+        <v>9687111646</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>1211</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D51" s="32">
+        <v>40224</v>
+      </c>
+      <c r="E51" s="27">
+        <v>764006954215</v>
+      </c>
+      <c r="F51" s="35">
+        <v>8200730410</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="19">
+        <v>1212</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D52" s="32">
+        <v>39614</v>
+      </c>
+      <c r="E52" s="27">
+        <v>329596170047</v>
+      </c>
+      <c r="F52" s="2">
+        <v>9016937704</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="19">
+        <v>1213</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="E53" s="28">
+        <v>520048808079</v>
+      </c>
+      <c r="F53" s="36">
+        <v>991338636</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>1214</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D54" s="32">
+        <v>40051</v>
+      </c>
+      <c r="E54" s="27">
+        <v>632504887936</v>
+      </c>
+      <c r="F54" s="2">
+        <v>9016677020</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>1215</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D55" s="32">
+        <v>39848</v>
+      </c>
+      <c r="E55" s="27">
+        <v>924194629769</v>
+      </c>
+      <c r="F55" s="2">
+        <v>8758595513</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="19">
+        <v>1216</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D56" s="32">
+        <v>40144</v>
+      </c>
+      <c r="E56" s="27">
+        <v>336666374564</v>
+      </c>
+      <c r="F56" s="2">
+        <v>8320226326</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>1217</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C57" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="F57" s="26">
+        <v>6352719479</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="19">
+        <v>1218</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="D58" s="33">
+        <v>40081</v>
+      </c>
+      <c r="E58" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="F58" s="26">
+        <v>9904123744</v>
+      </c>
+      <c r="G58" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>1219</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="D59" s="33">
+        <v>40152</v>
+      </c>
+      <c r="E59" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="F59" s="26">
+        <v>9574218015</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="19">
+        <v>1220</v>
+      </c>
+      <c r="B60" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="D60" s="33">
+        <v>40321</v>
+      </c>
+      <c r="E60" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="F60" s="26">
+        <v>9737894252</v>
+      </c>
+      <c r="G60" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>1221</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="E61" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="F61" s="26">
+        <v>7567095117</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="19">
+        <v>1222</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="E62" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="F62" s="37">
+        <v>6355764851</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>1223</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D63" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="E63" s="31">
+        <v>588971485746</v>
+      </c>
+      <c r="F63" s="35">
+        <v>8156035767</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="19">
+        <v>1224</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D64" s="33">
+        <v>40283</v>
+      </c>
+      <c r="E64" s="30">
+        <v>863609916544</v>
+      </c>
+      <c r="F64" s="37">
+        <v>9925669837</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>1225</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D65" s="32">
+        <v>40301</v>
+      </c>
+      <c r="E65" s="27">
+        <v>877868433283</v>
+      </c>
+      <c r="F65" s="35">
+        <v>9714374772</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="19">
+        <v>1226</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="D66" s="33">
+        <v>40108</v>
+      </c>
+      <c r="E66" s="30">
+        <v>387760716924</v>
+      </c>
+      <c r="F66" s="37">
+        <v>9016525318</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>1227</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C67" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="D67" s="33">
+        <v>40254</v>
+      </c>
+      <c r="E67" s="30">
+        <v>371214659024</v>
+      </c>
+      <c r="F67" s="37">
+        <v>9313281718</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="19">
+        <v>1228</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="D68" s="33">
+        <v>39972</v>
+      </c>
+      <c r="E68" s="30">
+        <v>716050924500</v>
+      </c>
+      <c r="F68" s="37">
+        <v>9925251810</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>1229</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="C69" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="D69" s="33">
+        <v>40003</v>
+      </c>
+      <c r="E69" s="30">
+        <v>770629036161</v>
+      </c>
+      <c r="F69" s="37">
+        <v>9664941182</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="19">
+        <v>1230</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D70" s="32">
+        <v>40141</v>
+      </c>
+      <c r="E70" s="27">
+        <v>646034972649</v>
+      </c>
+      <c r="F70" s="35">
+        <v>9979692514</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>1231</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D71" s="32">
+        <v>40014</v>
+      </c>
+      <c r="E71" s="27">
+        <v>681716388949</v>
+      </c>
+      <c r="F71" s="35">
+        <v>9824446619</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="19">
+        <v>1232</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D72" s="32">
+        <v>39888</v>
+      </c>
+      <c r="E72" s="27">
+        <v>680078961178</v>
+      </c>
+      <c r="F72" s="35">
+        <v>9016181529</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>1233</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D73" s="32">
+        <v>40168</v>
+      </c>
+      <c r="E73" s="27">
+        <v>934647778164</v>
+      </c>
+      <c r="F73" s="35">
+        <v>9313203487</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="19">
+        <v>1234</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D74" s="32">
+        <v>40188</v>
+      </c>
+      <c r="E74" s="27">
+        <v>743736078906</v>
+      </c>
+      <c r="F74" s="35">
+        <v>9879009201</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G79" s="1"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G80" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="E2:E40" numberStoredAsText="1"/>
+    <ignoredError sqref="E2:E40 E57:E62" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D043D23-75C9-4A79-B369-DB03044E1B80}">
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="22.28515625" customWidth="1"/>
@@ -2385,16 +3601,16 @@
       <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2426,12 +3642,11 @@
       <c r="I2" s="9">
         <v>31</v>
       </c>
-      <c r="J2" s="15">
+      <c r="J2" s="14">
         <v>38</v>
       </c>
-      <c r="K2" s="21"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="23"/>
+      <c r="K2" s="17"/>
+      <c r="M2" s="18"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
@@ -2461,12 +3676,11 @@
       <c r="I3" s="9">
         <v>20</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="14">
         <v>29</v>
       </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="23"/>
+      <c r="K3" s="17"/>
+      <c r="M3" s="18"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -2496,12 +3710,11 @@
       <c r="I4" s="9">
         <v>29</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="14">
         <v>38</v>
       </c>
-      <c r="K4" s="21"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="23"/>
+      <c r="K4" s="17"/>
+      <c r="M4" s="18"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
@@ -2531,12 +3744,11 @@
       <c r="I5" s="9">
         <v>39</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="14">
         <v>36</v>
       </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="23"/>
+      <c r="K5" s="17"/>
+      <c r="M5" s="18"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
@@ -2566,12 +3778,11 @@
       <c r="I6" s="9">
         <v>39</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="14">
         <v>36</v>
       </c>
-      <c r="K6" s="21"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="23"/>
+      <c r="K6" s="17"/>
+      <c r="M6" s="18"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
@@ -2601,12 +3812,11 @@
       <c r="I7" s="9">
         <v>21</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="14">
         <v>34</v>
       </c>
-      <c r="K7" s="21"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="23"/>
+      <c r="K7" s="17"/>
+      <c r="M7" s="18"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
@@ -2636,12 +3846,11 @@
       <c r="I8" s="9">
         <v>22</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="14">
         <v>33</v>
       </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="23"/>
+      <c r="K8" s="17"/>
+      <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
@@ -2671,12 +3880,11 @@
       <c r="I9" s="9">
         <v>35</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="14">
         <v>38</v>
       </c>
-      <c r="K9" s="21"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="23"/>
+      <c r="K9" s="17"/>
+      <c r="M9" s="18"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
@@ -2706,12 +3914,11 @@
       <c r="I10" s="9">
         <v>24</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="14">
         <v>25</v>
       </c>
-      <c r="K10" s="21"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="23"/>
+      <c r="K10" s="17"/>
+      <c r="M10" s="18"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
@@ -2741,12 +3948,11 @@
       <c r="I11" s="9">
         <v>25</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="14">
         <v>35</v>
       </c>
-      <c r="K11" s="21"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="23"/>
+      <c r="K11" s="17"/>
+      <c r="M11" s="18"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
@@ -2776,12 +3982,11 @@
       <c r="I12" s="9">
         <v>34</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="14">
         <v>32</v>
       </c>
-      <c r="K12" s="21"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="23"/>
+      <c r="K12" s="17"/>
+      <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
@@ -2811,12 +4016,11 @@
       <c r="I13" s="9">
         <v>9</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="14">
         <v>18</v>
       </c>
-      <c r="K13" s="21"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="23"/>
+      <c r="K13" s="17"/>
+      <c r="M13" s="18"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
@@ -2846,12 +4050,11 @@
       <c r="I14" s="9">
         <v>34</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="14">
         <v>40</v>
       </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="23"/>
+      <c r="K14" s="17"/>
+      <c r="M14" s="18"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
@@ -2881,12 +4084,11 @@
       <c r="I15" s="9">
         <v>38</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <v>39</v>
       </c>
-      <c r="K15" s="21"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="23"/>
+      <c r="K15" s="17"/>
+      <c r="M15" s="18"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
@@ -2916,12 +4118,11 @@
       <c r="I16" s="9">
         <v>38</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="14">
         <v>40</v>
       </c>
-      <c r="K16" s="21"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="23"/>
+      <c r="K16" s="17"/>
+      <c r="M16" s="18"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
@@ -2951,12 +4152,11 @@
       <c r="I17" s="9">
         <v>37</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="14">
         <v>34</v>
       </c>
-      <c r="K17" s="21"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="23"/>
+      <c r="K17" s="17"/>
+      <c r="M17" s="18"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
@@ -2986,12 +4186,11 @@
       <c r="I18" s="9">
         <v>38</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="14">
         <v>32</v>
       </c>
-      <c r="K18" s="21"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="23"/>
+      <c r="K18" s="17"/>
+      <c r="M18" s="18"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
@@ -3021,12 +4220,11 @@
       <c r="I19" s="9">
         <v>21</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="14">
         <v>32</v>
       </c>
-      <c r="K19" s="21"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="23"/>
+      <c r="K19" s="17"/>
+      <c r="M19" s="18"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
@@ -3056,12 +4254,11 @@
       <c r="I20" s="9">
         <v>8</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="14">
         <v>26</v>
       </c>
-      <c r="K20" s="21"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="23"/>
+      <c r="K20" s="17"/>
+      <c r="M20" s="18"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
@@ -3091,12 +4288,11 @@
       <c r="I21" s="9">
         <v>20</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="14">
         <v>24</v>
       </c>
-      <c r="K21" s="21"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="23"/>
+      <c r="K21" s="17"/>
+      <c r="M21" s="18"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
@@ -3126,12 +4322,11 @@
       <c r="I22" s="9">
         <v>20</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="14">
         <v>34</v>
       </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="23"/>
+      <c r="K22" s="17"/>
+      <c r="M22" s="18"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
@@ -3161,12 +4356,11 @@
       <c r="I23" s="9">
         <v>21</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="14">
         <v>27</v>
       </c>
-      <c r="K23" s="21"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="23"/>
+      <c r="K23" s="17"/>
+      <c r="M23" s="18"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
@@ -3196,12 +4390,11 @@
       <c r="I24" s="9">
         <v>31</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="14">
         <v>34</v>
       </c>
-      <c r="K24" s="21"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="23"/>
+      <c r="K24" s="17"/>
+      <c r="M24" s="18"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
@@ -3231,12 +4424,11 @@
       <c r="I25" s="9">
         <v>37</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J25" s="14">
         <v>38</v>
       </c>
-      <c r="K25" s="21"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="23"/>
+      <c r="K25" s="17"/>
+      <c r="M25" s="18"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
@@ -3266,12 +4458,11 @@
       <c r="I26" s="9">
         <v>27</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="14">
         <v>30</v>
       </c>
-      <c r="K26" s="21"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="23"/>
+      <c r="K26" s="17"/>
+      <c r="M26" s="18"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
@@ -3301,12 +4492,11 @@
       <c r="I27" s="9">
         <v>36</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="14">
         <v>38</v>
       </c>
-      <c r="K27" s="21"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="23"/>
+      <c r="K27" s="17"/>
+      <c r="M27" s="18"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
@@ -3336,12 +4526,11 @@
       <c r="I28" s="9">
         <v>30</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="14">
         <v>28</v>
       </c>
-      <c r="K28" s="21"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="23"/>
+      <c r="K28" s="17"/>
+      <c r="M28" s="18"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
@@ -3371,12 +4560,11 @@
       <c r="I29" s="9">
         <v>35</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="14">
         <v>37</v>
       </c>
-      <c r="K29" s="21"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="23"/>
+      <c r="K29" s="17"/>
+      <c r="M29" s="18"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
@@ -3406,12 +4594,11 @@
       <c r="I30" s="9">
         <v>36</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="14">
         <v>38</v>
       </c>
-      <c r="K30" s="21"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="23"/>
+      <c r="K30" s="17"/>
+      <c r="M30" s="18"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
@@ -3441,12 +4628,11 @@
       <c r="I31" s="9">
         <v>0</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="14">
         <v>36</v>
       </c>
-      <c r="K31" s="21"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="17"/>
+      <c r="M31" s="18"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
@@ -3476,12 +4662,11 @@
       <c r="I32" s="9">
         <v>36</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="14">
         <v>37</v>
       </c>
-      <c r="K32" s="21"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="23"/>
+      <c r="K32" s="17"/>
+      <c r="M32" s="18"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
@@ -3511,12 +4696,11 @@
       <c r="I33" s="9">
         <v>36</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="14">
         <v>35</v>
       </c>
-      <c r="K33" s="21"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="23"/>
+      <c r="K33" s="17"/>
+      <c r="M33" s="18"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
@@ -3546,12 +4730,11 @@
       <c r="I34" s="9">
         <v>28</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J34" s="14">
         <v>36</v>
       </c>
-      <c r="K34" s="21"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="23"/>
+      <c r="K34" s="17"/>
+      <c r="M34" s="18"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
@@ -3581,12 +4764,11 @@
       <c r="I35" s="9">
         <v>29</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="14">
         <v>31</v>
       </c>
-      <c r="K35" s="21"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="23"/>
+      <c r="K35" s="17"/>
+      <c r="M35" s="18"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
@@ -3616,12 +4798,11 @@
       <c r="I36" s="9">
         <v>34</v>
       </c>
-      <c r="J36" s="15">
+      <c r="J36" s="14">
         <v>26</v>
       </c>
-      <c r="K36" s="21"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="23"/>
+      <c r="K36" s="17"/>
+      <c r="M36" s="18"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
@@ -3651,12 +4832,11 @@
       <c r="I37" s="9">
         <v>33</v>
       </c>
-      <c r="J37" s="15">
+      <c r="J37" s="14">
         <v>36</v>
       </c>
-      <c r="K37" s="21"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="23"/>
+      <c r="K37" s="17"/>
+      <c r="M37" s="18"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
@@ -3686,12 +4866,11 @@
       <c r="I38" s="9">
         <v>21</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="14">
         <v>31</v>
       </c>
-      <c r="K38" s="21"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="23"/>
+      <c r="K38" s="17"/>
+      <c r="M38" s="18"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
@@ -3721,12 +4900,11 @@
       <c r="I39" s="9">
         <v>35</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>34</v>
       </c>
-      <c r="K39" s="21"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="23"/>
+      <c r="K39" s="17"/>
+      <c r="M39" s="18"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
@@ -3756,12 +4934,11 @@
       <c r="I40" s="9">
         <v>33</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>36</v>
       </c>
-      <c r="K40" s="21"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="23"/>
+      <c r="K40" s="17"/>
+      <c r="M40" s="18"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
@@ -3791,12 +4968,11 @@
       <c r="I41" s="11">
         <v>22</v>
       </c>
-      <c r="J41" s="16">
+      <c r="J41" s="15">
         <v>33</v>
       </c>
-      <c r="K41" s="21"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="23"/>
+      <c r="K41" s="17"/>
+      <c r="M41" s="18"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
@@ -3826,12 +5002,11 @@
       <c r="I42" s="11">
         <v>18</v>
       </c>
-      <c r="J42" s="16">
+      <c r="J42" s="15">
         <v>29</v>
       </c>
-      <c r="K42" s="21"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="23"/>
+      <c r="K42" s="17"/>
+      <c r="M42" s="18"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
@@ -3861,12 +5036,11 @@
       <c r="I43" s="11">
         <v>14</v>
       </c>
-      <c r="J43" s="16">
+      <c r="J43" s="15">
         <v>38</v>
       </c>
-      <c r="K43" s="21"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="23"/>
+      <c r="K43" s="17"/>
+      <c r="M43" s="18"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
@@ -3896,12 +5070,11 @@
       <c r="I44" s="9">
         <v>34</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>38</v>
       </c>
-      <c r="K44" s="21"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="23"/>
+      <c r="K44" s="17"/>
+      <c r="M44" s="18"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
@@ -3931,12 +5104,11 @@
       <c r="I45" s="9">
         <v>30</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>35</v>
       </c>
-      <c r="K45" s="21"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="23"/>
+      <c r="K45" s="17"/>
+      <c r="M45" s="18"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
@@ -3966,12 +5138,11 @@
       <c r="I46" s="9">
         <v>23</v>
       </c>
-      <c r="J46" s="15">
+      <c r="J46" s="14">
         <v>26</v>
       </c>
-      <c r="K46" s="21"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="23"/>
+      <c r="K46" s="17"/>
+      <c r="M46" s="18"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
@@ -4001,12 +5172,11 @@
       <c r="I47" s="9">
         <v>18</v>
       </c>
-      <c r="J47" s="15">
+      <c r="J47" s="14">
         <v>35</v>
       </c>
-      <c r="K47" s="21"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="23"/>
+      <c r="K47" s="17"/>
+      <c r="M47" s="18"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
@@ -4036,12 +5206,11 @@
       <c r="I48" s="9">
         <v>0</v>
       </c>
-      <c r="J48" s="15">
+      <c r="J48" s="14">
         <v>0</v>
       </c>
-      <c r="K48" s="21"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="23"/>
+      <c r="K48" s="17"/>
+      <c r="M48" s="18"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
@@ -4071,12 +5240,11 @@
       <c r="I49" s="9">
         <v>25</v>
       </c>
-      <c r="J49" s="15">
+      <c r="J49" s="14">
         <v>34</v>
       </c>
-      <c r="K49" s="21"/>
-      <c r="L49" s="22"/>
-      <c r="M49" s="23"/>
+      <c r="K49" s="17"/>
+      <c r="M49" s="18"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
@@ -4106,12 +5274,11 @@
       <c r="I50" s="9">
         <v>26</v>
       </c>
-      <c r="J50" s="15">
+      <c r="J50" s="14">
         <v>34</v>
       </c>
-      <c r="K50" s="21"/>
-      <c r="L50" s="22"/>
-      <c r="M50" s="23"/>
+      <c r="K50" s="17"/>
+      <c r="M50" s="18"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
@@ -4141,12 +5308,11 @@
       <c r="I51" s="9">
         <v>28</v>
       </c>
-      <c r="J51" s="15">
+      <c r="J51" s="14">
         <v>37</v>
       </c>
-      <c r="K51" s="21"/>
-      <c r="L51" s="22"/>
-      <c r="M51" s="23"/>
+      <c r="K51" s="17"/>
+      <c r="M51" s="18"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
@@ -4176,12 +5342,11 @@
       <c r="I52" s="9">
         <v>7</v>
       </c>
-      <c r="J52" s="15">
+      <c r="J52" s="14">
         <v>24</v>
       </c>
-      <c r="K52" s="21"/>
-      <c r="L52" s="22"/>
-      <c r="M52" s="23"/>
+      <c r="K52" s="17"/>
+      <c r="M52" s="18"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
@@ -4211,12 +5376,11 @@
       <c r="I53" s="9">
         <v>29</v>
       </c>
-      <c r="J53" s="15">
+      <c r="J53" s="14">
         <v>37</v>
       </c>
-      <c r="K53" s="21"/>
-      <c r="L53" s="22"/>
-      <c r="M53" s="23"/>
+      <c r="K53" s="17"/>
+      <c r="M53" s="18"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
@@ -4246,12 +5410,11 @@
       <c r="I54" s="9">
         <v>30</v>
       </c>
-      <c r="J54" s="15">
+      <c r="J54" s="14">
         <v>38</v>
       </c>
-      <c r="K54" s="21"/>
-      <c r="L54" s="22"/>
-      <c r="M54" s="23"/>
+      <c r="K54" s="17"/>
+      <c r="M54" s="18"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
@@ -4281,12 +5444,11 @@
       <c r="I55" s="9">
         <v>28</v>
       </c>
-      <c r="J55" s="15">
+      <c r="J55" s="14">
         <v>38</v>
       </c>
-      <c r="K55" s="21"/>
-      <c r="L55" s="22"/>
-      <c r="M55" s="23"/>
+      <c r="K55" s="17"/>
+      <c r="M55" s="18"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
@@ -4316,12 +5478,11 @@
       <c r="I56" s="9">
         <v>30</v>
       </c>
-      <c r="J56" s="15">
+      <c r="J56" s="14">
         <v>28</v>
       </c>
-      <c r="K56" s="21"/>
-      <c r="L56" s="22"/>
-      <c r="M56" s="23"/>
+      <c r="K56" s="17"/>
+      <c r="M56" s="18"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
@@ -4351,12 +5512,11 @@
       <c r="I57" s="9">
         <v>25</v>
       </c>
-      <c r="J57" s="15">
+      <c r="J57" s="14">
         <v>31</v>
       </c>
-      <c r="K57" s="21"/>
-      <c r="L57" s="22"/>
-      <c r="M57" s="23"/>
+      <c r="K57" s="17"/>
+      <c r="M57" s="18"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
@@ -4386,12 +5546,11 @@
       <c r="I58" s="9">
         <v>17</v>
       </c>
-      <c r="J58" s="15">
+      <c r="J58" s="14">
         <v>27</v>
       </c>
-      <c r="K58" s="21"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="23"/>
+      <c r="K58" s="17"/>
+      <c r="M58" s="18"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
@@ -4421,12 +5580,11 @@
       <c r="I59" s="9">
         <v>0</v>
       </c>
-      <c r="J59" s="15">
+      <c r="J59" s="14">
         <v>0</v>
       </c>
-      <c r="K59" s="21"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="23"/>
+      <c r="K59" s="17"/>
+      <c r="M59" s="18"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
@@ -4456,12 +5614,11 @@
       <c r="I60" s="9">
         <v>22</v>
       </c>
-      <c r="J60" s="15">
+      <c r="J60" s="14">
         <v>32</v>
       </c>
-      <c r="K60" s="21"/>
-      <c r="L60" s="22"/>
-      <c r="M60" s="23"/>
+      <c r="K60" s="17"/>
+      <c r="M60" s="18"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
@@ -4491,12 +5648,11 @@
       <c r="I61" s="9">
         <v>20</v>
       </c>
-      <c r="J61" s="15">
+      <c r="J61" s="14">
         <v>26</v>
       </c>
-      <c r="K61" s="21"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="23"/>
+      <c r="K61" s="17"/>
+      <c r="M61" s="18"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
@@ -4526,12 +5682,11 @@
       <c r="I62" s="9">
         <v>14</v>
       </c>
-      <c r="J62" s="15">
+      <c r="J62" s="14">
         <v>29</v>
       </c>
-      <c r="K62" s="21"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="23"/>
+      <c r="K62" s="17"/>
+      <c r="M62" s="18"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
@@ -4561,12 +5716,11 @@
       <c r="I63" s="9">
         <v>18</v>
       </c>
-      <c r="J63" s="15">
+      <c r="J63" s="14">
         <v>32</v>
       </c>
-      <c r="K63" s="21"/>
-      <c r="L63" s="22"/>
-      <c r="M63" s="23"/>
+      <c r="K63" s="17"/>
+      <c r="M63" s="18"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
@@ -4596,12 +5750,11 @@
       <c r="I64" s="9">
         <v>26</v>
       </c>
-      <c r="J64" s="15">
+      <c r="J64" s="14">
         <v>38</v>
       </c>
-      <c r="K64" s="21"/>
-      <c r="L64" s="22"/>
-      <c r="M64" s="23"/>
+      <c r="K64" s="17"/>
+      <c r="M64" s="18"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
@@ -4631,12 +5784,11 @@
       <c r="I65" s="9">
         <v>23</v>
       </c>
-      <c r="J65" s="15">
+      <c r="J65" s="14">
         <v>29</v>
       </c>
-      <c r="K65" s="21"/>
-      <c r="L65" s="22"/>
-      <c r="M65" s="23"/>
+      <c r="K65" s="17"/>
+      <c r="M65" s="18"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
@@ -4666,12 +5818,11 @@
       <c r="I66" s="9">
         <v>28</v>
       </c>
-      <c r="J66" s="15">
+      <c r="J66" s="14">
         <v>40</v>
       </c>
-      <c r="K66" s="21"/>
-      <c r="L66" s="22"/>
-      <c r="M66" s="23"/>
+      <c r="K66" s="17"/>
+      <c r="M66" s="18"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
@@ -4701,12 +5852,11 @@
       <c r="I67" s="9">
         <v>21</v>
       </c>
-      <c r="J67" s="15">
+      <c r="J67" s="14">
         <v>29</v>
       </c>
-      <c r="K67" s="21"/>
-      <c r="L67" s="22"/>
-      <c r="M67" s="23"/>
+      <c r="K67" s="17"/>
+      <c r="M67" s="18"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
@@ -4736,12 +5886,11 @@
       <c r="I68" s="9">
         <v>28</v>
       </c>
-      <c r="J68" s="15">
+      <c r="J68" s="14">
         <v>34</v>
       </c>
-      <c r="K68" s="21"/>
-      <c r="L68" s="22"/>
-      <c r="M68" s="23"/>
+      <c r="K68" s="17"/>
+      <c r="M68" s="18"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
@@ -4771,12 +5920,11 @@
       <c r="I69" s="9">
         <v>30</v>
       </c>
-      <c r="J69" s="15">
+      <c r="J69" s="14">
         <v>35</v>
       </c>
-      <c r="K69" s="21"/>
-      <c r="L69" s="22"/>
-      <c r="M69" s="23"/>
+      <c r="K69" s="17"/>
+      <c r="M69" s="18"/>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
@@ -4806,12 +5954,11 @@
       <c r="I70" s="9">
         <v>37</v>
       </c>
-      <c r="J70" s="15">
+      <c r="J70" s="14">
         <v>37</v>
       </c>
-      <c r="K70" s="21"/>
-      <c r="L70" s="22"/>
-      <c r="M70" s="23"/>
+      <c r="K70" s="17"/>
+      <c r="M70" s="18"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
@@ -4841,12 +5988,11 @@
       <c r="I71" s="9">
         <v>24</v>
       </c>
-      <c r="J71" s="15">
+      <c r="J71" s="14">
         <v>38</v>
       </c>
-      <c r="K71" s="21"/>
-      <c r="L71" s="22"/>
-      <c r="M71" s="23"/>
+      <c r="K71" s="17"/>
+      <c r="M71" s="18"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
@@ -4876,12 +6022,11 @@
       <c r="I72" s="9">
         <v>24</v>
       </c>
-      <c r="J72" s="15">
+      <c r="J72" s="14">
         <v>34</v>
       </c>
-      <c r="K72" s="21"/>
-      <c r="L72" s="22"/>
-      <c r="M72" s="23"/>
+      <c r="K72" s="17"/>
+      <c r="M72" s="18"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
@@ -4911,12 +6056,11 @@
       <c r="I73" s="9">
         <v>26</v>
       </c>
-      <c r="J73" s="15">
+      <c r="J73" s="14">
         <v>30</v>
       </c>
-      <c r="K73" s="21"/>
-      <c r="L73" s="22"/>
-      <c r="M73" s="23"/>
+      <c r="K73" s="17"/>
+      <c r="M73" s="18"/>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
@@ -4946,12 +6090,11 @@
       <c r="I74" s="9">
         <v>20</v>
       </c>
-      <c r="J74" s="15">
+      <c r="J74" s="14">
         <v>32</v>
       </c>
-      <c r="K74" s="21"/>
-      <c r="L74" s="22"/>
-      <c r="M74" s="23"/>
+      <c r="K74" s="17"/>
+      <c r="M74" s="18"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
@@ -4981,12 +6124,11 @@
       <c r="I75" s="9">
         <v>26</v>
       </c>
-      <c r="J75" s="15">
+      <c r="J75" s="14">
         <v>34</v>
       </c>
-      <c r="K75" s="21"/>
-      <c r="L75" s="22"/>
-      <c r="M75" s="23"/>
+      <c r="K75" s="17"/>
+      <c r="M75" s="18"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
@@ -5016,12 +6158,11 @@
       <c r="I76" s="9">
         <v>0</v>
       </c>
-      <c r="J76" s="15">
+      <c r="J76" s="14">
         <v>0</v>
       </c>
-      <c r="K76" s="21"/>
-      <c r="L76" s="22"/>
-      <c r="M76" s="23"/>
+      <c r="K76" s="17"/>
+      <c r="M76" s="18"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
@@ -5051,12 +6192,11 @@
       <c r="I77" s="9">
         <v>19</v>
       </c>
-      <c r="J77" s="15">
+      <c r="J77" s="14">
         <v>24</v>
       </c>
-      <c r="K77" s="21"/>
-      <c r="L77" s="22"/>
-      <c r="M77" s="23"/>
+      <c r="K77" s="17"/>
+      <c r="M77" s="18"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
@@ -5086,12 +6226,11 @@
       <c r="I78" s="9">
         <v>29</v>
       </c>
-      <c r="J78" s="15">
+      <c r="J78" s="14">
         <v>37</v>
       </c>
-      <c r="K78" s="21"/>
-      <c r="L78" s="22"/>
-      <c r="M78" s="23"/>
+      <c r="K78" s="17"/>
+      <c r="M78" s="18"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
@@ -5121,47 +6260,1112 @@
       <c r="I79" s="9">
         <v>28</v>
       </c>
-      <c r="J79" s="15">
+      <c r="J79" s="14">
         <v>33</v>
       </c>
-      <c r="K79" s="21"/>
-      <c r="L79" s="22"/>
-      <c r="M79" s="23"/>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="7">
-        <v>1101</v>
-      </c>
-      <c r="B80" s="13" t="s">
-        <v>13</v>
+      <c r="K79" s="17"/>
+      <c r="M79" s="18"/>
+    </row>
+    <row r="80" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A80" s="6">
+        <v>1201</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>259</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D80" s="8">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="E80" s="10"/>
-      <c r="F80" s="10">
+      <c r="F80" s="38">
+        <v>33</v>
+      </c>
+      <c r="G80" s="44">
+        <v>23</v>
+      </c>
+      <c r="H80" s="10"/>
+      <c r="I80" s="46"/>
+      <c r="J80" s="16"/>
+      <c r="K80" s="44">
+        <v>24</v>
+      </c>
+      <c r="L80" s="44">
+        <v>30</v>
+      </c>
+      <c r="M80" s="44">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" s="47">
+        <v>1202</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D81" s="8">
+        <v>200</v>
+      </c>
+      <c r="E81" s="7"/>
+      <c r="F81" s="39">
+        <v>36</v>
+      </c>
+      <c r="G81" s="39">
+        <v>25</v>
+      </c>
+      <c r="H81" s="7"/>
+      <c r="K81" s="39">
+        <v>30</v>
+      </c>
+      <c r="L81" s="39">
+        <v>26</v>
+      </c>
+      <c r="M81" s="39">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A82" s="6">
+        <v>1203</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D82" s="8">
+        <v>200</v>
+      </c>
+      <c r="E82" s="7"/>
+      <c r="F82" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="G82" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="H82" s="7"/>
+      <c r="K82" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="L82" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="M82" s="43" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="47">
+        <v>1204</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D83" s="8">
+        <v>200</v>
+      </c>
+      <c r="E83" s="7"/>
+      <c r="F83" s="41">
+        <v>16</v>
+      </c>
+      <c r="G83" s="39">
+        <v>17</v>
+      </c>
+      <c r="H83" s="7"/>
+      <c r="K83" s="39">
+        <v>8</v>
+      </c>
+      <c r="L83" s="39">
+        <v>6</v>
+      </c>
+      <c r="M83" s="42">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A84" s="6">
+        <v>1205</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D84" s="8">
+        <v>200</v>
+      </c>
+      <c r="E84" s="7"/>
+      <c r="F84" s="38">
+        <v>31</v>
+      </c>
+      <c r="G84" s="39">
+        <v>24</v>
+      </c>
+      <c r="H84" s="7"/>
+      <c r="K84" s="39">
+        <v>21</v>
+      </c>
+      <c r="L84" s="39">
+        <v>10</v>
+      </c>
+      <c r="M84" s="42">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A85" s="47">
+        <v>1206</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D85" s="8">
+        <v>200</v>
+      </c>
+      <c r="E85" s="7"/>
+      <c r="F85" s="38">
+        <v>34</v>
+      </c>
+      <c r="G85" s="39">
+        <v>35</v>
+      </c>
+      <c r="H85" s="7"/>
+      <c r="K85" s="39">
+        <v>22</v>
+      </c>
+      <c r="L85" s="39">
+        <v>18</v>
+      </c>
+      <c r="M85" s="42">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>1207</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D86" s="8">
+        <v>200</v>
+      </c>
+      <c r="E86" s="7"/>
+      <c r="F86" s="41">
+        <v>26</v>
+      </c>
+      <c r="G86" s="39">
+        <v>15</v>
+      </c>
+      <c r="H86" s="7"/>
+      <c r="K86" s="39">
+        <v>27</v>
+      </c>
+      <c r="L86" s="39">
+        <v>15</v>
+      </c>
+      <c r="M86" s="42">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="47">
+        <v>1208</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D87" s="8">
+        <v>200</v>
+      </c>
+      <c r="E87" s="7"/>
+      <c r="F87" s="42">
+        <v>34</v>
+      </c>
+      <c r="G87" s="39">
+        <v>24</v>
+      </c>
+      <c r="H87" s="7"/>
+      <c r="K87" s="39">
+        <v>38</v>
+      </c>
+      <c r="L87" s="39">
+        <v>30</v>
+      </c>
+      <c r="M87" s="39">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A88" s="6">
+        <v>1209</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D88" s="8">
+        <v>200</v>
+      </c>
+      <c r="E88" s="7"/>
+      <c r="F88" s="38">
+        <v>30</v>
+      </c>
+      <c r="G88" s="39">
+        <v>24</v>
+      </c>
+      <c r="H88" s="7"/>
+      <c r="K88" s="39">
         <v>20</v>
       </c>
-      <c r="G80" s="10">
+      <c r="L88" s="39">
+        <v>19</v>
+      </c>
+      <c r="M88" s="42">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="47">
+        <v>1210</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D89" s="8">
+        <v>200</v>
+      </c>
+      <c r="E89" s="7"/>
+      <c r="F89" s="41">
+        <v>39</v>
+      </c>
+      <c r="G89" s="39">
+        <v>31</v>
+      </c>
+      <c r="H89" s="7"/>
+      <c r="K89" s="39">
+        <v>33</v>
+      </c>
+      <c r="L89" s="39">
+        <v>30</v>
+      </c>
+      <c r="M89" s="42">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A90" s="6">
+        <v>1211</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D90" s="8">
+        <v>200</v>
+      </c>
+      <c r="E90" s="7"/>
+      <c r="F90" s="38">
+        <v>31</v>
+      </c>
+      <c r="G90" s="39">
+        <v>17</v>
+      </c>
+      <c r="H90" s="7"/>
+      <c r="K90" s="39">
+        <v>19</v>
+      </c>
+      <c r="L90" s="39">
+        <v>10</v>
+      </c>
+      <c r="M90" s="42">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A91" s="47">
+        <v>1212</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D91" s="8">
+        <v>200</v>
+      </c>
+      <c r="E91" s="7"/>
+      <c r="F91" s="38">
+        <v>34</v>
+      </c>
+      <c r="G91" s="39">
+        <v>27</v>
+      </c>
+      <c r="H91" s="7"/>
+      <c r="K91" s="39">
+        <v>34</v>
+      </c>
+      <c r="L91" s="39">
+        <v>24</v>
+      </c>
+      <c r="M91" s="42">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A92" s="47">
+        <v>1213</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D92" s="8">
+        <v>200</v>
+      </c>
+      <c r="E92" s="7"/>
+      <c r="F92" s="38">
+        <v>36</v>
+      </c>
+      <c r="G92" s="39">
+        <v>34</v>
+      </c>
+      <c r="H92" s="7"/>
+      <c r="K92" s="39">
+        <v>38</v>
+      </c>
+      <c r="L92" s="39">
+        <v>28</v>
+      </c>
+      <c r="M92" s="42">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A93" s="6">
+        <v>1214</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D93" s="8">
+        <v>200</v>
+      </c>
+      <c r="E93" s="7"/>
+      <c r="F93" s="38">
+        <v>34</v>
+      </c>
+      <c r="G93" s="39">
+        <v>31</v>
+      </c>
+      <c r="H93" s="7"/>
+      <c r="K93" s="39">
         <v>20</v>
       </c>
-      <c r="H80" s="10">
+      <c r="L93" s="39">
+        <v>14</v>
+      </c>
+      <c r="M93" s="42">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A94" s="6">
+        <v>1215</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D94" s="8">
+        <v>200</v>
+      </c>
+      <c r="E94" s="7"/>
+      <c r="F94" s="38">
+        <v>37</v>
+      </c>
+      <c r="G94" s="39">
+        <v>25</v>
+      </c>
+      <c r="H94" s="7"/>
+      <c r="K94" s="39">
+        <v>28</v>
+      </c>
+      <c r="L94" s="39">
+        <v>15</v>
+      </c>
+      <c r="M94" s="42">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A95" s="47">
+        <v>1216</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" s="8">
+        <v>200</v>
+      </c>
+      <c r="E95" s="7"/>
+      <c r="F95" s="38">
+        <v>31</v>
+      </c>
+      <c r="G95" s="39">
+        <v>24</v>
+      </c>
+      <c r="H95" s="7"/>
+      <c r="K95" s="39">
+        <v>25</v>
+      </c>
+      <c r="L95" s="39">
+        <v>14</v>
+      </c>
+      <c r="M95" s="42">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>1217</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D96" s="8">
+        <v>200</v>
+      </c>
+      <c r="E96" s="7"/>
+      <c r="F96" s="42">
+        <v>28</v>
+      </c>
+      <c r="G96" s="39">
+        <v>15</v>
+      </c>
+      <c r="H96" s="7"/>
+      <c r="K96" s="39">
+        <v>18</v>
+      </c>
+      <c r="L96" s="39">
+        <v>8</v>
+      </c>
+      <c r="M96" s="39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="47">
+        <v>1218</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D97" s="8">
+        <v>200</v>
+      </c>
+      <c r="E97" s="7"/>
+      <c r="F97" s="42">
+        <v>27</v>
+      </c>
+      <c r="G97" s="39">
+        <v>13</v>
+      </c>
+      <c r="H97" s="7"/>
+      <c r="K97" s="39">
+        <v>32</v>
+      </c>
+      <c r="L97" s="39">
+        <v>17</v>
+      </c>
+      <c r="M97" s="39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>1219</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D98" s="8">
+        <v>200</v>
+      </c>
+      <c r="E98" s="7"/>
+      <c r="F98" s="42">
+        <v>29</v>
+      </c>
+      <c r="G98" s="39">
+        <v>37</v>
+      </c>
+      <c r="H98" s="7"/>
+      <c r="K98" s="39">
+        <v>35</v>
+      </c>
+      <c r="L98" s="39">
+        <v>21</v>
+      </c>
+      <c r="M98" s="39">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="47">
+        <v>1220</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D99" s="8">
+        <v>200</v>
+      </c>
+      <c r="E99" s="7"/>
+      <c r="F99" s="42">
+        <v>25</v>
+      </c>
+      <c r="G99" s="39">
+        <v>7</v>
+      </c>
+      <c r="H99" s="7"/>
+      <c r="K99" s="39">
+        <v>19</v>
+      </c>
+      <c r="L99" s="39">
+        <v>11</v>
+      </c>
+      <c r="M99" s="39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>1221</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D100" s="8">
+        <v>200</v>
+      </c>
+      <c r="E100" s="7"/>
+      <c r="F100" s="42">
+        <v>32</v>
+      </c>
+      <c r="G100" s="39">
+        <v>21</v>
+      </c>
+      <c r="H100" s="7"/>
+      <c r="K100" s="39">
+        <v>25</v>
+      </c>
+      <c r="L100" s="39">
+        <v>20</v>
+      </c>
+      <c r="M100" s="39">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="47">
+        <v>1222</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D101" s="8">
+        <v>200</v>
+      </c>
+      <c r="E101" s="7"/>
+      <c r="F101" s="42">
+        <v>28</v>
+      </c>
+      <c r="G101" s="39">
+        <v>16</v>
+      </c>
+      <c r="H101" s="7"/>
+      <c r="K101" s="39">
+        <v>31</v>
+      </c>
+      <c r="L101" s="39">
+        <v>14</v>
+      </c>
+      <c r="M101" s="39">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>1223</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D102" s="8">
+        <v>200</v>
+      </c>
+      <c r="E102" s="7"/>
+      <c r="F102" s="39">
+        <v>35</v>
+      </c>
+      <c r="G102" s="39">
+        <v>37</v>
+      </c>
+      <c r="H102" s="39">
+        <v>35</v>
+      </c>
+      <c r="K102" s="39">
+        <v>32</v>
+      </c>
+      <c r="L102" s="39">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="47">
+        <v>1224</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D103" s="8">
+        <v>200</v>
+      </c>
+      <c r="E103" s="7"/>
+      <c r="F103" s="42">
+        <v>33</v>
+      </c>
+      <c r="G103" s="39">
         <v>30</v>
       </c>
-      <c r="I80" s="10"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="24">
+      <c r="H103" s="39">
+        <v>30</v>
+      </c>
+      <c r="K103" s="39">
+        <v>32</v>
+      </c>
+      <c r="L103" s="39">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>1225</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D104" s="8">
+        <v>200</v>
+      </c>
+      <c r="E104" s="7"/>
+      <c r="F104" s="42">
+        <v>34</v>
+      </c>
+      <c r="G104" s="39">
+        <v>26</v>
+      </c>
+      <c r="H104" s="39">
+        <v>34</v>
+      </c>
+      <c r="K104" s="39">
+        <v>32</v>
+      </c>
+      <c r="L104" s="39">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="47">
+        <v>1226</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D105" s="8">
+        <v>200</v>
+      </c>
+      <c r="E105" s="7"/>
+      <c r="F105" s="42">
+        <v>30</v>
+      </c>
+      <c r="G105" s="39">
+        <v>23</v>
+      </c>
+      <c r="H105" s="39">
+        <v>25</v>
+      </c>
+      <c r="K105" s="39">
+        <v>21</v>
+      </c>
+      <c r="L105" s="39">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>1227</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D106" s="8">
+        <v>200</v>
+      </c>
+      <c r="E106" s="7"/>
+      <c r="F106" s="42">
+        <v>37</v>
+      </c>
+      <c r="G106" s="39">
+        <v>25</v>
+      </c>
+      <c r="H106" s="39">
+        <v>30</v>
+      </c>
+      <c r="K106" s="39">
+        <v>32</v>
+      </c>
+      <c r="L106" s="39">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="47">
+        <v>1228</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D107" s="8">
+        <v>200</v>
+      </c>
+      <c r="E107" s="7"/>
+      <c r="F107" s="42">
+        <v>36</v>
+      </c>
+      <c r="G107" s="39">
+        <v>34</v>
+      </c>
+      <c r="H107" s="39">
+        <v>30</v>
+      </c>
+      <c r="K107" s="39">
+        <v>33</v>
+      </c>
+      <c r="L107" s="39">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>1229</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D108" s="8">
+        <v>200</v>
+      </c>
+      <c r="E108" s="7"/>
+      <c r="F108" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="G108" s="39">
+        <v>24</v>
+      </c>
+      <c r="H108" s="39">
+        <v>25</v>
+      </c>
+      <c r="K108" s="39">
+        <v>26</v>
+      </c>
+      <c r="L108" s="45" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="47">
+        <v>1230</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D109" s="8">
+        <v>200</v>
+      </c>
+      <c r="E109" s="7"/>
+      <c r="F109" s="42">
+        <v>37</v>
+      </c>
+      <c r="G109" s="39">
+        <v>22</v>
+      </c>
+      <c r="H109" s="39">
+        <v>32</v>
+      </c>
+      <c r="K109" s="39">
+        <v>23</v>
+      </c>
+      <c r="L109" s="39">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>1231</v>
+      </c>
+      <c r="B110" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D110" s="8">
+        <v>200</v>
+      </c>
+      <c r="E110" s="7"/>
+      <c r="F110" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="G110" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="H110" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="K110" s="39" t="s">
+        <v>263</v>
+      </c>
+      <c r="L110" s="45" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="47">
+        <v>1232</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D111" s="8">
+        <v>200</v>
+      </c>
+      <c r="E111" s="7"/>
+      <c r="F111" s="42">
+        <v>36</v>
+      </c>
+      <c r="G111" s="39">
+        <v>32</v>
+      </c>
+      <c r="H111" s="39">
+        <v>32</v>
+      </c>
+      <c r="K111" s="39">
+        <v>34</v>
+      </c>
+      <c r="L111" s="39">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>1233</v>
+      </c>
+      <c r="B112" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D112" s="8">
+        <v>200</v>
+      </c>
+      <c r="E112" s="7"/>
+      <c r="F112" s="42">
+        <v>35</v>
+      </c>
+      <c r="G112" s="39">
+        <v>27</v>
+      </c>
+      <c r="H112" s="39">
+        <v>34</v>
+      </c>
+      <c r="K112" s="39">
+        <v>31</v>
+      </c>
+      <c r="L112" s="39">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="47">
+        <v>1234</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D113" s="8">
+        <v>200</v>
+      </c>
+      <c r="E113" s="7"/>
+      <c r="F113" s="42">
+        <v>33</v>
+      </c>
+      <c r="G113" s="39">
+        <v>24</v>
+      </c>
+      <c r="H113" s="39">
+        <v>31</v>
+      </c>
+      <c r="K113" s="39">
         <v>20</v>
       </c>
-      <c r="L80" s="25">
-        <v>12</v>
-      </c>
-      <c r="M80" s="26"/>
+      <c r="L113" s="39">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F81 F87">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F96:F113">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G81:G95">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G96:G113">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K81">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K82:K113">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L81 L87">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L82:L113">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M81 M87">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M82:M101">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H102:H113">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A2E9BF-3622-4B56-AA70-AFF7F45F89D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C4AFF0-CEC3-44D9-B5F9-C110E482BA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="291">
   <si>
     <t>Roll_No</t>
   </si>
@@ -829,6 +829,87 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>30.11.2009</t>
+  </si>
+  <si>
+    <t>10.09.2010</t>
+  </si>
+  <si>
+    <t>22.10.2008</t>
+  </si>
+  <si>
+    <t>10.01.2009</t>
+  </si>
+  <si>
+    <t>22.09.2009</t>
+  </si>
+  <si>
+    <t>27.06.2009</t>
+  </si>
+  <si>
+    <t>16.12.2009</t>
+  </si>
+  <si>
+    <t>06.02.2010</t>
+  </si>
+  <si>
+    <t>10.10.2008</t>
+  </si>
+  <si>
+    <t>03.05.2010</t>
+  </si>
+  <si>
+    <t>15.02.2010</t>
+  </si>
+  <si>
+    <t>15.06.2008</t>
+  </si>
+  <si>
+    <t>26.08.2009</t>
+  </si>
+  <si>
+    <t>04.02.2009</t>
+  </si>
+  <si>
+    <t>27.11.2009</t>
+  </si>
+  <si>
+    <t>25.09.2009</t>
+  </si>
+  <si>
+    <t>05.12.2009</t>
+  </si>
+  <si>
+    <t>23.05.2010</t>
+  </si>
+  <si>
+    <t>15.04.2010</t>
+  </si>
+  <si>
+    <t>22.10.2009</t>
+  </si>
+  <si>
+    <t>17.03.2010</t>
+  </si>
+  <si>
+    <t>08.06.2009</t>
+  </si>
+  <si>
+    <t>09.07.2009</t>
+  </si>
+  <si>
+    <t>20.07.2009</t>
+  </si>
+  <si>
+    <t>16.03.2009</t>
+  </si>
+  <si>
+    <t>21.12.2009</t>
+  </si>
+  <si>
+    <t>10.01.2010</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1150,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1152,15 +1233,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1200,6 +1272,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -1614,7 +1687,7 @@
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2668,8 +2741,8 @@
       <c r="C41" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D41" s="32">
-        <v>40147</v>
+      <c r="D41" s="45" t="s">
+        <v>264</v>
       </c>
       <c r="E41" s="27">
         <v>629725429548</v>
@@ -2694,13 +2767,13 @@
       <c r="C42" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D42" s="32">
-        <v>40431</v>
+      <c r="D42" s="45" t="s">
+        <v>265</v>
       </c>
       <c r="E42" s="27">
         <v>868784631083</v>
       </c>
-      <c r="F42" s="35">
+      <c r="F42" s="32">
         <v>9624104337</v>
       </c>
       <c r="G42" s="12" t="s">
@@ -2720,13 +2793,13 @@
       <c r="C43" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D43" s="32">
-        <v>39743</v>
+      <c r="D43" s="45" t="s">
+        <v>266</v>
       </c>
       <c r="E43" s="27">
         <v>861502383654</v>
       </c>
-      <c r="F43" s="35">
+      <c r="F43" s="32">
         <v>8141169136</v>
       </c>
       <c r="G43" s="12" t="s">
@@ -2746,8 +2819,8 @@
       <c r="C44" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D44" s="32">
-        <v>39823</v>
+      <c r="D44" s="45" t="s">
+        <v>267</v>
       </c>
       <c r="E44" s="27">
         <v>523235907356</v>
@@ -2772,13 +2845,13 @@
       <c r="C45" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D45" s="32">
-        <v>40078</v>
+      <c r="D45" s="45" t="s">
+        <v>268</v>
       </c>
       <c r="E45" s="27">
         <v>892372104796</v>
       </c>
-      <c r="F45" s="35">
+      <c r="F45" s="32">
         <v>9265841928</v>
       </c>
       <c r="G45" s="12" t="s">
@@ -2798,13 +2871,13 @@
       <c r="C46" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D46" s="32">
-        <v>39991</v>
+      <c r="D46" s="45" t="s">
+        <v>269</v>
       </c>
       <c r="E46" s="27">
         <v>412140699697</v>
       </c>
-      <c r="F46" s="35">
+      <c r="F46" s="32">
         <v>9725282548</v>
       </c>
       <c r="G46" s="12" t="s">
@@ -2824,13 +2897,13 @@
       <c r="C47" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="32">
-        <v>40163</v>
+      <c r="D47" s="45" t="s">
+        <v>270</v>
       </c>
       <c r="E47" s="27">
         <v>240156702958</v>
       </c>
-      <c r="F47" s="35">
+      <c r="F47" s="32">
         <v>9687875011</v>
       </c>
       <c r="G47" s="12" t="s">
@@ -2850,13 +2923,13 @@
       <c r="C48" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D48" s="32">
-        <v>40215</v>
+      <c r="D48" s="45" t="s">
+        <v>271</v>
       </c>
       <c r="E48" s="27">
         <v>279595726744</v>
       </c>
-      <c r="F48" s="35">
+      <c r="F48" s="32">
         <v>9879537857</v>
       </c>
       <c r="G48" s="12" t="s">
@@ -2876,8 +2949,8 @@
       <c r="C49" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D49" s="32">
-        <v>39731</v>
+      <c r="D49" s="45" t="s">
+        <v>272</v>
       </c>
       <c r="E49" s="27">
         <v>916336765264</v>
@@ -2902,13 +2975,13 @@
       <c r="C50" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D50" s="32">
-        <v>40301</v>
+      <c r="D50" s="45" t="s">
+        <v>273</v>
       </c>
       <c r="E50" s="27">
         <v>705953487400</v>
       </c>
-      <c r="F50" s="35">
+      <c r="F50" s="32">
         <v>9687111646</v>
       </c>
       <c r="G50" s="12" t="s">
@@ -2928,13 +3001,13 @@
       <c r="C51" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D51" s="32">
-        <v>40224</v>
+      <c r="D51" s="45" t="s">
+        <v>274</v>
       </c>
       <c r="E51" s="27">
         <v>764006954215</v>
       </c>
-      <c r="F51" s="35">
+      <c r="F51" s="32">
         <v>8200730410</v>
       </c>
       <c r="G51" s="12" t="s">
@@ -2954,8 +3027,8 @@
       <c r="C52" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D52" s="32">
-        <v>39614</v>
+      <c r="D52" s="45" t="s">
+        <v>275</v>
       </c>
       <c r="E52" s="27">
         <v>329596170047</v>
@@ -2980,13 +3053,13 @@
       <c r="C53" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="D53" s="34" t="s">
+      <c r="D53" s="45" t="s">
         <v>254</v>
       </c>
       <c r="E53" s="28">
         <v>520048808079</v>
       </c>
-      <c r="F53" s="36">
+      <c r="F53" s="33">
         <v>991338636</v>
       </c>
       <c r="G53" s="12" t="s">
@@ -3006,8 +3079,8 @@
       <c r="C54" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D54" s="32">
-        <v>40051</v>
+      <c r="D54" s="45" t="s">
+        <v>276</v>
       </c>
       <c r="E54" s="27">
         <v>632504887936</v>
@@ -3032,8 +3105,8 @@
       <c r="C55" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D55" s="32">
-        <v>39848</v>
+      <c r="D55" s="45" t="s">
+        <v>277</v>
       </c>
       <c r="E55" s="27">
         <v>924194629769</v>
@@ -3058,8 +3131,8 @@
       <c r="C56" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D56" s="32">
-        <v>40144</v>
+      <c r="D56" s="45" t="s">
+        <v>278</v>
       </c>
       <c r="E56" s="27">
         <v>336666374564</v>
@@ -3084,7 +3157,7 @@
       <c r="C57" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="D57" s="33" t="s">
+      <c r="D57" s="45" t="s">
         <v>255</v>
       </c>
       <c r="E57" s="29" t="s">
@@ -3110,8 +3183,8 @@
       <c r="C58" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="D58" s="33">
-        <v>40081</v>
+      <c r="D58" s="45" t="s">
+        <v>279</v>
       </c>
       <c r="E58" s="29" t="s">
         <v>249</v>
@@ -3136,8 +3209,8 @@
       <c r="C59" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="D59" s="33">
-        <v>40152</v>
+      <c r="D59" s="45" t="s">
+        <v>280</v>
       </c>
       <c r="E59" s="29" t="s">
         <v>250</v>
@@ -3162,8 +3235,8 @@
       <c r="C60" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="D60" s="33">
-        <v>40321</v>
+      <c r="D60" s="45" t="s">
+        <v>281</v>
       </c>
       <c r="E60" s="29" t="s">
         <v>251</v>
@@ -3188,7 +3261,7 @@
       <c r="C61" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="D61" s="33" t="s">
+      <c r="D61" s="45" t="s">
         <v>256</v>
       </c>
       <c r="E61" s="29" t="s">
@@ -3214,13 +3287,13 @@
       <c r="C62" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="D62" s="33" t="s">
+      <c r="D62" s="45" t="s">
         <v>257</v>
       </c>
       <c r="E62" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="F62" s="37">
+      <c r="F62" s="34">
         <v>6355764851</v>
       </c>
       <c r="G62" s="12" t="s">
@@ -3240,13 +3313,13 @@
       <c r="C63" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D63" s="32" t="s">
+      <c r="D63" s="45" t="s">
         <v>258</v>
       </c>
       <c r="E63" s="31">
         <v>588971485746</v>
       </c>
-      <c r="F63" s="35">
+      <c r="F63" s="32">
         <v>8156035767</v>
       </c>
       <c r="G63" s="12" t="s">
@@ -3266,13 +3339,13 @@
       <c r="C64" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="D64" s="33">
-        <v>40283</v>
+      <c r="D64" s="45" t="s">
+        <v>282</v>
       </c>
       <c r="E64" s="30">
         <v>863609916544</v>
       </c>
-      <c r="F64" s="37">
+      <c r="F64" s="34">
         <v>9925669837</v>
       </c>
       <c r="G64" s="12" t="s">
@@ -3292,13 +3365,13 @@
       <c r="C65" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D65" s="32">
-        <v>40301</v>
+      <c r="D65" s="45" t="s">
+        <v>273</v>
       </c>
       <c r="E65" s="27">
         <v>877868433283</v>
       </c>
-      <c r="F65" s="35">
+      <c r="F65" s="32">
         <v>9714374772</v>
       </c>
       <c r="G65" s="12" t="s">
@@ -3318,13 +3391,13 @@
       <c r="C66" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="D66" s="33">
-        <v>40108</v>
+      <c r="D66" s="45" t="s">
+        <v>283</v>
       </c>
       <c r="E66" s="30">
         <v>387760716924</v>
       </c>
-      <c r="F66" s="37">
+      <c r="F66" s="34">
         <v>9016525318</v>
       </c>
       <c r="G66" s="12" t="s">
@@ -3344,13 +3417,13 @@
       <c r="C67" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="D67" s="33">
-        <v>40254</v>
+      <c r="D67" s="45" t="s">
+        <v>284</v>
       </c>
       <c r="E67" s="30">
         <v>371214659024</v>
       </c>
-      <c r="F67" s="37">
+      <c r="F67" s="34">
         <v>9313281718</v>
       </c>
       <c r="G67" s="12" t="s">
@@ -3370,13 +3443,13 @@
       <c r="C68" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="D68" s="33">
-        <v>39972</v>
+      <c r="D68" s="45" t="s">
+        <v>285</v>
       </c>
       <c r="E68" s="30">
         <v>716050924500</v>
       </c>
-      <c r="F68" s="37">
+      <c r="F68" s="34">
         <v>9925251810</v>
       </c>
       <c r="G68" s="12" t="s">
@@ -3396,13 +3469,13 @@
       <c r="C69" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="D69" s="33">
-        <v>40003</v>
+      <c r="D69" s="45" t="s">
+        <v>286</v>
       </c>
       <c r="E69" s="30">
         <v>770629036161</v>
       </c>
-      <c r="F69" s="37">
+      <c r="F69" s="34">
         <v>9664941182</v>
       </c>
       <c r="G69" s="12" t="s">
@@ -3422,13 +3495,13 @@
       <c r="C70" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D70" s="32">
-        <v>40141</v>
+      <c r="D70" s="45" t="s">
+        <v>255</v>
       </c>
       <c r="E70" s="27">
         <v>646034972649</v>
       </c>
-      <c r="F70" s="35">
+      <c r="F70" s="32">
         <v>9979692514</v>
       </c>
       <c r="G70" s="12" t="s">
@@ -3448,13 +3521,13 @@
       <c r="C71" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D71" s="32">
-        <v>40014</v>
+      <c r="D71" s="45" t="s">
+        <v>287</v>
       </c>
       <c r="E71" s="27">
         <v>681716388949</v>
       </c>
-      <c r="F71" s="35">
+      <c r="F71" s="32">
         <v>9824446619</v>
       </c>
       <c r="G71" s="12" t="s">
@@ -3474,13 +3547,13 @@
       <c r="C72" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D72" s="32">
-        <v>39888</v>
+      <c r="D72" s="45" t="s">
+        <v>288</v>
       </c>
       <c r="E72" s="27">
         <v>680078961178</v>
       </c>
-      <c r="F72" s="35">
+      <c r="F72" s="32">
         <v>9016181529</v>
       </c>
       <c r="G72" s="12" t="s">
@@ -3500,13 +3573,13 @@
       <c r="C73" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D73" s="32">
-        <v>40168</v>
+      <c r="D73" s="45" t="s">
+        <v>289</v>
       </c>
       <c r="E73" s="27">
         <v>934647778164</v>
       </c>
-      <c r="F73" s="35">
+      <c r="F73" s="32">
         <v>9313203487</v>
       </c>
       <c r="G73" s="12" t="s">
@@ -3526,13 +3599,13 @@
       <c r="C74" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D74" s="32">
-        <v>40188</v>
+      <c r="D74" s="45" t="s">
+        <v>290</v>
       </c>
       <c r="E74" s="27">
         <v>743736078906</v>
       </c>
-      <c r="F74" s="35">
+      <c r="F74" s="32">
         <v>9879009201</v>
       </c>
       <c r="G74" s="12" t="s">
@@ -3567,7 +3640,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D043D23-75C9-4A79-B369-DB03044E1B80}">
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="22.28515625" customWidth="1"/>
@@ -6280,27 +6353,27 @@
         <v>200</v>
       </c>
       <c r="E80" s="10"/>
-      <c r="F80" s="38">
+      <c r="F80" s="35">
         <v>33</v>
       </c>
-      <c r="G80" s="44">
+      <c r="G80" s="41">
         <v>23</v>
       </c>
       <c r="H80" s="10"/>
-      <c r="I80" s="46"/>
+      <c r="I80" s="43"/>
       <c r="J80" s="16"/>
-      <c r="K80" s="44">
+      <c r="K80" s="41">
         <v>24</v>
       </c>
-      <c r="L80" s="44">
+      <c r="L80" s="41">
         <v>30</v>
       </c>
-      <c r="M80" s="44">
+      <c r="M80" s="41">
         <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="47">
+      <c r="A81" s="44">
         <v>1202</v>
       </c>
       <c r="B81" s="12" t="s">
@@ -6313,20 +6386,20 @@
         <v>200</v>
       </c>
       <c r="E81" s="7"/>
-      <c r="F81" s="39">
+      <c r="F81" s="36">
         <v>36</v>
       </c>
-      <c r="G81" s="39">
+      <c r="G81" s="36">
         <v>25</v>
       </c>
       <c r="H81" s="7"/>
-      <c r="K81" s="39">
+      <c r="K81" s="36">
         <v>30</v>
       </c>
-      <c r="L81" s="39">
+      <c r="L81" s="36">
         <v>26</v>
       </c>
-      <c r="M81" s="39">
+      <c r="M81" s="36">
         <v>19</v>
       </c>
     </row>
@@ -6344,25 +6417,25 @@
         <v>200</v>
       </c>
       <c r="E82" s="7"/>
-      <c r="F82" s="40" t="s">
+      <c r="F82" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="G82" s="45" t="s">
+      <c r="G82" s="42" t="s">
         <v>262</v>
       </c>
       <c r="H82" s="7"/>
-      <c r="K82" s="45" t="s">
+      <c r="K82" s="42" t="s">
         <v>262</v>
       </c>
-      <c r="L82" s="45" t="s">
+      <c r="L82" s="42" t="s">
         <v>262</v>
       </c>
-      <c r="M82" s="43" t="s">
+      <c r="M82" s="40" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="47">
+      <c r="A83" s="44">
         <v>1204</v>
       </c>
       <c r="B83" s="12" t="s">
@@ -6375,20 +6448,20 @@
         <v>200</v>
       </c>
       <c r="E83" s="7"/>
-      <c r="F83" s="41">
+      <c r="F83" s="38">
         <v>16</v>
       </c>
-      <c r="G83" s="39">
+      <c r="G83" s="36">
         <v>17</v>
       </c>
       <c r="H83" s="7"/>
-      <c r="K83" s="39">
+      <c r="K83" s="36">
         <v>8</v>
       </c>
-      <c r="L83" s="39">
+      <c r="L83" s="36">
         <v>6</v>
       </c>
-      <c r="M83" s="42">
+      <c r="M83" s="39">
         <v>19</v>
       </c>
     </row>
@@ -6406,25 +6479,25 @@
         <v>200</v>
       </c>
       <c r="E84" s="7"/>
-      <c r="F84" s="38">
+      <c r="F84" s="35">
         <v>31</v>
       </c>
-      <c r="G84" s="39">
+      <c r="G84" s="36">
         <v>24</v>
       </c>
       <c r="H84" s="7"/>
-      <c r="K84" s="39">
+      <c r="K84" s="36">
         <v>21</v>
       </c>
-      <c r="L84" s="39">
+      <c r="L84" s="36">
         <v>10</v>
       </c>
-      <c r="M84" s="42">
+      <c r="M84" s="39">
         <v>25</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A85" s="47">
+      <c r="A85" s="44">
         <v>1206</v>
       </c>
       <c r="B85" s="12" t="s">
@@ -6437,20 +6510,20 @@
         <v>200</v>
       </c>
       <c r="E85" s="7"/>
-      <c r="F85" s="38">
+      <c r="F85" s="35">
         <v>34</v>
       </c>
-      <c r="G85" s="39">
+      <c r="G85" s="36">
         <v>35</v>
       </c>
       <c r="H85" s="7"/>
-      <c r="K85" s="39">
+      <c r="K85" s="36">
         <v>22</v>
       </c>
-      <c r="L85" s="39">
-        <v>18</v>
-      </c>
-      <c r="M85" s="42">
+      <c r="L85" s="36">
+        <v>18</v>
+      </c>
+      <c r="M85" s="39">
         <v>26</v>
       </c>
     </row>
@@ -6468,25 +6541,25 @@
         <v>200</v>
       </c>
       <c r="E86" s="7"/>
-      <c r="F86" s="41">
+      <c r="F86" s="38">
         <v>26</v>
       </c>
-      <c r="G86" s="39">
+      <c r="G86" s="36">
         <v>15</v>
       </c>
       <c r="H86" s="7"/>
-      <c r="K86" s="39">
+      <c r="K86" s="36">
         <v>27</v>
       </c>
-      <c r="L86" s="39">
+      <c r="L86" s="36">
         <v>15</v>
       </c>
-      <c r="M86" s="42">
+      <c r="M86" s="39">
         <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="47">
+      <c r="A87" s="44">
         <v>1208</v>
       </c>
       <c r="B87" s="12" t="s">
@@ -6499,20 +6572,20 @@
         <v>200</v>
       </c>
       <c r="E87" s="7"/>
-      <c r="F87" s="42">
+      <c r="F87" s="39">
         <v>34</v>
       </c>
-      <c r="G87" s="39">
+      <c r="G87" s="36">
         <v>24</v>
       </c>
       <c r="H87" s="7"/>
-      <c r="K87" s="39">
+      <c r="K87" s="36">
         <v>38</v>
       </c>
-      <c r="L87" s="39">
+      <c r="L87" s="36">
         <v>30</v>
       </c>
-      <c r="M87" s="39">
+      <c r="M87" s="36">
         <v>25</v>
       </c>
     </row>
@@ -6530,25 +6603,25 @@
         <v>200</v>
       </c>
       <c r="E88" s="7"/>
-      <c r="F88" s="38">
+      <c r="F88" s="35">
         <v>30</v>
       </c>
-      <c r="G88" s="39">
+      <c r="G88" s="36">
         <v>24</v>
       </c>
       <c r="H88" s="7"/>
-      <c r="K88" s="39">
+      <c r="K88" s="36">
         <v>20</v>
       </c>
-      <c r="L88" s="39">
+      <c r="L88" s="36">
         <v>19</v>
       </c>
-      <c r="M88" s="42">
+      <c r="M88" s="39">
         <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="47">
+      <c r="A89" s="44">
         <v>1210</v>
       </c>
       <c r="B89" s="12" t="s">
@@ -6561,20 +6634,20 @@
         <v>200</v>
       </c>
       <c r="E89" s="7"/>
-      <c r="F89" s="41">
+      <c r="F89" s="38">
         <v>39</v>
       </c>
-      <c r="G89" s="39">
+      <c r="G89" s="36">
         <v>31</v>
       </c>
       <c r="H89" s="7"/>
-      <c r="K89" s="39">
+      <c r="K89" s="36">
         <v>33</v>
       </c>
-      <c r="L89" s="39">
+      <c r="L89" s="36">
         <v>30</v>
       </c>
-      <c r="M89" s="42">
+      <c r="M89" s="39">
         <v>28</v>
       </c>
     </row>
@@ -6592,25 +6665,25 @@
         <v>200</v>
       </c>
       <c r="E90" s="7"/>
-      <c r="F90" s="38">
+      <c r="F90" s="35">
         <v>31</v>
       </c>
-      <c r="G90" s="39">
+      <c r="G90" s="36">
         <v>17</v>
       </c>
       <c r="H90" s="7"/>
-      <c r="K90" s="39">
+      <c r="K90" s="36">
         <v>19</v>
       </c>
-      <c r="L90" s="39">
+      <c r="L90" s="36">
         <v>10</v>
       </c>
-      <c r="M90" s="42">
+      <c r="M90" s="39">
         <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A91" s="47">
+      <c r="A91" s="44">
         <v>1212</v>
       </c>
       <c r="B91" s="12" t="s">
@@ -6623,25 +6696,25 @@
         <v>200</v>
       </c>
       <c r="E91" s="7"/>
-      <c r="F91" s="38">
+      <c r="F91" s="35">
         <v>34</v>
       </c>
-      <c r="G91" s="39">
+      <c r="G91" s="36">
         <v>27</v>
       </c>
       <c r="H91" s="7"/>
-      <c r="K91" s="39">
+      <c r="K91" s="36">
         <v>34</v>
       </c>
-      <c r="L91" s="39">
+      <c r="L91" s="36">
         <v>24</v>
       </c>
-      <c r="M91" s="42">
+      <c r="M91" s="39">
         <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A92" s="47">
+      <c r="A92" s="44">
         <v>1213</v>
       </c>
       <c r="B92" s="12" t="s">
@@ -6654,20 +6727,20 @@
         <v>200</v>
       </c>
       <c r="E92" s="7"/>
-      <c r="F92" s="38">
+      <c r="F92" s="35">
         <v>36</v>
       </c>
-      <c r="G92" s="39">
+      <c r="G92" s="36">
         <v>34</v>
       </c>
       <c r="H92" s="7"/>
-      <c r="K92" s="39">
+      <c r="K92" s="36">
         <v>38</v>
       </c>
-      <c r="L92" s="39">
+      <c r="L92" s="36">
         <v>28</v>
       </c>
-      <c r="M92" s="42">
+      <c r="M92" s="39">
         <v>23</v>
       </c>
     </row>
@@ -6685,20 +6758,20 @@
         <v>200</v>
       </c>
       <c r="E93" s="7"/>
-      <c r="F93" s="38">
+      <c r="F93" s="35">
         <v>34</v>
       </c>
-      <c r="G93" s="39">
+      <c r="G93" s="36">
         <v>31</v>
       </c>
       <c r="H93" s="7"/>
-      <c r="K93" s="39">
+      <c r="K93" s="36">
         <v>20</v>
       </c>
-      <c r="L93" s="39">
+      <c r="L93" s="36">
         <v>14</v>
       </c>
-      <c r="M93" s="42">
+      <c r="M93" s="39">
         <v>18</v>
       </c>
     </row>
@@ -6716,25 +6789,25 @@
         <v>200</v>
       </c>
       <c r="E94" s="7"/>
-      <c r="F94" s="38">
+      <c r="F94" s="35">
         <v>37</v>
       </c>
-      <c r="G94" s="39">
+      <c r="G94" s="36">
         <v>25</v>
       </c>
       <c r="H94" s="7"/>
-      <c r="K94" s="39">
+      <c r="K94" s="36">
         <v>28</v>
       </c>
-      <c r="L94" s="39">
+      <c r="L94" s="36">
         <v>15</v>
       </c>
-      <c r="M94" s="42">
+      <c r="M94" s="39">
         <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A95" s="47">
+      <c r="A95" s="44">
         <v>1216</v>
       </c>
       <c r="B95" s="12" t="s">
@@ -6747,20 +6820,20 @@
         <v>200</v>
       </c>
       <c r="E95" s="7"/>
-      <c r="F95" s="38">
+      <c r="F95" s="35">
         <v>31</v>
       </c>
-      <c r="G95" s="39">
+      <c r="G95" s="36">
         <v>24</v>
       </c>
       <c r="H95" s="7"/>
-      <c r="K95" s="39">
+      <c r="K95" s="36">
         <v>25</v>
       </c>
-      <c r="L95" s="39">
+      <c r="L95" s="36">
         <v>14</v>
       </c>
-      <c r="M95" s="42">
+      <c r="M95" s="39">
         <v>24</v>
       </c>
     </row>
@@ -6778,25 +6851,25 @@
         <v>200</v>
       </c>
       <c r="E96" s="7"/>
-      <c r="F96" s="42">
+      <c r="F96" s="39">
         <v>28</v>
       </c>
-      <c r="G96" s="39">
+      <c r="G96" s="36">
         <v>15</v>
       </c>
       <c r="H96" s="7"/>
-      <c r="K96" s="39">
-        <v>18</v>
-      </c>
-      <c r="L96" s="39">
+      <c r="K96" s="36">
+        <v>18</v>
+      </c>
+      <c r="L96" s="36">
         <v>8</v>
       </c>
-      <c r="M96" s="39">
+      <c r="M96" s="36">
         <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="47">
+      <c r="A97" s="44">
         <v>1218</v>
       </c>
       <c r="B97" s="12" t="s">
@@ -6809,20 +6882,20 @@
         <v>200</v>
       </c>
       <c r="E97" s="7"/>
-      <c r="F97" s="42">
+      <c r="F97" s="39">
         <v>27</v>
       </c>
-      <c r="G97" s="39">
+      <c r="G97" s="36">
         <v>13</v>
       </c>
       <c r="H97" s="7"/>
-      <c r="K97" s="39">
+      <c r="K97" s="36">
         <v>32</v>
       </c>
-      <c r="L97" s="39">
+      <c r="L97" s="36">
         <v>17</v>
       </c>
-      <c r="M97" s="39">
+      <c r="M97" s="36">
         <v>10</v>
       </c>
     </row>
@@ -6840,25 +6913,25 @@
         <v>200</v>
       </c>
       <c r="E98" s="7"/>
-      <c r="F98" s="42">
+      <c r="F98" s="39">
         <v>29</v>
       </c>
-      <c r="G98" s="39">
+      <c r="G98" s="36">
         <v>37</v>
       </c>
       <c r="H98" s="7"/>
-      <c r="K98" s="39">
+      <c r="K98" s="36">
         <v>35</v>
       </c>
-      <c r="L98" s="39">
+      <c r="L98" s="36">
         <v>21</v>
       </c>
-      <c r="M98" s="39">
+      <c r="M98" s="36">
         <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="47">
+      <c r="A99" s="44">
         <v>1220</v>
       </c>
       <c r="B99" s="12" t="s">
@@ -6871,20 +6944,20 @@
         <v>200</v>
       </c>
       <c r="E99" s="7"/>
-      <c r="F99" s="42">
+      <c r="F99" s="39">
         <v>25</v>
       </c>
-      <c r="G99" s="39">
+      <c r="G99" s="36">
         <v>7</v>
       </c>
       <c r="H99" s="7"/>
-      <c r="K99" s="39">
+      <c r="K99" s="36">
         <v>19</v>
       </c>
-      <c r="L99" s="39">
+      <c r="L99" s="36">
         <v>11</v>
       </c>
-      <c r="M99" s="39">
+      <c r="M99" s="36">
         <v>10</v>
       </c>
     </row>
@@ -6902,25 +6975,25 @@
         <v>200</v>
       </c>
       <c r="E100" s="7"/>
-      <c r="F100" s="42">
+      <c r="F100" s="39">
         <v>32</v>
       </c>
-      <c r="G100" s="39">
+      <c r="G100" s="36">
         <v>21</v>
       </c>
       <c r="H100" s="7"/>
-      <c r="K100" s="39">
+      <c r="K100" s="36">
         <v>25</v>
       </c>
-      <c r="L100" s="39">
+      <c r="L100" s="36">
         <v>20</v>
       </c>
-      <c r="M100" s="39">
+      <c r="M100" s="36">
         <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="47">
+      <c r="A101" s="44">
         <v>1222</v>
       </c>
       <c r="B101" s="12" t="s">
@@ -6933,20 +7006,20 @@
         <v>200</v>
       </c>
       <c r="E101" s="7"/>
-      <c r="F101" s="42">
+      <c r="F101" s="39">
         <v>28</v>
       </c>
-      <c r="G101" s="39">
+      <c r="G101" s="36">
         <v>16</v>
       </c>
       <c r="H101" s="7"/>
-      <c r="K101" s="39">
+      <c r="K101" s="36">
         <v>31</v>
       </c>
-      <c r="L101" s="39">
+      <c r="L101" s="36">
         <v>14</v>
       </c>
-      <c r="M101" s="39">
+      <c r="M101" s="36">
         <v>17</v>
       </c>
     </row>
@@ -6964,24 +7037,24 @@
         <v>200</v>
       </c>
       <c r="E102" s="7"/>
-      <c r="F102" s="39">
+      <c r="F102" s="36">
         <v>35</v>
       </c>
-      <c r="G102" s="39">
+      <c r="G102" s="36">
         <v>37</v>
       </c>
-      <c r="H102" s="39">
+      <c r="H102" s="36">
         <v>35</v>
       </c>
-      <c r="K102" s="39">
+      <c r="K102" s="36">
         <v>32</v>
       </c>
-      <c r="L102" s="39">
+      <c r="L102" s="36">
         <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="47">
+      <c r="A103" s="44">
         <v>1224</v>
       </c>
       <c r="B103" s="12" t="s">
@@ -6994,19 +7067,19 @@
         <v>200</v>
       </c>
       <c r="E103" s="7"/>
-      <c r="F103" s="42">
+      <c r="F103" s="39">
         <v>33</v>
       </c>
-      <c r="G103" s="39">
+      <c r="G103" s="36">
         <v>30</v>
       </c>
-      <c r="H103" s="39">
+      <c r="H103" s="36">
         <v>30</v>
       </c>
-      <c r="K103" s="39">
+      <c r="K103" s="36">
         <v>32</v>
       </c>
-      <c r="L103" s="39">
+      <c r="L103" s="36">
         <v>25</v>
       </c>
     </row>
@@ -7024,24 +7097,24 @@
         <v>200</v>
       </c>
       <c r="E104" s="7"/>
-      <c r="F104" s="42">
+      <c r="F104" s="39">
         <v>34</v>
       </c>
-      <c r="G104" s="39">
+      <c r="G104" s="36">
         <v>26</v>
       </c>
-      <c r="H104" s="39">
+      <c r="H104" s="36">
         <v>34</v>
       </c>
-      <c r="K104" s="39">
+      <c r="K104" s="36">
         <v>32</v>
       </c>
-      <c r="L104" s="39">
+      <c r="L104" s="36">
         <v>31</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="47">
+      <c r="A105" s="44">
         <v>1226</v>
       </c>
       <c r="B105" s="12" t="s">
@@ -7054,19 +7127,19 @@
         <v>200</v>
       </c>
       <c r="E105" s="7"/>
-      <c r="F105" s="42">
+      <c r="F105" s="39">
         <v>30</v>
       </c>
-      <c r="G105" s="39">
+      <c r="G105" s="36">
         <v>23</v>
       </c>
-      <c r="H105" s="39">
+      <c r="H105" s="36">
         <v>25</v>
       </c>
-      <c r="K105" s="39">
+      <c r="K105" s="36">
         <v>21</v>
       </c>
-      <c r="L105" s="39">
+      <c r="L105" s="36">
         <v>16</v>
       </c>
     </row>
@@ -7084,24 +7157,24 @@
         <v>200</v>
       </c>
       <c r="E106" s="7"/>
-      <c r="F106" s="42">
+      <c r="F106" s="39">
         <v>37</v>
       </c>
-      <c r="G106" s="39">
+      <c r="G106" s="36">
         <v>25</v>
       </c>
-      <c r="H106" s="39">
+      <c r="H106" s="36">
         <v>30</v>
       </c>
-      <c r="K106" s="39">
+      <c r="K106" s="36">
         <v>32</v>
       </c>
-      <c r="L106" s="39">
+      <c r="L106" s="36">
         <v>31</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="47">
+      <c r="A107" s="44">
         <v>1228</v>
       </c>
       <c r="B107" s="12" t="s">
@@ -7114,19 +7187,19 @@
         <v>200</v>
       </c>
       <c r="E107" s="7"/>
-      <c r="F107" s="42">
+      <c r="F107" s="39">
         <v>36</v>
       </c>
-      <c r="G107" s="39">
+      <c r="G107" s="36">
         <v>34</v>
       </c>
-      <c r="H107" s="39">
+      <c r="H107" s="36">
         <v>30</v>
       </c>
-      <c r="K107" s="39">
+      <c r="K107" s="36">
         <v>33</v>
       </c>
-      <c r="L107" s="39">
+      <c r="L107" s="36">
         <v>24</v>
       </c>
     </row>
@@ -7144,24 +7217,24 @@
         <v>200</v>
       </c>
       <c r="E108" s="7"/>
-      <c r="F108" s="43" t="s">
+      <c r="F108" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="G108" s="39">
+      <c r="G108" s="36">
         <v>24</v>
       </c>
-      <c r="H108" s="39">
+      <c r="H108" s="36">
         <v>25</v>
       </c>
-      <c r="K108" s="39">
+      <c r="K108" s="36">
         <v>26</v>
       </c>
-      <c r="L108" s="45" t="s">
+      <c r="L108" s="42" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="47">
+      <c r="A109" s="44">
         <v>1230</v>
       </c>
       <c r="B109" s="12" t="s">
@@ -7174,19 +7247,19 @@
         <v>200</v>
       </c>
       <c r="E109" s="7"/>
-      <c r="F109" s="42">
+      <c r="F109" s="39">
         <v>37</v>
       </c>
-      <c r="G109" s="39">
+      <c r="G109" s="36">
         <v>22</v>
       </c>
-      <c r="H109" s="39">
+      <c r="H109" s="36">
         <v>32</v>
       </c>
-      <c r="K109" s="39">
+      <c r="K109" s="36">
         <v>23</v>
       </c>
-      <c r="L109" s="39">
+      <c r="L109" s="36">
         <v>18</v>
       </c>
     </row>
@@ -7204,24 +7277,24 @@
         <v>200</v>
       </c>
       <c r="E110" s="7"/>
-      <c r="F110" s="43" t="s">
+      <c r="F110" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="G110" s="45" t="s">
+      <c r="G110" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="H110" s="45" t="s">
+      <c r="H110" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="K110" s="39" t="s">
+      <c r="K110" s="36" t="s">
         <v>263</v>
       </c>
-      <c r="L110" s="45" t="s">
+      <c r="L110" s="42" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="47">
+      <c r="A111" s="44">
         <v>1232</v>
       </c>
       <c r="B111" s="12" t="s">
@@ -7234,19 +7307,19 @@
         <v>200</v>
       </c>
       <c r="E111" s="7"/>
-      <c r="F111" s="42">
+      <c r="F111" s="39">
         <v>36</v>
       </c>
-      <c r="G111" s="39">
+      <c r="G111" s="36">
         <v>32</v>
       </c>
-      <c r="H111" s="39">
+      <c r="H111" s="36">
         <v>32</v>
       </c>
-      <c r="K111" s="39">
+      <c r="K111" s="36">
         <v>34</v>
       </c>
-      <c r="L111" s="39">
+      <c r="L111" s="36">
         <v>26</v>
       </c>
     </row>
@@ -7264,24 +7337,24 @@
         <v>200</v>
       </c>
       <c r="E112" s="7"/>
-      <c r="F112" s="42">
+      <c r="F112" s="39">
         <v>35</v>
       </c>
-      <c r="G112" s="39">
+      <c r="G112" s="36">
         <v>27</v>
       </c>
-      <c r="H112" s="39">
+      <c r="H112" s="36">
         <v>34</v>
       </c>
-      <c r="K112" s="39">
+      <c r="K112" s="36">
         <v>31</v>
       </c>
-      <c r="L112" s="39">
+      <c r="L112" s="36">
         <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="47">
+      <c r="A113" s="44">
         <v>1234</v>
       </c>
       <c r="B113" s="12" t="s">
@@ -7294,20 +7367,496 @@
         <v>200</v>
       </c>
       <c r="E113" s="7"/>
-      <c r="F113" s="42">
+      <c r="F113" s="39">
         <v>33</v>
       </c>
-      <c r="G113" s="39">
+      <c r="G113" s="36">
         <v>24</v>
       </c>
-      <c r="H113" s="39">
+      <c r="H113" s="36">
         <v>31</v>
       </c>
-      <c r="K113" s="39">
+      <c r="K113" s="36">
         <v>20</v>
       </c>
-      <c r="L113" s="39">
+      <c r="L113" s="36">
         <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>1201</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D114" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" s="44">
+        <v>1202</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D115" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>1203</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D116" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" s="44">
+        <v>1204</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D117" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>1205</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D118" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" s="44">
+        <v>1206</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D119" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>1207</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D120" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" s="44">
+        <v>1208</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D121" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>1209</v>
+      </c>
+      <c r="B122" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D122" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" s="44">
+        <v>1210</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D123" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>1211</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D124" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" s="44">
+        <v>1212</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D125" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" s="44">
+        <v>1213</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D126" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>1214</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D127" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>1215</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D128" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="44">
+        <v>1216</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D129" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>1217</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D130" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="44">
+        <v>1218</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D131" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>1219</v>
+      </c>
+      <c r="B132" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D132" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="44">
+        <v>1220</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D133" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>1221</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D134" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="44">
+        <v>1222</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D135" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>1223</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D136" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="44">
+        <v>1224</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D137" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>1225</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D138" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="44">
+        <v>1226</v>
+      </c>
+      <c r="B139" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D139" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>1227</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D140" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="44">
+        <v>1228</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D141" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>1229</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D142" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="44">
+        <v>1230</v>
+      </c>
+      <c r="B143" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D143" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>1231</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D144" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="44">
+        <v>1232</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D145" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>1233</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D146" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="44">
+        <v>1234</v>
+      </c>
+      <c r="B147" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D147" s="8">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C4AFF0-CEC3-44D9-B5F9-C110E482BA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AEC9A3-6A32-4328-9709-B9B2535DBCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
+    <workbookView xWindow="-30" yWindow="135" windowWidth="14820" windowHeight="15450" activeTab="1" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="292">
   <si>
     <t>Roll_No</t>
   </si>
@@ -910,6 +910,9 @@
   </si>
   <si>
     <t>10.01.2010</t>
+  </si>
+  <si>
+    <t>AB</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1282,84 @@
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1681,7 +1761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542F166A-4256-4AA6-A03A-29FB16EA9D15}">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -3615,20 +3695,185 @@
         <v>261</v>
       </c>
     </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>1101</v>
+      </c>
+    </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>1102</v>
+      </c>
       <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>1103</v>
+      </c>
       <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>1104</v>
+      </c>
       <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>1105</v>
+      </c>
       <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>1106</v>
+      </c>
       <c r="G80" s="1"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>1135</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3640,7 +3885,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D043D23-75C9-4A79-B369-DB03044E1B80}">
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M181"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="22.28515625" customWidth="1"/>
@@ -7353,7 +7598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="44">
         <v>1234</v>
       </c>
@@ -7383,7 +7628,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
         <v>1201</v>
       </c>
@@ -7396,8 +7641,23 @@
       <c r="D114" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F114" s="35">
+        <v>33</v>
+      </c>
+      <c r="G114" s="41">
+        <v>33</v>
+      </c>
+      <c r="K114" s="41">
+        <v>28</v>
+      </c>
+      <c r="L114" s="41">
+        <v>28</v>
+      </c>
+      <c r="M114" s="41">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="44">
         <v>1202</v>
       </c>
@@ -7410,8 +7670,23 @@
       <c r="D115" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F115" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="G115" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="K115" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="L115" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="M115" s="36" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
         <v>1203</v>
       </c>
@@ -7424,8 +7699,23 @@
       <c r="D116" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F116" s="35">
+        <v>33</v>
+      </c>
+      <c r="G116" s="36">
+        <v>29</v>
+      </c>
+      <c r="K116" s="36">
+        <v>36</v>
+      </c>
+      <c r="L116" s="36">
+        <v>25</v>
+      </c>
+      <c r="M116" s="39">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="44">
         <v>1204</v>
       </c>
@@ -7438,8 +7728,23 @@
       <c r="D117" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F117" s="38">
+        <v>18</v>
+      </c>
+      <c r="G117" s="36">
+        <v>25</v>
+      </c>
+      <c r="K117" s="36">
+        <v>13</v>
+      </c>
+      <c r="L117" s="36">
+        <v>19</v>
+      </c>
+      <c r="M117" s="39">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
         <v>1205</v>
       </c>
@@ -7452,8 +7757,23 @@
       <c r="D118" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F118" s="35">
+        <v>33</v>
+      </c>
+      <c r="G118" s="36">
+        <v>22</v>
+      </c>
+      <c r="K118" s="36">
+        <v>31</v>
+      </c>
+      <c r="L118" s="36">
+        <v>16</v>
+      </c>
+      <c r="M118" s="39">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A119" s="44">
         <v>1206</v>
       </c>
@@ -7466,8 +7786,23 @@
       <c r="D119" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F119" s="35">
+        <v>36</v>
+      </c>
+      <c r="G119" s="36">
+        <v>38</v>
+      </c>
+      <c r="K119" s="36">
+        <v>29</v>
+      </c>
+      <c r="L119" s="36">
+        <v>31</v>
+      </c>
+      <c r="M119" s="39">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>1207</v>
       </c>
@@ -7480,8 +7815,23 @@
       <c r="D120" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F120" s="38">
+        <v>35</v>
+      </c>
+      <c r="G120" s="36">
+        <v>33</v>
+      </c>
+      <c r="K120" s="36">
+        <v>30</v>
+      </c>
+      <c r="L120" s="36">
+        <v>28</v>
+      </c>
+      <c r="M120" s="39">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="44">
         <v>1208</v>
       </c>
@@ -7494,8 +7844,23 @@
       <c r="D121" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F121" s="39">
+        <v>37</v>
+      </c>
+      <c r="G121" s="36">
+        <v>36</v>
+      </c>
+      <c r="K121" s="36">
+        <v>40</v>
+      </c>
+      <c r="L121" s="36">
+        <v>31</v>
+      </c>
+      <c r="M121" s="36">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
         <v>1209</v>
       </c>
@@ -7508,8 +7873,23 @@
       <c r="D122" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F122" s="35">
+        <v>32</v>
+      </c>
+      <c r="G122" s="36">
+        <v>34</v>
+      </c>
+      <c r="K122" s="36">
+        <v>30</v>
+      </c>
+      <c r="L122" s="36">
+        <v>24</v>
+      </c>
+      <c r="M122" s="39">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="44">
         <v>1210</v>
       </c>
@@ -7522,8 +7902,23 @@
       <c r="D123" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F123" s="38">
+        <v>35</v>
+      </c>
+      <c r="G123" s="36">
+        <v>38</v>
+      </c>
+      <c r="K123" s="36">
+        <v>39</v>
+      </c>
+      <c r="L123" s="36">
+        <v>28</v>
+      </c>
+      <c r="M123" s="39">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
         <v>1211</v>
       </c>
@@ -7536,8 +7931,23 @@
       <c r="D124" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F124" s="35">
+        <v>34</v>
+      </c>
+      <c r="G124" s="36">
+        <v>34</v>
+      </c>
+      <c r="K124" s="36">
+        <v>33</v>
+      </c>
+      <c r="L124" s="36">
+        <v>22</v>
+      </c>
+      <c r="M124" s="39">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A125" s="44">
         <v>1212</v>
       </c>
@@ -7550,8 +7960,23 @@
       <c r="D125" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F125" s="35">
+        <v>38</v>
+      </c>
+      <c r="G125" s="36">
+        <v>35</v>
+      </c>
+      <c r="K125" s="36">
+        <v>39</v>
+      </c>
+      <c r="L125" s="36">
+        <v>27</v>
+      </c>
+      <c r="M125" s="39">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A126" s="44">
         <v>1213</v>
       </c>
@@ -7564,8 +7989,23 @@
       <c r="D126" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F126" s="35">
+        <v>33</v>
+      </c>
+      <c r="G126" s="36">
+        <v>34</v>
+      </c>
+      <c r="K126" s="36">
+        <v>39</v>
+      </c>
+      <c r="L126" s="36">
+        <v>33</v>
+      </c>
+      <c r="M126" s="39">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
         <v>1214</v>
       </c>
@@ -7578,8 +8018,23 @@
       <c r="D127" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F127" s="35">
+        <v>30</v>
+      </c>
+      <c r="G127" s="36">
+        <v>28</v>
+      </c>
+      <c r="K127" s="36">
+        <v>25</v>
+      </c>
+      <c r="L127" s="36">
+        <v>22</v>
+      </c>
+      <c r="M127" s="39">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
         <v>1215</v>
       </c>
@@ -7592,8 +8047,23 @@
       <c r="D128" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F128" s="35">
+        <v>37</v>
+      </c>
+      <c r="G128" s="36">
+        <v>33</v>
+      </c>
+      <c r="K128" s="36">
+        <v>36</v>
+      </c>
+      <c r="L128" s="36">
+        <v>21</v>
+      </c>
+      <c r="M128" s="39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A129" s="44">
         <v>1216</v>
       </c>
@@ -7606,8 +8076,23 @@
       <c r="D129" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F129" s="35">
+        <v>33</v>
+      </c>
+      <c r="G129" s="36">
+        <v>29</v>
+      </c>
+      <c r="K129" s="36">
+        <v>34</v>
+      </c>
+      <c r="L129" s="36">
+        <v>21</v>
+      </c>
+      <c r="M129" s="39">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>1217</v>
       </c>
@@ -7620,8 +8105,23 @@
       <c r="D130" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F130" s="39">
+        <v>27</v>
+      </c>
+      <c r="G130" s="36">
+        <v>28</v>
+      </c>
+      <c r="K130" s="36">
+        <v>26</v>
+      </c>
+      <c r="L130" s="36">
+        <v>15</v>
+      </c>
+      <c r="M130" s="36">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="44">
         <v>1218</v>
       </c>
@@ -7634,8 +8134,23 @@
       <c r="D131" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F131" s="39">
+        <v>27</v>
+      </c>
+      <c r="G131" s="36">
+        <v>20</v>
+      </c>
+      <c r="K131" s="36">
+        <v>36</v>
+      </c>
+      <c r="L131" s="36">
+        <v>18</v>
+      </c>
+      <c r="M131" s="36">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>1219</v>
       </c>
@@ -7648,8 +8163,23 @@
       <c r="D132" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F132" s="39">
+        <v>28</v>
+      </c>
+      <c r="G132" s="36">
+        <v>36</v>
+      </c>
+      <c r="K132" s="36">
+        <v>39</v>
+      </c>
+      <c r="L132" s="36">
+        <v>25</v>
+      </c>
+      <c r="M132" s="36">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="44">
         <v>1220</v>
       </c>
@@ -7662,8 +8192,23 @@
       <c r="D133" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F133" s="39">
+        <v>30</v>
+      </c>
+      <c r="G133" s="36">
+        <v>22</v>
+      </c>
+      <c r="K133" s="36">
+        <v>14</v>
+      </c>
+      <c r="L133" s="36">
+        <v>14</v>
+      </c>
+      <c r="M133" s="36">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>1221</v>
       </c>
@@ -7676,8 +8221,23 @@
       <c r="D134" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F134" s="39">
+        <v>26</v>
+      </c>
+      <c r="G134" s="36">
+        <v>25</v>
+      </c>
+      <c r="K134" s="36">
+        <v>39</v>
+      </c>
+      <c r="L134" s="36">
+        <v>24</v>
+      </c>
+      <c r="M134" s="36">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="44">
         <v>1222</v>
       </c>
@@ -7690,8 +8250,23 @@
       <c r="D135" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F135" s="39">
+        <v>29</v>
+      </c>
+      <c r="G135" s="36">
+        <v>25</v>
+      </c>
+      <c r="K135" s="36">
+        <v>24</v>
+      </c>
+      <c r="L135" s="36">
+        <v>16</v>
+      </c>
+      <c r="M135" s="36">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>1223</v>
       </c>
@@ -7704,8 +8279,23 @@
       <c r="D136" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F136" s="39">
+        <v>34</v>
+      </c>
+      <c r="G136" s="36">
+        <v>36</v>
+      </c>
+      <c r="H136" s="36">
+        <v>33</v>
+      </c>
+      <c r="K136" s="36">
+        <v>40</v>
+      </c>
+      <c r="L136" s="36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="44">
         <v>1224</v>
       </c>
@@ -7718,8 +8308,23 @@
       <c r="D137" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F137" s="36">
+        <v>32</v>
+      </c>
+      <c r="G137" s="36">
+        <v>36</v>
+      </c>
+      <c r="H137" s="36">
+        <v>30</v>
+      </c>
+      <c r="K137" s="36">
+        <v>40</v>
+      </c>
+      <c r="L137" s="36">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>1225</v>
       </c>
@@ -7732,8 +8337,23 @@
       <c r="D138" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F138" s="39">
+        <v>0</v>
+      </c>
+      <c r="G138" s="36">
+        <v>0</v>
+      </c>
+      <c r="H138" s="36">
+        <v>0</v>
+      </c>
+      <c r="K138" s="36">
+        <v>0</v>
+      </c>
+      <c r="L138" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="44">
         <v>1226</v>
       </c>
@@ -7746,8 +8366,23 @@
       <c r="D139" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F139" s="39">
+        <v>34</v>
+      </c>
+      <c r="G139" s="36">
+        <v>34</v>
+      </c>
+      <c r="H139" s="36">
+        <v>30</v>
+      </c>
+      <c r="K139" s="36">
+        <v>28</v>
+      </c>
+      <c r="L139" s="36">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>1227</v>
       </c>
@@ -7760,8 +8395,23 @@
       <c r="D140" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F140" s="39">
+        <v>35</v>
+      </c>
+      <c r="G140" s="36">
+        <v>37</v>
+      </c>
+      <c r="H140" s="36">
+        <v>30</v>
+      </c>
+      <c r="K140" s="36">
+        <v>40</v>
+      </c>
+      <c r="L140" s="36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="44">
         <v>1228</v>
       </c>
@@ -7774,8 +8424,23 @@
       <c r="D141" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F141" s="39">
+        <v>34</v>
+      </c>
+      <c r="G141" s="36">
+        <v>33</v>
+      </c>
+      <c r="H141" s="36">
+        <v>30</v>
+      </c>
+      <c r="K141" s="36">
+        <v>35</v>
+      </c>
+      <c r="L141" s="36">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>1229</v>
       </c>
@@ -7788,8 +8453,23 @@
       <c r="D142" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F142" s="39">
+        <v>37</v>
+      </c>
+      <c r="G142" s="36">
+        <v>36</v>
+      </c>
+      <c r="H142" s="36">
+        <v>29</v>
+      </c>
+      <c r="K142" s="36">
+        <v>35</v>
+      </c>
+      <c r="L142" s="36">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="44">
         <v>1230</v>
       </c>
@@ -7802,8 +8482,23 @@
       <c r="D143" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F143" s="39">
+        <v>32</v>
+      </c>
+      <c r="G143" s="36">
+        <v>33</v>
+      </c>
+      <c r="H143" s="36">
+        <v>28</v>
+      </c>
+      <c r="K143" s="36">
+        <v>39</v>
+      </c>
+      <c r="L143" s="36">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>1231</v>
       </c>
@@ -7816,8 +8511,23 @@
       <c r="D144" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F144" s="39">
+        <v>32</v>
+      </c>
+      <c r="G144" s="36">
+        <v>36</v>
+      </c>
+      <c r="H144" s="36">
+        <v>32</v>
+      </c>
+      <c r="K144" s="36">
+        <v>39</v>
+      </c>
+      <c r="L144" s="36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="44">
         <v>1232</v>
       </c>
@@ -7830,8 +8540,23 @@
       <c r="D145" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F145" s="39">
+        <v>39</v>
+      </c>
+      <c r="G145" s="36">
+        <v>35</v>
+      </c>
+      <c r="H145" s="36">
+        <v>35</v>
+      </c>
+      <c r="K145" s="36">
+        <v>39</v>
+      </c>
+      <c r="L145" s="36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>1233</v>
       </c>
@@ -7844,8 +8569,23 @@
       <c r="D146" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F146" s="39">
+        <v>34</v>
+      </c>
+      <c r="G146" s="36">
+        <v>36</v>
+      </c>
+      <c r="H146" s="36">
+        <v>35</v>
+      </c>
+      <c r="K146" s="36">
+        <v>39</v>
+      </c>
+      <c r="L146" s="36">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="44">
         <v>1234</v>
       </c>
@@ -7858,60 +8598,267 @@
       <c r="D147" s="8">
         <v>200</v>
       </c>
+      <c r="F147" s="39">
+        <v>33</v>
+      </c>
+      <c r="G147" s="36">
+        <v>35</v>
+      </c>
+      <c r="H147" s="36">
+        <v>29</v>
+      </c>
+      <c r="K147" s="36">
+        <v>28</v>
+      </c>
+      <c r="L147" s="36">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" s="6"/>
+      <c r="B148" s="12"/>
+      <c r="C148" s="8"/>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" s="44"/>
+      <c r="B149" s="12"/>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" s="6"/>
+      <c r="B150" s="12"/>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" s="44"/>
+      <c r="B151" s="12"/>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" s="6"/>
+      <c r="B152" s="12"/>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" s="44"/>
+      <c r="B153" s="12"/>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" s="6"/>
+      <c r="B154" s="12"/>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" s="44"/>
+      <c r="B155" s="12"/>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" s="6"/>
+      <c r="B156" s="12"/>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" s="44"/>
+      <c r="B157" s="12"/>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" s="6"/>
+      <c r="B158" s="12"/>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" s="44"/>
+      <c r="B159" s="12"/>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" s="44"/>
+      <c r="B160" s="12"/>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="6"/>
+      <c r="B161" s="12"/>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="6"/>
+      <c r="B162" s="12"/>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="44"/>
+      <c r="B163" s="12"/>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="6"/>
+      <c r="B164" s="12"/>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="44"/>
+      <c r="B165" s="12"/>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="6"/>
+      <c r="B166" s="12"/>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="44"/>
+      <c r="B167" s="12"/>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="6"/>
+      <c r="B168" s="12"/>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="44"/>
+      <c r="B169" s="12"/>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="6"/>
+      <c r="B170" s="12"/>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="44"/>
+      <c r="B171" s="12"/>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="6"/>
+      <c r="B172" s="12"/>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="44"/>
+      <c r="B173" s="12"/>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="6"/>
+      <c r="B174" s="12"/>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="44"/>
+      <c r="B175" s="12"/>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="6"/>
+      <c r="B176" s="12"/>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="44"/>
+      <c r="B177" s="12"/>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="6"/>
+      <c r="B178" s="12"/>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="44"/>
+      <c r="B179" s="12"/>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="6"/>
+      <c r="B180" s="12"/>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="44"/>
+      <c r="B181" s="12"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F81 F87">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="22" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F113">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G81:G95">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G96:G113">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="19" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K81">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="18" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K82:K113">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L81 L87">
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L82:L113">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M81 M87">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M82:M101">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H102:H113">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F130:F147">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F115 F121">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G130:G147">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G115:G129">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M130:M135">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M115:M129">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
+      <formula>13.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H136:H147">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L82:L113">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+  <conditionalFormatting sqref="K130:K147">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M81 M87">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="K115:K129">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M82:M101">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="L130:L147">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H102:H113">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="L115:L129">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>

--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AEC9A3-6A32-4328-9709-B9B2535DBCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A082E7F5-DD34-4DF7-A5F2-69EA8604BAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="135" windowWidth="14820" windowHeight="15450" activeTab="1" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="299">
   <si>
     <t>Roll_No</t>
   </si>
@@ -609,9 +609,6 @@
     <t>SACHIN RATHVA</t>
   </si>
   <si>
-    <t>SNEHABEN PANCHOLI</t>
-  </si>
-  <si>
     <t>SUMIT RATHVA</t>
   </si>
   <si>
@@ -913,6 +910,30 @@
   </si>
   <si>
     <t>AB</t>
+  </si>
+  <si>
+    <t>SNEHABEN RATHVA</t>
+  </si>
+  <si>
+    <t>DEMO</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>01.01.2000</t>
+  </si>
+  <si>
+    <t>TERM-1</t>
+  </si>
+  <si>
+    <t>TERM-2</t>
+  </si>
+  <si>
+    <t>PWT-3</t>
+  </si>
+  <si>
+    <t>PWT-4</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1174,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1199,7 +1220,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1274,99 +1295,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike val="0"/>
-      </font>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <b/>
@@ -1761,7 +1716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542F166A-4256-4AA6-A03A-29FB16EA9D15}">
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1799,48 +1754,48 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>61</v>
+        <v>1000</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>293</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="F2" s="2">
-        <v>6353423130</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H2" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E2" s="47">
+        <v>574747014579</v>
+      </c>
+      <c r="F2" s="3">
+        <v>9602857698</v>
+      </c>
+      <c r="G2" s="46">
+        <v>10</v>
+      </c>
+      <c r="H2" s="48" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="F3" s="2">
-        <v>9925636156</v>
+        <v>139</v>
+      </c>
+      <c r="F3" s="3">
+        <v>6353423130</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>178</v>
@@ -1851,22 +1806,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="3">
-        <v>7861847673</v>
+        <v>140</v>
+      </c>
+      <c r="F4" s="2">
+        <v>9925636156</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>178</v>
@@ -1876,23 +1831,23 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F5" s="2">
-        <v>9727883707</v>
+      <c r="A5" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="3">
+        <v>7861847673</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>178</v>
@@ -1903,22 +1858,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F6" s="3">
-        <v>9925520169</v>
+        <v>142</v>
+      </c>
+      <c r="F6" s="2">
+        <v>9727883707</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>178</v>
@@ -1929,22 +1884,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="F7" s="2">
-        <v>9313643310</v>
+        <v>143</v>
+      </c>
+      <c r="F7" s="3">
+        <v>9925520169</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>178</v>
@@ -1955,22 +1910,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>9825938737</v>
+        <v>9313643310</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>178</v>
@@ -1981,22 +1936,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F9" s="2">
-        <v>8980177520</v>
+        <v>9825938737</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>178</v>
@@ -2007,22 +1962,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F10" s="2">
-        <v>9537598991</v>
+        <v>8980177520</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>178</v>
@@ -2033,22 +1988,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F11" s="2">
-        <v>9712863175</v>
+        <v>9537598991</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>178</v>
@@ -2059,22 +2014,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F12" s="2">
-        <v>7567358072</v>
+        <v>9712863175</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>178</v>
@@ -2085,22 +2040,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F13" s="3">
-        <v>8141828290</v>
+        <v>149</v>
+      </c>
+      <c r="F13" s="2">
+        <v>7567358072</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>178</v>
@@ -2111,22 +2066,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="F14" s="2">
-        <v>9974704919</v>
+        <v>150</v>
+      </c>
+      <c r="F14" s="3">
+        <v>8141828290</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>178</v>
@@ -2137,22 +2092,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F15" s="2">
-        <v>9913943175</v>
+        <v>9974704919</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>178</v>
@@ -2163,22 +2118,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F16" s="2">
-        <v>9978463169</v>
+        <v>9913943175</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>178</v>
@@ -2189,22 +2144,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F17" s="3">
-        <v>9925251723</v>
+        <v>153</v>
+      </c>
+      <c r="F17" s="2">
+        <v>9978463169</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>178</v>
@@ -2215,22 +2170,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F18" s="2">
-        <v>9712972430</v>
+        <v>154</v>
+      </c>
+      <c r="F18" s="3">
+        <v>9925251723</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>178</v>
@@ -2241,22 +2196,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F19" s="4">
-        <v>9925260543</v>
+        <v>155</v>
+      </c>
+      <c r="F19" s="2">
+        <v>9712972430</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>178</v>
@@ -2267,22 +2222,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F20" s="2">
-        <v>6340300055</v>
+        <v>156</v>
+      </c>
+      <c r="F20" s="4">
+        <v>9925260543</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>178</v>
@@ -2293,22 +2248,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F21" s="2">
-        <v>6354598416</v>
+        <v>6340300055</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>178</v>
@@ -2319,22 +2274,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F22" s="2">
-        <v>9537854070</v>
+        <v>6354598416</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>178</v>
@@ -2345,22 +2300,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F23" s="3">
-        <v>9726573288</v>
+        <v>159</v>
+      </c>
+      <c r="F23" s="2">
+        <v>9537854070</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>178</v>
@@ -2371,22 +2326,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="F24" s="2">
-        <v>6340300195</v>
+        <v>160</v>
+      </c>
+      <c r="F24" s="3">
+        <v>9726573288</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>178</v>
@@ -2397,22 +2352,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F25" s="3">
-        <v>9879769465</v>
+        <v>161</v>
+      </c>
+      <c r="F25" s="2">
+        <v>6340300195</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>178</v>
@@ -2423,22 +2378,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F26" s="3">
-        <v>8780316912</v>
+        <v>9879769465</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>178</v>
@@ -2449,22 +2404,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="F27" s="4">
-        <v>9723255189</v>
+        <v>163</v>
+      </c>
+      <c r="F27" s="3">
+        <v>8780316912</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>178</v>
@@ -2475,22 +2430,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="F28" s="2">
-        <v>8141284920</v>
+        <v>164</v>
+      </c>
+      <c r="F28" s="4">
+        <v>9723255189</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>178</v>
@@ -2501,22 +2456,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F29" s="2">
-        <v>9825512456</v>
+        <v>8141284920</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>178</v>
@@ -2527,22 +2482,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F30" s="4">
-        <v>9001844668</v>
+        <v>166</v>
+      </c>
+      <c r="F30" s="2">
+        <v>9825512456</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>178</v>
@@ -2553,22 +2508,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="F31" s="2">
-        <v>9574632300</v>
+        <v>167</v>
+      </c>
+      <c r="F31" s="4">
+        <v>9001844668</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>178</v>
@@ -2579,22 +2534,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F32" s="2">
-        <v>9727926762</v>
+        <v>9574632300</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>178</v>
@@ -2605,22 +2560,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="F33" s="3">
-        <v>6354922106</v>
+        <v>169</v>
+      </c>
+      <c r="F33" s="2">
+        <v>9727926762</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>178</v>
@@ -2631,22 +2586,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F34" s="3">
-        <v>6352551344</v>
+        <v>6354922106</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>178</v>
@@ -2657,22 +2612,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F35" s="3">
-        <v>9427075491</v>
+        <v>6352551344</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>178</v>
@@ -2683,22 +2638,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F36" s="3">
-        <v>9687168715</v>
+        <v>9427075491</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>178</v>
@@ -2709,22 +2664,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="F37" s="2">
-        <v>9099247253</v>
+        <v>173</v>
+      </c>
+      <c r="F37" s="3">
+        <v>9687168715</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>178</v>
@@ -2735,22 +2690,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F38" s="2">
-        <v>9726658420</v>
+        <v>9099247253</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>178</v>
@@ -2761,22 +2716,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F39" s="3">
-        <v>9316586342</v>
+        <v>175</v>
+      </c>
+      <c r="F39" s="2">
+        <v>9726658420</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>178</v>
@@ -2787,22 +2742,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F40" s="3">
-        <v>9909233642</v>
+        <v>9316586342</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>178</v>
@@ -2812,1080 +2767,1106 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+      <c r="A41" s="7">
+        <v>1039</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F41" s="3">
+        <v>9909233642</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
         <v>1201</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B42" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C42" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D42" s="44" t="s">
+        <v>263</v>
+      </c>
+      <c r="E42" s="27">
+        <v>629725429548</v>
+      </c>
+      <c r="F42" s="2">
+        <v>7874735374</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="19">
+        <v>1202</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D41" s="45" t="s">
+      <c r="D43" s="44" t="s">
         <v>264</v>
       </c>
-      <c r="E41" s="27">
-        <v>629725429548</v>
-      </c>
-      <c r="F41" s="2">
-        <v>7874735374</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="19">
-        <v>1202</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="E43" s="27">
+        <v>868784631083</v>
+      </c>
+      <c r="F43" s="32">
+        <v>9624104337</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>1203</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D42" s="45" t="s">
+      <c r="D44" s="44" t="s">
         <v>265</v>
       </c>
-      <c r="E42" s="27">
-        <v>868784631083</v>
-      </c>
-      <c r="F42" s="32">
-        <v>9624104337</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>1203</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="E44" s="27">
+        <v>861502383654</v>
+      </c>
+      <c r="F44" s="32">
+        <v>8141169136</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="19">
+        <v>1204</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D43" s="45" t="s">
+      <c r="D45" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="E43" s="27">
-        <v>861502383654</v>
-      </c>
-      <c r="F43" s="32">
-        <v>8141169136</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="19">
-        <v>1204</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="E45" s="27">
+        <v>523235907356</v>
+      </c>
+      <c r="F45" s="2">
+        <v>9737392469</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>1205</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D44" s="45" t="s">
+      <c r="D46" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="E44" s="27">
-        <v>523235907356</v>
-      </c>
-      <c r="F44" s="2">
-        <v>9737392469</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
-        <v>1205</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="E46" s="27">
+        <v>892372104796</v>
+      </c>
+      <c r="F46" s="32">
+        <v>9265841928</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="19">
+        <v>1206</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D45" s="45" t="s">
+      <c r="D47" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="E45" s="27">
-        <v>892372104796</v>
-      </c>
-      <c r="F45" s="32">
-        <v>9265841928</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="19">
-        <v>1206</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="E47" s="27">
+        <v>412140699697</v>
+      </c>
+      <c r="F47" s="32">
+        <v>9725282548</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>1207</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D46" s="45" t="s">
+      <c r="D48" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="E46" s="27">
-        <v>412140699697</v>
-      </c>
-      <c r="F46" s="32">
-        <v>9725282548</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
-        <v>1207</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="E48" s="27">
+        <v>240156702958</v>
+      </c>
+      <c r="F48" s="32">
+        <v>9687875011</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="19">
+        <v>1208</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="45" t="s">
+      <c r="D49" s="44" t="s">
         <v>270</v>
       </c>
-      <c r="E47" s="27">
-        <v>240156702958</v>
-      </c>
-      <c r="F47" s="32">
-        <v>9687875011</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="19">
-        <v>1208</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="E49" s="27">
+        <v>279595726744</v>
+      </c>
+      <c r="F49" s="32">
+        <v>9879537857</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>1209</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D48" s="45" t="s">
+      <c r="D50" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="E48" s="27">
-        <v>279595726744</v>
-      </c>
-      <c r="F48" s="32">
-        <v>9879537857</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
-        <v>1209</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="E50" s="27">
+        <v>916336765264</v>
+      </c>
+      <c r="F50" s="2">
+        <v>9537575058</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="19">
+        <v>1210</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D49" s="45" t="s">
+      <c r="D51" s="44" t="s">
         <v>272</v>
       </c>
-      <c r="E49" s="27">
-        <v>916336765264</v>
-      </c>
-      <c r="F49" s="2">
-        <v>9537575058</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="19">
-        <v>1210</v>
-      </c>
-      <c r="B50" s="20" t="s">
+      <c r="E51" s="27">
+        <v>705953487400</v>
+      </c>
+      <c r="F51" s="32">
+        <v>9687111646</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>1211</v>
+      </c>
+      <c r="B52" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D50" s="45" t="s">
+      <c r="D52" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="E50" s="27">
-        <v>705953487400</v>
-      </c>
-      <c r="F50" s="32">
-        <v>9687111646</v>
-      </c>
-      <c r="G50" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
-        <v>1211</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D51" s="45" t="s">
-        <v>274</v>
-      </c>
-      <c r="E51" s="27">
+      <c r="E52" s="27">
         <v>764006954215</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F52" s="32">
         <v>8200730410</v>
       </c>
-      <c r="G51" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="19">
-        <v>1212</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D52" s="45" t="s">
-        <v>275</v>
-      </c>
-      <c r="E52" s="27">
-        <v>329596170047</v>
-      </c>
-      <c r="F52" s="2">
-        <v>9016937704</v>
-      </c>
       <c r="G52" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="19">
+        <v>1212</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D53" s="44" t="s">
+        <v>274</v>
+      </c>
+      <c r="E53" s="27">
+        <v>329596170047</v>
+      </c>
+      <c r="F53" s="2">
+        <v>9016937704</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="19">
         <v>1213</v>
       </c>
-      <c r="B53" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="C53" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="D53" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="E53" s="28">
+      <c r="B54" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="D54" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="E54" s="28">
         <v>520048808079</v>
       </c>
-      <c r="F53" s="33">
+      <c r="F54" s="33">
         <v>991338636</v>
       </c>
-      <c r="G53" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
-        <v>1214</v>
-      </c>
-      <c r="B54" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D54" s="45" t="s">
-        <v>276</v>
-      </c>
-      <c r="E54" s="27">
-        <v>632504887936</v>
-      </c>
-      <c r="F54" s="2">
-        <v>9016677020</v>
-      </c>
       <c r="G54" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
+        <v>1214</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D55" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="E55" s="27">
+        <v>632504887936</v>
+      </c>
+      <c r="F55" s="2">
+        <v>9016677020</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
         <v>1215</v>
       </c>
-      <c r="B55" s="20" t="s">
+      <c r="B56" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D56" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="E56" s="27">
+        <v>924194629769</v>
+      </c>
+      <c r="F56" s="2">
+        <v>8758595513</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="19">
+        <v>1216</v>
+      </c>
+      <c r="B57" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D55" s="45" t="s">
+      <c r="D57" s="44" t="s">
         <v>277</v>
       </c>
-      <c r="E55" s="27">
-        <v>924194629769</v>
-      </c>
-      <c r="F55" s="2">
-        <v>8758595513</v>
-      </c>
-      <c r="G55" s="12" t="s">
+      <c r="E57" s="27">
+        <v>336666374564</v>
+      </c>
+      <c r="F57" s="2">
+        <v>8320226326</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>1217</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="D58" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="E58" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="F58" s="26">
+        <v>6352719479</v>
+      </c>
+      <c r="G58" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="19">
+        <v>1218</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="D59" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="E59" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="F59" s="26">
+        <v>9904123744</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>1219</v>
+      </c>
+      <c r="B60" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>279</v>
+      </c>
+      <c r="E60" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="F60" s="26">
+        <v>9574218015</v>
+      </c>
+      <c r="G60" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="19">
+        <v>1220</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="D61" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="E61" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="F61" s="26">
+        <v>9737894252</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>1221</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="C62" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="D62" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="E62" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="F62" s="26">
+        <v>7567095117</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="19">
+        <v>1222</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="C63" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="D63" s="44" t="s">
+        <v>256</v>
+      </c>
+      <c r="E63" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="F63" s="34">
+        <v>6355764851</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>1223</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D64" s="44" t="s">
+        <v>257</v>
+      </c>
+      <c r="E64" s="31">
+        <v>588971485746</v>
+      </c>
+      <c r="F64" s="32">
+        <v>8156035767</v>
+      </c>
+      <c r="G64" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="H55" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="19">
-        <v>1216</v>
-      </c>
-      <c r="B56" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D56" s="45" t="s">
-        <v>278</v>
-      </c>
-      <c r="E56" s="27">
-        <v>336666374564</v>
-      </c>
-      <c r="F56" s="2">
-        <v>8320226326</v>
-      </c>
-      <c r="G56" s="12" t="s">
+      <c r="H64" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="19">
+        <v>1224</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C65" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D65" s="44" t="s">
+        <v>281</v>
+      </c>
+      <c r="E65" s="30">
+        <v>863609916544</v>
+      </c>
+      <c r="F65" s="34">
+        <v>9925669837</v>
+      </c>
+      <c r="G65" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="H56" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>1217</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="C57" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="D57" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="E57" s="29" t="s">
-        <v>248</v>
-      </c>
-      <c r="F57" s="26">
-        <v>6352719479</v>
-      </c>
-      <c r="G57" s="12" t="s">
+      <c r="H65" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>1225</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D66" s="44" t="s">
+        <v>272</v>
+      </c>
+      <c r="E66" s="27">
+        <v>877868433283</v>
+      </c>
+      <c r="F66" s="32">
+        <v>9714374772</v>
+      </c>
+      <c r="G66" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="H57" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="19">
-        <v>1218</v>
-      </c>
-      <c r="B58" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="C58" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="D58" s="45" t="s">
-        <v>279</v>
-      </c>
-      <c r="E58" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="F58" s="26">
-        <v>9904123744</v>
-      </c>
-      <c r="G58" s="12" t="s">
+      <c r="H66" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="19">
+        <v>1226</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C67" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D67" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="E67" s="30">
+        <v>387760716924</v>
+      </c>
+      <c r="F67" s="34">
+        <v>9016525318</v>
+      </c>
+      <c r="G67" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="H58" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
-        <v>1219</v>
-      </c>
-      <c r="B59" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="C59" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="D59" s="45" t="s">
-        <v>280</v>
-      </c>
-      <c r="E59" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="F59" s="26">
-        <v>9574218015</v>
-      </c>
-      <c r="G59" s="12" t="s">
+      <c r="H67" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>1227</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="D68" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="E68" s="30">
+        <v>371214659024</v>
+      </c>
+      <c r="F68" s="34">
+        <v>9313281718</v>
+      </c>
+      <c r="G68" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="H59" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="19">
-        <v>1220</v>
-      </c>
-      <c r="B60" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="C60" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="D60" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="E60" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="F60" s="26">
-        <v>9737894252</v>
-      </c>
-      <c r="G60" s="12" t="s">
+      <c r="H68" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="19">
+        <v>1228</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="D69" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="E69" s="30">
+        <v>716050924500</v>
+      </c>
+      <c r="F69" s="34">
+        <v>9925251810</v>
+      </c>
+      <c r="G69" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="H60" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
-        <v>1221</v>
-      </c>
-      <c r="B61" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="C61" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="D61" s="45" t="s">
-        <v>256</v>
-      </c>
-      <c r="E61" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="F61" s="26">
-        <v>7567095117</v>
-      </c>
-      <c r="G61" s="12" t="s">
+      <c r="H69" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>1229</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="C70" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="D70" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="E70" s="30">
+        <v>770629036161</v>
+      </c>
+      <c r="F70" s="34">
+        <v>9664941182</v>
+      </c>
+      <c r="G70" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="H61" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="19">
-        <v>1222</v>
-      </c>
-      <c r="B62" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="C62" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="D62" s="45" t="s">
-        <v>257</v>
-      </c>
-      <c r="E62" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="F62" s="34">
-        <v>6355764851</v>
-      </c>
-      <c r="G62" s="12" t="s">
+      <c r="H70" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="19">
+        <v>1230</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D71" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="E71" s="27">
+        <v>646034972649</v>
+      </c>
+      <c r="F71" s="32">
+        <v>9979692514</v>
+      </c>
+      <c r="G71" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="H62" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
-        <v>1223</v>
-      </c>
-      <c r="B63" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D63" s="45" t="s">
-        <v>258</v>
-      </c>
-      <c r="E63" s="31">
-        <v>588971485746</v>
-      </c>
-      <c r="F63" s="32">
-        <v>8156035767</v>
-      </c>
-      <c r="G63" s="12" t="s">
+      <c r="H71" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H63" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="19">
-        <v>1224</v>
-      </c>
-      <c r="B64" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="C64" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="D64" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="E64" s="30">
-        <v>863609916544</v>
-      </c>
-      <c r="F64" s="34">
-        <v>9925669837</v>
-      </c>
-      <c r="G64" s="12" t="s">
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>1231</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D72" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="E72" s="27">
+        <v>681716388949</v>
+      </c>
+      <c r="F72" s="32">
+        <v>9824446619</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H64" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
-        <v>1225</v>
-      </c>
-      <c r="B65" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D65" s="45" t="s">
-        <v>273</v>
-      </c>
-      <c r="E65" s="27">
-        <v>877868433283</v>
-      </c>
-      <c r="F65" s="32">
-        <v>9714374772</v>
-      </c>
-      <c r="G65" s="12" t="s">
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="19">
+        <v>1232</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D73" s="44" t="s">
+        <v>287</v>
+      </c>
+      <c r="E73" s="27">
+        <v>680078961178</v>
+      </c>
+      <c r="F73" s="32">
+        <v>9016181529</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H73" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H65" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="19">
-        <v>1226</v>
-      </c>
-      <c r="B66" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="C66" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="D66" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="E66" s="30">
-        <v>387760716924</v>
-      </c>
-      <c r="F66" s="34">
-        <v>9016525318</v>
-      </c>
-      <c r="G66" s="12" t="s">
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>1233</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D74" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="E74" s="27">
+        <v>934647778164</v>
+      </c>
+      <c r="F74" s="32">
+        <v>9313203487</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H66" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
-        <v>1227</v>
-      </c>
-      <c r="B67" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="C67" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="D67" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="E67" s="30">
-        <v>371214659024</v>
-      </c>
-      <c r="F67" s="34">
-        <v>9313281718</v>
-      </c>
-      <c r="G67" s="12" t="s">
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="19">
+        <v>1234</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D75" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="E75" s="27">
+        <v>743736078906</v>
+      </c>
+      <c r="F75" s="32">
+        <v>9879009201</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H75" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="H67" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="19">
-        <v>1228</v>
-      </c>
-      <c r="B68" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="D68" s="45" t="s">
-        <v>285</v>
-      </c>
-      <c r="E68" s="30">
-        <v>716050924500</v>
-      </c>
-      <c r="F68" s="34">
-        <v>9925251810</v>
-      </c>
-      <c r="G68" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
-        <v>1229</v>
-      </c>
-      <c r="B69" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="C69" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="D69" s="45" t="s">
-        <v>286</v>
-      </c>
-      <c r="E69" s="30">
-        <v>770629036161</v>
-      </c>
-      <c r="F69" s="34">
-        <v>9664941182</v>
-      </c>
-      <c r="G69" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="19">
-        <v>1230</v>
-      </c>
-      <c r="B70" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D70" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="E70" s="27">
-        <v>646034972649</v>
-      </c>
-      <c r="F70" s="32">
-        <v>9979692514</v>
-      </c>
-      <c r="G70" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
-        <v>1231</v>
-      </c>
-      <c r="B71" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D71" s="45" t="s">
-        <v>287</v>
-      </c>
-      <c r="E71" s="27">
-        <v>681716388949</v>
-      </c>
-      <c r="F71" s="32">
-        <v>9824446619</v>
-      </c>
-      <c r="G71" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="H71" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="19">
-        <v>1232</v>
-      </c>
-      <c r="B72" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D72" s="45" t="s">
-        <v>288</v>
-      </c>
-      <c r="E72" s="27">
-        <v>680078961178</v>
-      </c>
-      <c r="F72" s="32">
-        <v>9016181529</v>
-      </c>
-      <c r="G72" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
-        <v>1233</v>
-      </c>
-      <c r="B73" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D73" s="45" t="s">
-        <v>289</v>
-      </c>
-      <c r="E73" s="27">
-        <v>934647778164</v>
-      </c>
-      <c r="F73" s="32">
-        <v>9313203487</v>
-      </c>
-      <c r="G73" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="19">
-        <v>1234</v>
-      </c>
-      <c r="B74" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D74" s="45" t="s">
-        <v>290</v>
-      </c>
-      <c r="E74" s="27">
-        <v>743736078906</v>
-      </c>
-      <c r="F74" s="32">
-        <v>9879009201</v>
-      </c>
-      <c r="G74" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
-        <v>1101</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>1102</v>
-      </c>
-      <c r="G76" s="1"/>
+        <v>1101</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
+        <v>1105</v>
+      </c>
+      <c r="G80" s="1"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
         <v>1106</v>
       </c>
-      <c r="G80" s="1"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
+      <c r="G81" s="1"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
         <v>1107</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
         <v>1108</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="6">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
         <v>1109</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
         <v>1110</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
         <v>1111</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
         <v>1112</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
         <v>1113</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
         <v>1114</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
         <v>1115</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="6">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
         <v>1116</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
         <v>1117</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
         <v>1118</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
         <v>1119</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
         <v>1120</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
         <v>1121</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
-        <v>1122</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
         <v>1135</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="E2:E40 E57:E62" numberStoredAsText="1"/>
+    <ignoredError sqref="E3:E41 E58:E63" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D043D23-75C9-4A79-B369-DB03044E1B80}">
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="22.28515625" customWidth="1"/>
@@ -3933,212 +3914,218 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="A2" s="49">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="49">
+        <v>10</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="50">
+        <v>240</v>
+      </c>
+      <c r="E2" s="51">
+        <v>20</v>
+      </c>
+      <c r="F2" s="51">
+        <v>20</v>
+      </c>
+      <c r="G2" s="51">
+        <v>20</v>
+      </c>
+      <c r="H2" s="51">
+        <v>20</v>
+      </c>
+      <c r="I2" s="51">
+        <v>20</v>
+      </c>
+      <c r="J2" s="51">
+        <v>20</v>
+      </c>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="49">
+        <v>1000</v>
+      </c>
+      <c r="B3" s="49">
+        <v>10</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="50">
+        <v>240</v>
+      </c>
+      <c r="E3" s="51">
+        <v>20</v>
+      </c>
+      <c r="F3" s="51">
+        <v>20</v>
+      </c>
+      <c r="G3" s="51">
+        <v>20</v>
+      </c>
+      <c r="H3" s="51">
+        <v>20</v>
+      </c>
+      <c r="I3" s="51">
+        <v>20</v>
+      </c>
+      <c r="J3" s="51">
+        <v>20</v>
+      </c>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="49">
+        <v>1000</v>
+      </c>
+      <c r="B4" s="49">
+        <v>10</v>
+      </c>
+      <c r="C4" s="50" t="s">
+        <v>297</v>
+      </c>
+      <c r="D4" s="50">
+        <v>240</v>
+      </c>
+      <c r="E4" s="51">
+        <v>20</v>
+      </c>
+      <c r="F4" s="51">
+        <v>20</v>
+      </c>
+      <c r="G4" s="51">
+        <v>20</v>
+      </c>
+      <c r="H4" s="51">
+        <v>20</v>
+      </c>
+      <c r="I4" s="51">
+        <v>20</v>
+      </c>
+      <c r="J4" s="51">
+        <v>20</v>
+      </c>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="49">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="49">
+        <v>10</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>298</v>
+      </c>
+      <c r="D5" s="50">
+        <v>240</v>
+      </c>
+      <c r="E5" s="51">
+        <v>20</v>
+      </c>
+      <c r="F5" s="51">
+        <v>20</v>
+      </c>
+      <c r="G5" s="51">
+        <v>20</v>
+      </c>
+      <c r="H5" s="51">
+        <v>20</v>
+      </c>
+      <c r="I5" s="51">
+        <v>20</v>
+      </c>
+      <c r="J5" s="51">
+        <v>20</v>
+      </c>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="49">
+        <v>1000</v>
+      </c>
+      <c r="B6" s="49">
+        <v>10</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="D6" s="50">
+        <v>480</v>
+      </c>
+      <c r="E6" s="51">
+        <v>40</v>
+      </c>
+      <c r="F6" s="51">
+        <v>40</v>
+      </c>
+      <c r="G6" s="51">
+        <v>40</v>
+      </c>
+      <c r="H6" s="51">
+        <v>40</v>
+      </c>
+      <c r="I6" s="51">
+        <v>40</v>
+      </c>
+      <c r="J6" s="51">
+        <v>40</v>
+      </c>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="49">
+        <v>1000</v>
+      </c>
+      <c r="B7" s="49">
+        <v>10</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="D7" s="50">
+        <v>480</v>
+      </c>
+      <c r="E7" s="51">
+        <v>40</v>
+      </c>
+      <c r="F7" s="51">
+        <v>40</v>
+      </c>
+      <c r="G7" s="51">
+        <v>40</v>
+      </c>
+      <c r="H7" s="51">
+        <v>40</v>
+      </c>
+      <c r="I7" s="51">
+        <v>40</v>
+      </c>
+      <c r="J7" s="51">
+        <v>40</v>
+      </c>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>1001</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="8">
-        <v>240</v>
-      </c>
-      <c r="E2" s="9">
-        <v>38</v>
-      </c>
-      <c r="F2" s="10">
-        <v>35</v>
-      </c>
-      <c r="G2" s="9">
-        <v>29</v>
-      </c>
-      <c r="H2" s="9">
-        <v>35</v>
-      </c>
-      <c r="I2" s="9">
-        <v>31</v>
-      </c>
-      <c r="J2" s="14">
-        <v>38</v>
-      </c>
-      <c r="K2" s="17"/>
-      <c r="M2" s="18"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="8">
-        <v>240</v>
-      </c>
-      <c r="E3" s="9">
-        <v>32</v>
-      </c>
-      <c r="F3" s="10">
-        <v>29</v>
-      </c>
-      <c r="G3" s="9">
-        <v>23</v>
-      </c>
-      <c r="H3" s="9">
-        <v>15</v>
-      </c>
-      <c r="I3" s="9">
-        <v>20</v>
-      </c>
-      <c r="J3" s="14">
-        <v>29</v>
-      </c>
-      <c r="K3" s="17"/>
-      <c r="M3" s="18"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="8">
-        <v>240</v>
-      </c>
-      <c r="E4" s="9">
-        <v>37</v>
-      </c>
-      <c r="F4" s="9">
-        <v>35</v>
-      </c>
-      <c r="G4" s="9">
-        <v>31</v>
-      </c>
-      <c r="H4" s="9">
-        <v>29</v>
-      </c>
-      <c r="I4" s="9">
-        <v>29</v>
-      </c>
-      <c r="J4" s="14">
-        <v>38</v>
-      </c>
-      <c r="K4" s="17"/>
-      <c r="M4" s="18"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="8">
-        <v>240</v>
-      </c>
-      <c r="E5" s="9">
-        <v>40</v>
-      </c>
-      <c r="F5" s="9">
-        <v>37</v>
-      </c>
-      <c r="G5" s="9">
-        <v>34</v>
-      </c>
-      <c r="H5" s="9">
-        <v>38</v>
-      </c>
-      <c r="I5" s="9">
-        <v>39</v>
-      </c>
-      <c r="J5" s="14">
-        <v>36</v>
-      </c>
-      <c r="K5" s="17"/>
-      <c r="M5" s="18"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="8">
-        <v>240</v>
-      </c>
-      <c r="E6" s="9">
-        <v>38</v>
-      </c>
-      <c r="F6" s="9">
-        <v>34</v>
-      </c>
-      <c r="G6" s="9">
-        <v>24</v>
-      </c>
-      <c r="H6" s="9">
-        <v>32</v>
-      </c>
-      <c r="I6" s="9">
-        <v>39</v>
-      </c>
-      <c r="J6" s="14">
-        <v>36</v>
-      </c>
-      <c r="K6" s="17"/>
-      <c r="M6" s="18"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>1006</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="8">
-        <v>240</v>
-      </c>
-      <c r="E7" s="9">
-        <v>32</v>
-      </c>
-      <c r="F7" s="9">
-        <v>34</v>
-      </c>
-      <c r="G7" s="9">
-        <v>22</v>
-      </c>
-      <c r="H7" s="9">
-        <v>22</v>
-      </c>
-      <c r="I7" s="9">
-        <v>21</v>
-      </c>
-      <c r="J7" s="14">
-        <v>34</v>
-      </c>
-      <c r="K7" s="17"/>
-      <c r="M7" s="18"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>1007</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>178</v>
@@ -4150,29 +4137,29 @@
         <v>240</v>
       </c>
       <c r="E8" s="9">
-        <v>36</v>
-      </c>
-      <c r="F8" s="9">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="F8" s="10">
+        <v>35</v>
       </c>
       <c r="G8" s="9">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H8" s="9">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I8" s="9">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J8" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K8" s="17"/>
       <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>1008</v>
+      <c r="A9" s="6">
+        <v>1002</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>178</v>
@@ -4184,29 +4171,29 @@
         <v>240</v>
       </c>
       <c r="E9" s="9">
-        <v>38</v>
-      </c>
-      <c r="F9" s="9">
-        <v>37</v>
+        <v>32</v>
+      </c>
+      <c r="F9" s="10">
+        <v>29</v>
       </c>
       <c r="G9" s="9">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H9" s="9">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="I9" s="9">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J9" s="14">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K9" s="17"/>
       <c r="M9" s="18"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>1009</v>
+      <c r="A10" s="6">
+        <v>1003</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>178</v>
@@ -4218,29 +4205,29 @@
         <v>240</v>
       </c>
       <c r="E10" s="9">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F10" s="9">
+        <v>35</v>
+      </c>
+      <c r="G10" s="9">
+        <v>31</v>
+      </c>
+      <c r="H10" s="9">
         <v>29</v>
       </c>
-      <c r="G10" s="9">
-        <v>26</v>
-      </c>
-      <c r="H10" s="9">
-        <v>19</v>
-      </c>
       <c r="I10" s="9">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J10" s="14">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="K10" s="17"/>
       <c r="M10" s="18"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>178</v>
@@ -4252,29 +4239,29 @@
         <v>240</v>
       </c>
       <c r="E11" s="9">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F11" s="9">
+        <v>37</v>
+      </c>
+      <c r="G11" s="9">
         <v>34</v>
       </c>
-      <c r="G11" s="9">
-        <v>25</v>
-      </c>
       <c r="H11" s="9">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I11" s="9">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J11" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K11" s="17"/>
       <c r="M11" s="18"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>178</v>
@@ -4289,26 +4276,26 @@
         <v>38</v>
       </c>
       <c r="F12" s="9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G12" s="9">
         <v>24</v>
       </c>
       <c r="H12" s="9">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I12" s="9">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J12" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K12" s="17"/>
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>178</v>
@@ -4320,29 +4307,29 @@
         <v>240</v>
       </c>
       <c r="E13" s="9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13" s="9">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G13" s="9">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H13" s="9">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I13" s="9">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J13" s="14">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K13" s="17"/>
       <c r="M13" s="18"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>178</v>
@@ -4354,29 +4341,29 @@
         <v>240</v>
       </c>
       <c r="E14" s="9">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F14" s="9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G14" s="9">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H14" s="9">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I14" s="9">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="J14" s="14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K14" s="17"/>
       <c r="M14" s="18"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>178</v>
@@ -4388,29 +4375,29 @@
         <v>240</v>
       </c>
       <c r="E15" s="9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F15" s="9">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G15" s="9">
+        <v>32</v>
+      </c>
+      <c r="H15" s="9">
         <v>34</v>
       </c>
-      <c r="H15" s="9">
-        <v>36</v>
-      </c>
       <c r="I15" s="9">
+        <v>35</v>
+      </c>
+      <c r="J15" s="14">
         <v>38</v>
-      </c>
-      <c r="J15" s="14">
-        <v>39</v>
       </c>
       <c r="K15" s="17"/>
       <c r="M15" s="18"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>178</v>
@@ -4422,29 +4409,29 @@
         <v>240</v>
       </c>
       <c r="E16" s="9">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F16" s="9">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G16" s="9">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H16" s="9">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I16" s="9">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K16" s="17"/>
       <c r="M16" s="18"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>178</v>
@@ -4456,29 +4443,29 @@
         <v>240</v>
       </c>
       <c r="E17" s="9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17" s="9">
+        <v>34</v>
+      </c>
+      <c r="G17" s="9">
+        <v>25</v>
+      </c>
+      <c r="H17" s="9">
+        <v>24</v>
+      </c>
+      <c r="I17" s="9">
+        <v>25</v>
+      </c>
+      <c r="J17" s="14">
         <v>35</v>
-      </c>
-      <c r="G17" s="9">
-        <v>27</v>
-      </c>
-      <c r="H17" s="9">
-        <v>29</v>
-      </c>
-      <c r="I17" s="9">
-        <v>37</v>
-      </c>
-      <c r="J17" s="14">
-        <v>34</v>
       </c>
       <c r="K17" s="17"/>
       <c r="M17" s="18"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>178</v>
@@ -4493,16 +4480,16 @@
         <v>38</v>
       </c>
       <c r="F18" s="9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18" s="9">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I18" s="9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
         <v>32</v>
@@ -4512,7 +4499,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>178</v>
@@ -4524,29 +4511,29 @@
         <v>240</v>
       </c>
       <c r="E19" s="9">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F19" s="9">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G19" s="9">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H19" s="9">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I19" s="9">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J19" s="14">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K19" s="17"/>
       <c r="M19" s="18"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>178</v>
@@ -4558,29 +4545,29 @@
         <v>240</v>
       </c>
       <c r="E20" s="9">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F20" s="9">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G20" s="9">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H20" s="9">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I20" s="9">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="J20" s="14">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="K20" s="17"/>
       <c r="M20" s="18"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>178</v>
@@ -4592,29 +4579,29 @@
         <v>240</v>
       </c>
       <c r="E21" s="9">
+        <v>40</v>
+      </c>
+      <c r="F21" s="9">
+        <v>39</v>
+      </c>
+      <c r="G21" s="9">
         <v>34</v>
       </c>
-      <c r="F21" s="9">
-        <v>27</v>
-      </c>
-      <c r="G21" s="9">
-        <v>20</v>
-      </c>
       <c r="H21" s="9">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I21" s="9">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J21" s="14">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K21" s="17"/>
       <c r="M21" s="18"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>178</v>
@@ -4626,29 +4613,29 @@
         <v>240</v>
       </c>
       <c r="E22" s="9">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F22" s="9">
+        <v>38</v>
+      </c>
+      <c r="G22" s="9">
+        <v>30</v>
+      </c>
+      <c r="H22" s="9">
         <v>34</v>
       </c>
-      <c r="G22" s="9">
-        <v>18</v>
-      </c>
-      <c r="H22" s="9">
-        <v>20</v>
-      </c>
       <c r="I22" s="9">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J22" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K22" s="17"/>
       <c r="M22" s="18"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>178</v>
@@ -4660,29 +4647,29 @@
         <v>240</v>
       </c>
       <c r="E23" s="9">
+        <v>36</v>
+      </c>
+      <c r="F23" s="9">
+        <v>35</v>
+      </c>
+      <c r="G23" s="9">
+        <v>27</v>
+      </c>
+      <c r="H23" s="9">
+        <v>29</v>
+      </c>
+      <c r="I23" s="9">
+        <v>37</v>
+      </c>
+      <c r="J23" s="14">
         <v>34</v>
-      </c>
-      <c r="F23" s="9">
-        <v>33</v>
-      </c>
-      <c r="G23" s="9">
-        <v>26</v>
-      </c>
-      <c r="H23" s="9">
-        <v>17</v>
-      </c>
-      <c r="I23" s="9">
-        <v>21</v>
-      </c>
-      <c r="J23" s="14">
-        <v>27</v>
       </c>
       <c r="K23" s="17"/>
       <c r="M23" s="18"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>178</v>
@@ -4697,26 +4684,26 @@
         <v>38</v>
       </c>
       <c r="F24" s="9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G24" s="9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H24" s="9">
         <v>31</v>
       </c>
       <c r="I24" s="9">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J24" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K24" s="17"/>
       <c r="M24" s="18"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>178</v>
@@ -4728,29 +4715,29 @@
         <v>240</v>
       </c>
       <c r="E25" s="9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F25" s="9">
         <v>36</v>
       </c>
       <c r="G25" s="9">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H25" s="9">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I25" s="9">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="J25" s="14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K25" s="17"/>
       <c r="M25" s="18"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>178</v>
@@ -4762,29 +4749,29 @@
         <v>240</v>
       </c>
       <c r="E26" s="9">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F26" s="9">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G26" s="9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H26" s="9">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I26" s="9">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J26" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K26" s="17"/>
       <c r="M26" s="18"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>178</v>
@@ -4796,29 +4783,29 @@
         <v>240</v>
       </c>
       <c r="E27" s="9">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F27" s="9">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G27" s="9">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H27" s="9">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I27" s="9">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="K27" s="17"/>
       <c r="M27" s="18"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>178</v>
@@ -4830,29 +4817,29 @@
         <v>240</v>
       </c>
       <c r="E28" s="9">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F28" s="9">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G28" s="9">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H28" s="9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I28" s="9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K28" s="17"/>
       <c r="M28" s="18"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>178</v>
@@ -4864,29 +4851,29 @@
         <v>240</v>
       </c>
       <c r="E29" s="9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F29" s="9">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G29" s="9">
         <v>26</v>
       </c>
       <c r="H29" s="9">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I29" s="9">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J29" s="14">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K29" s="17"/>
       <c r="M29" s="18"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>178</v>
@@ -4901,26 +4888,26 @@
         <v>38</v>
       </c>
       <c r="F30" s="9">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G30" s="9">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H30" s="9">
+        <v>31</v>
+      </c>
+      <c r="I30" s="9">
+        <v>31</v>
+      </c>
+      <c r="J30" s="14">
         <v>34</v>
-      </c>
-      <c r="I30" s="9">
-        <v>36</v>
-      </c>
-      <c r="J30" s="14">
-        <v>38</v>
       </c>
       <c r="K30" s="17"/>
       <c r="M30" s="18"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>178</v>
@@ -4932,29 +4919,29 @@
         <v>240</v>
       </c>
       <c r="E31" s="9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F31" s="9">
         <v>36</v>
       </c>
       <c r="G31" s="9">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H31" s="9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I31" s="9">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J31" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K31" s="17"/>
       <c r="M31" s="18"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>178</v>
@@ -4969,26 +4956,26 @@
         <v>39</v>
       </c>
       <c r="F32" s="9">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G32" s="9">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H32" s="9">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I32" s="9">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J32" s="14">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K32" s="17"/>
       <c r="M32" s="18"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>178</v>
@@ -5003,26 +4990,26 @@
         <v>39</v>
       </c>
       <c r="F33" s="9">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G33" s="9">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H33" s="9">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I33" s="9">
         <v>36</v>
       </c>
       <c r="J33" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K33" s="17"/>
       <c r="M33" s="18"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>178</v>
@@ -5034,29 +5021,29 @@
         <v>240</v>
       </c>
       <c r="E34" s="9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F34" s="9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G34" s="9">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H34" s="9">
+        <v>25</v>
+      </c>
+      <c r="I34" s="9">
         <v>30</v>
       </c>
-      <c r="I34" s="9">
+      <c r="J34" s="14">
         <v>28</v>
-      </c>
-      <c r="J34" s="14">
-        <v>36</v>
       </c>
       <c r="K34" s="17"/>
       <c r="M34" s="18"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>178</v>
@@ -5068,29 +5055,29 @@
         <v>240</v>
       </c>
       <c r="E35" s="9">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F35" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G35" s="9">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H35" s="9">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I35" s="9">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J35" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K35" s="17"/>
       <c r="M35" s="18"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>178</v>
@@ -5102,29 +5089,29 @@
         <v>240</v>
       </c>
       <c r="E36" s="9">
+        <v>38</v>
+      </c>
+      <c r="F36" s="9">
+        <v>37</v>
+      </c>
+      <c r="G36" s="9">
+        <v>30</v>
+      </c>
+      <c r="H36" s="9">
         <v>34</v>
       </c>
-      <c r="F36" s="9">
-        <v>29</v>
-      </c>
-      <c r="G36" s="9">
-        <v>22</v>
-      </c>
-      <c r="H36" s="9">
-        <v>18</v>
-      </c>
       <c r="I36" s="9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J36" s="14">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K36" s="17"/>
       <c r="M36" s="18"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>178</v>
@@ -5136,19 +5123,19 @@
         <v>240</v>
       </c>
       <c r="E37" s="9">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F37" s="9">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G37" s="9">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H37" s="9">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I37" s="9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J37" s="14">
         <v>36</v>
@@ -5158,7 +5145,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>178</v>
@@ -5170,29 +5157,29 @@
         <v>240</v>
       </c>
       <c r="E38" s="9">
+        <v>39</v>
+      </c>
+      <c r="F38" s="9">
+        <v>35</v>
+      </c>
+      <c r="G38" s="9">
+        <v>33</v>
+      </c>
+      <c r="H38" s="9">
+        <v>32</v>
+      </c>
+      <c r="I38" s="9">
+        <v>36</v>
+      </c>
+      <c r="J38" s="14">
         <v>37</v>
-      </c>
-      <c r="F38" s="9">
-        <v>31</v>
-      </c>
-      <c r="G38" s="9">
-        <v>22</v>
-      </c>
-      <c r="H38" s="9">
-        <v>25</v>
-      </c>
-      <c r="I38" s="9">
-        <v>21</v>
-      </c>
-      <c r="J38" s="14">
-        <v>31</v>
       </c>
       <c r="K38" s="17"/>
       <c r="M38" s="18"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>178</v>
@@ -5204,29 +5191,29 @@
         <v>240</v>
       </c>
       <c r="E39" s="9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F39" s="9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G39" s="9">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H39" s="9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I39" s="9">
+        <v>36</v>
+      </c>
+      <c r="J39" s="14">
         <v>35</v>
-      </c>
-      <c r="J39" s="14">
-        <v>34</v>
       </c>
       <c r="K39" s="17"/>
       <c r="M39" s="18"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>178</v>
@@ -5238,19 +5225,19 @@
         <v>240</v>
       </c>
       <c r="E40" s="9">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F40" s="9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G40" s="9">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H40" s="9">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I40" s="9">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J40" s="14">
         <v>36</v>
@@ -5259,184 +5246,184 @@
       <c r="M40" s="18"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
-        <v>1001</v>
+      <c r="A41" s="7">
+        <v>1034</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>178</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="D41" s="8">
         <v>240</v>
       </c>
-      <c r="E41" s="11">
-        <v>39</v>
+      <c r="E41" s="9">
+        <v>32</v>
       </c>
       <c r="F41" s="9">
-        <v>39</v>
-      </c>
-      <c r="G41" s="11">
-        <v>28</v>
-      </c>
-      <c r="H41" s="11">
-        <v>26</v>
-      </c>
-      <c r="I41" s="11">
-        <v>22</v>
-      </c>
-      <c r="J41" s="15">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="G41" s="9">
+        <v>16</v>
+      </c>
+      <c r="H41" s="9">
+        <v>30</v>
+      </c>
+      <c r="I41" s="9">
+        <v>29</v>
+      </c>
+      <c r="J41" s="14">
+        <v>31</v>
       </c>
       <c r="K41" s="17"/>
       <c r="M41" s="18"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
-        <v>1002</v>
+      <c r="A42" s="7">
+        <v>1035</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>178</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="D42" s="8">
         <v>240</v>
       </c>
-      <c r="E42" s="11">
-        <v>33</v>
+      <c r="E42" s="9">
+        <v>34</v>
       </c>
       <c r="F42" s="9">
-        <v>33</v>
-      </c>
-      <c r="G42" s="11">
-        <v>17</v>
-      </c>
-      <c r="H42" s="11">
-        <v>14</v>
-      </c>
-      <c r="I42" s="11">
+        <v>29</v>
+      </c>
+      <c r="G42" s="9">
+        <v>22</v>
+      </c>
+      <c r="H42" s="9">
         <v>18</v>
       </c>
-      <c r="J42" s="15">
-        <v>29</v>
+      <c r="I42" s="9">
+        <v>34</v>
+      </c>
+      <c r="J42" s="14">
+        <v>26</v>
       </c>
       <c r="K42" s="17"/>
       <c r="M42" s="18"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>1003</v>
+      <c r="A43" s="7">
+        <v>1036</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>178</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="D43" s="8">
         <v>240</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="9">
         <v>37</v>
       </c>
       <c r="F43" s="9">
-        <v>40</v>
-      </c>
-      <c r="G43" s="11">
-        <v>23</v>
-      </c>
-      <c r="H43" s="11">
-        <v>21</v>
-      </c>
-      <c r="I43" s="11">
-        <v>14</v>
-      </c>
-      <c r="J43" s="15">
-        <v>38</v>
+        <v>32</v>
+      </c>
+      <c r="G43" s="9">
+        <v>28</v>
+      </c>
+      <c r="H43" s="9">
+        <v>22</v>
+      </c>
+      <c r="I43" s="9">
+        <v>33</v>
+      </c>
+      <c r="J43" s="14">
+        <v>36</v>
       </c>
       <c r="K43" s="17"/>
       <c r="M43" s="18"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
-        <v>1004</v>
+        <v>1037</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>178</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="D44" s="8">
         <v>240</v>
       </c>
       <c r="E44" s="9">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F44" s="9">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G44" s="9">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H44" s="9">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="I44" s="9">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J44" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K44" s="17"/>
       <c r="M44" s="18"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
-        <v>1005</v>
+        <v>1038</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>178</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="D45" s="8">
         <v>240</v>
       </c>
       <c r="E45" s="9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F45" s="9">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G45" s="9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H45" s="9">
         <v>33</v>
       </c>
       <c r="I45" s="9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J45" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K45" s="17"/>
       <c r="M45" s="18"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
-        <v>1006</v>
+        <v>1039</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>178</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="D46" s="8">
         <v>240</v>
@@ -5445,26 +5432,26 @@
         <v>39</v>
       </c>
       <c r="F46" s="9">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G46" s="9">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H46" s="9">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I46" s="9">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J46" s="14">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K46" s="17"/>
       <c r="M46" s="18"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
-        <v>1007</v>
+      <c r="A47" s="6">
+        <v>1001</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>178</v>
@@ -5475,30 +5462,30 @@
       <c r="D47" s="8">
         <v>240</v>
       </c>
-      <c r="E47" s="9">
-        <v>36</v>
+      <c r="E47" s="11">
+        <v>39</v>
       </c>
       <c r="F47" s="9">
-        <v>37</v>
-      </c>
-      <c r="G47" s="9">
-        <v>25</v>
-      </c>
-      <c r="H47" s="9">
-        <v>15</v>
-      </c>
-      <c r="I47" s="9">
-        <v>18</v>
-      </c>
-      <c r="J47" s="14">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="G47" s="11">
+        <v>28</v>
+      </c>
+      <c r="H47" s="11">
+        <v>26</v>
+      </c>
+      <c r="I47" s="11">
+        <v>22</v>
+      </c>
+      <c r="J47" s="15">
+        <v>33</v>
       </c>
       <c r="K47" s="17"/>
       <c r="M47" s="18"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
-        <v>1008</v>
+      <c r="A48" s="6">
+        <v>1002</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>178</v>
@@ -5509,30 +5496,30 @@
       <c r="D48" s="8">
         <v>240</v>
       </c>
-      <c r="E48" s="9">
-        <v>0</v>
+      <c r="E48" s="11">
+        <v>33</v>
       </c>
       <c r="F48" s="9">
-        <v>0</v>
-      </c>
-      <c r="G48" s="9">
-        <v>0</v>
-      </c>
-      <c r="H48" s="9">
-        <v>23</v>
-      </c>
-      <c r="I48" s="9">
-        <v>0</v>
-      </c>
-      <c r="J48" s="14">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="G48" s="11">
+        <v>17</v>
+      </c>
+      <c r="H48" s="11">
+        <v>14</v>
+      </c>
+      <c r="I48" s="11">
+        <v>18</v>
+      </c>
+      <c r="J48" s="15">
+        <v>29</v>
       </c>
       <c r="K48" s="17"/>
       <c r="M48" s="18"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
-        <v>1009</v>
+      <c r="A49" s="6">
+        <v>1003</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>178</v>
@@ -5543,30 +5530,30 @@
       <c r="D49" s="8">
         <v>240</v>
       </c>
-      <c r="E49" s="9">
-        <v>36</v>
+      <c r="E49" s="11">
+        <v>37</v>
       </c>
       <c r="F49" s="9">
-        <v>36</v>
-      </c>
-      <c r="G49" s="9">
-        <v>22</v>
-      </c>
-      <c r="H49" s="9">
-        <v>17</v>
-      </c>
-      <c r="I49" s="9">
-        <v>25</v>
-      </c>
-      <c r="J49" s="14">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="G49" s="11">
+        <v>23</v>
+      </c>
+      <c r="H49" s="11">
+        <v>21</v>
+      </c>
+      <c r="I49" s="11">
+        <v>14</v>
+      </c>
+      <c r="J49" s="15">
+        <v>38</v>
       </c>
       <c r="K49" s="17"/>
       <c r="M49" s="18"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>178</v>
@@ -5578,29 +5565,29 @@
         <v>240</v>
       </c>
       <c r="E50" s="9">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F50" s="9">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G50" s="9">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H50" s="9">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I50" s="9">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J50" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K50" s="17"/>
       <c r="M50" s="18"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>178</v>
@@ -5615,26 +5602,26 @@
         <v>39</v>
       </c>
       <c r="F51" s="9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G51" s="9">
         <v>27</v>
       </c>
       <c r="H51" s="9">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I51" s="9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J51" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K51" s="17"/>
       <c r="M51" s="18"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>178</v>
@@ -5646,29 +5633,29 @@
         <v>240</v>
       </c>
       <c r="E52" s="9">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F52" s="9">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G52" s="9">
+        <v>23</v>
+      </c>
+      <c r="H52" s="9">
         <v>15</v>
       </c>
-      <c r="H52" s="9">
-        <v>14</v>
-      </c>
       <c r="I52" s="9">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J52" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K52" s="17"/>
       <c r="M52" s="18"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>178</v>
@@ -5680,29 +5667,29 @@
         <v>240</v>
       </c>
       <c r="E53" s="9">
+        <v>36</v>
+      </c>
+      <c r="F53" s="9">
         <v>37</v>
       </c>
-      <c r="F53" s="9">
-        <v>40</v>
-      </c>
       <c r="G53" s="9">
+        <v>25</v>
+      </c>
+      <c r="H53" s="9">
+        <v>15</v>
+      </c>
+      <c r="I53" s="9">
+        <v>18</v>
+      </c>
+      <c r="J53" s="14">
         <v>35</v>
-      </c>
-      <c r="H53" s="9">
-        <v>35</v>
-      </c>
-      <c r="I53" s="9">
-        <v>29</v>
-      </c>
-      <c r="J53" s="14">
-        <v>37</v>
       </c>
       <c r="K53" s="17"/>
       <c r="M53" s="18"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>178</v>
@@ -5714,29 +5701,29 @@
         <v>240</v>
       </c>
       <c r="E54" s="9">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F54" s="9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G54" s="9">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H54" s="9">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I54" s="9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J54" s="14">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K54" s="17"/>
       <c r="M54" s="18"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>178</v>
@@ -5751,26 +5738,26 @@
         <v>36</v>
       </c>
       <c r="F55" s="9">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G55" s="9">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H55" s="9">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I55" s="9">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J55" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K55" s="17"/>
       <c r="M55" s="18"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>178</v>
@@ -5782,29 +5769,29 @@
         <v>240</v>
       </c>
       <c r="E56" s="9">
+        <v>35</v>
+      </c>
+      <c r="F56" s="9">
         <v>37</v>
       </c>
-      <c r="F56" s="9">
-        <v>40</v>
-      </c>
       <c r="G56" s="9">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H56" s="9">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I56" s="9">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J56" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K56" s="17"/>
       <c r="M56" s="18"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>178</v>
@@ -5816,29 +5803,29 @@
         <v>240</v>
       </c>
       <c r="E57" s="9">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F57" s="9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G57" s="9">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H57" s="9">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I57" s="9">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J57" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K57" s="17"/>
       <c r="M57" s="18"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>178</v>
@@ -5850,29 +5837,29 @@
         <v>240</v>
       </c>
       <c r="E58" s="9">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F58" s="9">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G58" s="9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H58" s="9">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I58" s="9">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J58" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K58" s="17"/>
       <c r="M58" s="18"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>178</v>
@@ -5884,29 +5871,29 @@
         <v>240</v>
       </c>
       <c r="E59" s="9">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F59" s="9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G59" s="9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H59" s="9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I59" s="9">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J59" s="14">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K59" s="17"/>
       <c r="M59" s="18"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>178</v>
@@ -5918,29 +5905,29 @@
         <v>240</v>
       </c>
       <c r="E60" s="9">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F60" s="9">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G60" s="9">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H60" s="9">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I60" s="9">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J60" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K60" s="17"/>
       <c r="M60" s="18"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>178</v>
@@ -5952,29 +5939,29 @@
         <v>240</v>
       </c>
       <c r="E61" s="9">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F61" s="9">
+        <v>40</v>
+      </c>
+      <c r="G61" s="9">
+        <v>28</v>
+      </c>
+      <c r="H61" s="9">
+        <v>29</v>
+      </c>
+      <c r="I61" s="9">
+        <v>28</v>
+      </c>
+      <c r="J61" s="14">
         <v>38</v>
-      </c>
-      <c r="G61" s="9">
-        <v>23</v>
-      </c>
-      <c r="H61" s="9">
-        <v>19</v>
-      </c>
-      <c r="I61" s="9">
-        <v>20</v>
-      </c>
-      <c r="J61" s="14">
-        <v>26</v>
       </c>
       <c r="K61" s="17"/>
       <c r="M61" s="18"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>178</v>
@@ -5989,26 +5976,26 @@
         <v>37</v>
       </c>
       <c r="F62" s="9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G62" s="9">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H62" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I62" s="9">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J62" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K62" s="17"/>
       <c r="M62" s="18"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>178</v>
@@ -6020,29 +6007,29 @@
         <v>240</v>
       </c>
       <c r="E63" s="9">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F63" s="9">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G63" s="9">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H63" s="9">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I63" s="9">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J63" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K63" s="17"/>
       <c r="M63" s="18"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>178</v>
@@ -6054,29 +6041,29 @@
         <v>240</v>
       </c>
       <c r="E64" s="9">
+        <v>37</v>
+      </c>
+      <c r="F64" s="9">
         <v>39</v>
       </c>
-      <c r="F64" s="9">
-        <v>40</v>
-      </c>
       <c r="G64" s="9">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H64" s="9">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I64" s="9">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J64" s="14">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="K64" s="17"/>
       <c r="M64" s="18"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>178</v>
@@ -6088,29 +6075,29 @@
         <v>240</v>
       </c>
       <c r="E65" s="9">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F65" s="9">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G65" s="9">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H65" s="9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I65" s="9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J65" s="14">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K65" s="17"/>
       <c r="M65" s="18"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>178</v>
@@ -6122,29 +6109,29 @@
         <v>240</v>
       </c>
       <c r="E66" s="9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F66" s="9">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G66" s="9">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H66" s="9">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I66" s="9">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J66" s="14">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="K66" s="17"/>
       <c r="M66" s="18"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>178</v>
@@ -6156,29 +6143,29 @@
         <v>240</v>
       </c>
       <c r="E67" s="9">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F67" s="9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G67" s="9">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H67" s="9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I67" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J67" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K67" s="17"/>
       <c r="M67" s="18"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>178</v>
@@ -6190,29 +6177,29 @@
         <v>240</v>
       </c>
       <c r="E68" s="9">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F68" s="9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G68" s="9">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H68" s="9">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="I68" s="9">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J68" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K68" s="17"/>
       <c r="M68" s="18"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>178</v>
@@ -6224,29 +6211,29 @@
         <v>240</v>
       </c>
       <c r="E69" s="9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F69" s="9">
         <v>40</v>
       </c>
       <c r="G69" s="9">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H69" s="9">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I69" s="9">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J69" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K69" s="17"/>
       <c r="M69" s="18"/>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>178</v>
@@ -6258,29 +6245,29 @@
         <v>240</v>
       </c>
       <c r="E70" s="9">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F70" s="9">
+        <v>40</v>
+      </c>
+      <c r="G70" s="9">
+        <v>31</v>
+      </c>
+      <c r="H70" s="9">
+        <v>34</v>
+      </c>
+      <c r="I70" s="9">
+        <v>26</v>
+      </c>
+      <c r="J70" s="14">
         <v>38</v>
-      </c>
-      <c r="G70" s="9">
-        <v>36</v>
-      </c>
-      <c r="H70" s="9">
-        <v>38</v>
-      </c>
-      <c r="I70" s="9">
-        <v>37</v>
-      </c>
-      <c r="J70" s="14">
-        <v>37</v>
       </c>
       <c r="K70" s="17"/>
       <c r="M70" s="18"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>178</v>
@@ -6295,26 +6282,26 @@
         <v>39</v>
       </c>
       <c r="F71" s="9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G71" s="9">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H71" s="9">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I71" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J71" s="14">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K71" s="17"/>
       <c r="M71" s="18"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>178</v>
@@ -6326,29 +6313,29 @@
         <v>240</v>
       </c>
       <c r="E72" s="9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F72" s="9">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G72" s="9">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H72" s="9">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I72" s="9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J72" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K72" s="17"/>
       <c r="M72" s="18"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>178</v>
@@ -6360,29 +6347,29 @@
         <v>240</v>
       </c>
       <c r="E73" s="9">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F73" s="9">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G73" s="9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H73" s="9">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I73" s="9">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J73" s="14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K73" s="17"/>
       <c r="M73" s="18"/>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>178</v>
@@ -6394,29 +6381,29 @@
         <v>240</v>
       </c>
       <c r="E74" s="9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F74" s="9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G74" s="9">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H74" s="9">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I74" s="9">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J74" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K74" s="17"/>
       <c r="M74" s="18"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>178</v>
@@ -6428,29 +6415,29 @@
         <v>240</v>
       </c>
       <c r="E75" s="9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F75" s="9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G75" s="9">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H75" s="9">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I75" s="9">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J75" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K75" s="17"/>
       <c r="M75" s="18"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>178</v>
@@ -6462,29 +6449,29 @@
         <v>240</v>
       </c>
       <c r="E76" s="9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F76" s="9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G76" s="9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H76" s="9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I76" s="9">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J76" s="14">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K76" s="17"/>
       <c r="M76" s="18"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>178</v>
@@ -6496,29 +6483,29 @@
         <v>240</v>
       </c>
       <c r="E77" s="9">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F77" s="9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G77" s="9">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H77" s="9">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I77" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J77" s="14">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K77" s="17"/>
       <c r="M77" s="18"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>178</v>
@@ -6530,29 +6517,29 @@
         <v>240</v>
       </c>
       <c r="E78" s="9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F78" s="9">
         <v>37</v>
       </c>
       <c r="G78" s="9">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H78" s="9">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I78" s="9">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J78" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K78" s="17"/>
       <c r="M78" s="18"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>178</v>
@@ -6564,220 +6551,236 @@
         <v>240</v>
       </c>
       <c r="E79" s="9">
+        <v>38</v>
+      </c>
+      <c r="F79" s="9">
         <v>37</v>
       </c>
-      <c r="F79" s="9">
-        <v>40</v>
-      </c>
       <c r="G79" s="9">
+        <v>24</v>
+      </c>
+      <c r="H79" s="9">
+        <v>28</v>
+      </c>
+      <c r="I79" s="9">
+        <v>26</v>
+      </c>
+      <c r="J79" s="14">
         <v>30</v>
-      </c>
-      <c r="H79" s="9">
-        <v>22</v>
-      </c>
-      <c r="I79" s="9">
-        <v>28</v>
-      </c>
-      <c r="J79" s="14">
-        <v>33</v>
       </c>
       <c r="K79" s="17"/>
       <c r="M79" s="18"/>
     </row>
-    <row r="80" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A80" s="6">
-        <v>1201</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>259</v>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" s="7">
+        <v>1034</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D80" s="8">
-        <v>200</v>
-      </c>
-      <c r="E80" s="10"/>
-      <c r="F80" s="35">
-        <v>33</v>
-      </c>
-      <c r="G80" s="41">
-        <v>23</v>
-      </c>
-      <c r="H80" s="10"/>
-      <c r="I80" s="43"/>
-      <c r="J80" s="16"/>
-      <c r="K80" s="41">
-        <v>24</v>
-      </c>
-      <c r="L80" s="41">
-        <v>30</v>
-      </c>
-      <c r="M80" s="41">
-        <v>28</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="E80" s="9">
+        <v>32</v>
+      </c>
+      <c r="F80" s="9">
+        <v>37</v>
+      </c>
+      <c r="G80" s="9">
+        <v>20</v>
+      </c>
+      <c r="H80" s="9">
+        <v>25</v>
+      </c>
+      <c r="I80" s="9">
+        <v>20</v>
+      </c>
+      <c r="J80" s="14">
+        <v>32</v>
+      </c>
+      <c r="K80" s="17"/>
+      <c r="M80" s="18"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="44">
-        <v>1202</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>259</v>
+      <c r="A81" s="7">
+        <v>1035</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D81" s="8">
-        <v>200</v>
-      </c>
-      <c r="E81" s="7"/>
-      <c r="F81" s="36">
-        <v>36</v>
-      </c>
-      <c r="G81" s="36">
-        <v>25</v>
-      </c>
-      <c r="H81" s="7"/>
-      <c r="K81" s="36">
-        <v>30</v>
-      </c>
-      <c r="L81" s="36">
+        <v>240</v>
+      </c>
+      <c r="E81" s="9">
+        <v>39</v>
+      </c>
+      <c r="F81" s="9">
+        <v>38</v>
+      </c>
+      <c r="G81" s="9">
+        <v>23</v>
+      </c>
+      <c r="H81" s="9">
+        <v>19</v>
+      </c>
+      <c r="I81" s="9">
         <v>26</v>
       </c>
-      <c r="M81" s="36">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A82" s="6">
-        <v>1203</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>259</v>
+      <c r="J81" s="14">
+        <v>34</v>
+      </c>
+      <c r="K81" s="17"/>
+      <c r="M81" s="18"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="7">
+        <v>1036</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D82" s="8">
-        <v>200</v>
-      </c>
-      <c r="E82" s="7"/>
-      <c r="F82" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="G82" s="42" t="s">
-        <v>262</v>
-      </c>
-      <c r="H82" s="7"/>
-      <c r="K82" s="42" t="s">
-        <v>262</v>
-      </c>
-      <c r="L82" s="42" t="s">
-        <v>262</v>
-      </c>
-      <c r="M82" s="40" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="44">
-        <v>1204</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>259</v>
+        <v>240</v>
+      </c>
+      <c r="E82" s="9">
+        <v>0</v>
+      </c>
+      <c r="F82" s="9">
+        <v>0</v>
+      </c>
+      <c r="G82" s="9">
+        <v>0</v>
+      </c>
+      <c r="H82" s="9">
+        <v>0</v>
+      </c>
+      <c r="I82" s="9">
+        <v>0</v>
+      </c>
+      <c r="J82" s="14">
+        <v>0</v>
+      </c>
+      <c r="K82" s="17"/>
+      <c r="M82" s="18"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" s="7">
+        <v>1037</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D83" s="8">
-        <v>200</v>
-      </c>
-      <c r="E83" s="7"/>
-      <c r="F83" s="38">
-        <v>16</v>
-      </c>
-      <c r="G83" s="36">
-        <v>17</v>
-      </c>
-      <c r="H83" s="7"/>
-      <c r="K83" s="36">
-        <v>8</v>
-      </c>
-      <c r="L83" s="36">
-        <v>6</v>
-      </c>
-      <c r="M83" s="39">
+        <v>240</v>
+      </c>
+      <c r="E83" s="9">
+        <v>37</v>
+      </c>
+      <c r="F83" s="9">
+        <v>39</v>
+      </c>
+      <c r="G83" s="9">
+        <v>23</v>
+      </c>
+      <c r="H83" s="9">
+        <v>20</v>
+      </c>
+      <c r="I83" s="9">
         <v>19</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A84" s="6">
-        <v>1205</v>
-      </c>
-      <c r="B84" s="12" t="s">
-        <v>259</v>
+      <c r="J83" s="14">
+        <v>24</v>
+      </c>
+      <c r="K83" s="17"/>
+      <c r="M83" s="18"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" s="7">
+        <v>1038</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D84" s="8">
-        <v>200</v>
-      </c>
-      <c r="E84" s="7"/>
-      <c r="F84" s="35">
-        <v>31</v>
-      </c>
-      <c r="G84" s="36">
-        <v>24</v>
-      </c>
-      <c r="H84" s="7"/>
-      <c r="K84" s="36">
-        <v>21</v>
-      </c>
-      <c r="L84" s="36">
-        <v>10</v>
-      </c>
-      <c r="M84" s="39">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A85" s="44">
-        <v>1206</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>259</v>
+        <v>240</v>
+      </c>
+      <c r="E84" s="9">
+        <v>38</v>
+      </c>
+      <c r="F84" s="9">
+        <v>37</v>
+      </c>
+      <c r="G84" s="9">
+        <v>28</v>
+      </c>
+      <c r="H84" s="9">
+        <v>30</v>
+      </c>
+      <c r="I84" s="9">
+        <v>29</v>
+      </c>
+      <c r="J84" s="14">
+        <v>37</v>
+      </c>
+      <c r="K84" s="17"/>
+      <c r="M84" s="18"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="7">
+        <v>1039</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D85" s="8">
-        <v>200</v>
-      </c>
-      <c r="E85" s="7"/>
-      <c r="F85" s="35">
-        <v>34</v>
-      </c>
-      <c r="G85" s="36">
-        <v>35</v>
-      </c>
-      <c r="H85" s="7"/>
-      <c r="K85" s="36">
+        <v>240</v>
+      </c>
+      <c r="E85" s="9">
+        <v>37</v>
+      </c>
+      <c r="F85" s="9">
+        <v>40</v>
+      </c>
+      <c r="G85" s="9">
+        <v>30</v>
+      </c>
+      <c r="H85" s="9">
         <v>22</v>
       </c>
-      <c r="L85" s="36">
-        <v>18</v>
-      </c>
-      <c r="M85" s="39">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I85" s="9">
+        <v>28</v>
+      </c>
+      <c r="J85" s="14">
+        <v>33</v>
+      </c>
+      <c r="K85" s="17"/>
+      <c r="M85" s="18"/>
+    </row>
+    <row r="86" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>180</v>
@@ -6785,30 +6788,32 @@
       <c r="D86" s="8">
         <v>200</v>
       </c>
-      <c r="E86" s="7"/>
-      <c r="F86" s="38">
-        <v>26</v>
-      </c>
-      <c r="G86" s="36">
-        <v>15</v>
-      </c>
-      <c r="H86" s="7"/>
-      <c r="K86" s="36">
-        <v>27</v>
-      </c>
-      <c r="L86" s="36">
-        <v>15</v>
-      </c>
-      <c r="M86" s="39">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="44">
-        <v>1208</v>
+      <c r="E86" s="10"/>
+      <c r="F86" s="35">
+        <v>33</v>
+      </c>
+      <c r="G86" s="41">
+        <v>23</v>
+      </c>
+      <c r="H86" s="10"/>
+      <c r="I86" s="43"/>
+      <c r="J86" s="16"/>
+      <c r="K86" s="41">
+        <v>24</v>
+      </c>
+      <c r="L86" s="41">
+        <v>30</v>
+      </c>
+      <c r="M86" s="41">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" s="7">
+        <v>1202</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>180</v>
@@ -6817,29 +6822,29 @@
         <v>200</v>
       </c>
       <c r="E87" s="7"/>
-      <c r="F87" s="39">
-        <v>34</v>
+      <c r="F87" s="36">
+        <v>36</v>
       </c>
       <c r="G87" s="36">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H87" s="7"/>
       <c r="K87" s="36">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L87" s="36">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M87" s="36">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>180</v>
@@ -6848,29 +6853,29 @@
         <v>200</v>
       </c>
       <c r="E88" s="7"/>
-      <c r="F88" s="35">
-        <v>30</v>
-      </c>
-      <c r="G88" s="36">
-        <v>24</v>
+      <c r="F88" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="G88" s="42" t="s">
+        <v>261</v>
       </c>
       <c r="H88" s="7"/>
-      <c r="K88" s="36">
-        <v>20</v>
-      </c>
-      <c r="L88" s="36">
-        <v>19</v>
-      </c>
-      <c r="M88" s="39">
-        <v>25</v>
+      <c r="K88" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="L88" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="M88" s="40" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="44">
-        <v>1210</v>
+      <c r="A89" s="7">
+        <v>1204</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>180</v>
@@ -6880,28 +6885,28 @@
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="38">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G89" s="36">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H89" s="7"/>
       <c r="K89" s="36">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="L89" s="36">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M89" s="39">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>180</v>
@@ -6914,25 +6919,25 @@
         <v>31</v>
       </c>
       <c r="G90" s="36">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H90" s="7"/>
       <c r="K90" s="36">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L90" s="36">
         <v>10</v>
       </c>
       <c r="M90" s="39">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A91" s="44">
-        <v>1212</v>
+      <c r="A91" s="7">
+        <v>1206</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>180</v>
@@ -6945,25 +6950,25 @@
         <v>34</v>
       </c>
       <c r="G91" s="36">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H91" s="7"/>
       <c r="K91" s="36">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="L91" s="36">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M91" s="39">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A92" s="44">
-        <v>1213</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>1207</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>180</v>
@@ -6972,29 +6977,29 @@
         <v>200</v>
       </c>
       <c r="E92" s="7"/>
-      <c r="F92" s="35">
-        <v>36</v>
+      <c r="F92" s="38">
+        <v>26</v>
       </c>
       <c r="G92" s="36">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H92" s="7"/>
       <c r="K92" s="36">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="L92" s="36">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M92" s="39">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A93" s="6">
-        <v>1214</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="7">
+        <v>1208</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>180</v>
@@ -7003,29 +7008,29 @@
         <v>200</v>
       </c>
       <c r="E93" s="7"/>
-      <c r="F93" s="35">
+      <c r="F93" s="39">
         <v>34</v>
       </c>
       <c r="G93" s="36">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H93" s="7"/>
       <c r="K93" s="36">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="L93" s="36">
-        <v>14</v>
-      </c>
-      <c r="M93" s="39">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="M93" s="36">
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>180</v>
@@ -7035,28 +7040,28 @@
       </c>
       <c r="E94" s="7"/>
       <c r="F94" s="35">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G94" s="36">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H94" s="7"/>
       <c r="K94" s="36">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="L94" s="36">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M94" s="39">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A95" s="44">
-        <v>1216</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="7">
+        <v>1210</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>180</v>
@@ -7065,29 +7070,29 @@
         <v>200</v>
       </c>
       <c r="E95" s="7"/>
-      <c r="F95" s="35">
+      <c r="F95" s="38">
+        <v>39</v>
+      </c>
+      <c r="G95" s="36">
         <v>31</v>
-      </c>
-      <c r="G95" s="36">
-        <v>24</v>
       </c>
       <c r="H95" s="7"/>
       <c r="K95" s="36">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L95" s="36">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="M95" s="39">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>180</v>
@@ -7096,29 +7101,29 @@
         <v>200</v>
       </c>
       <c r="E96" s="7"/>
-      <c r="F96" s="39">
-        <v>28</v>
+      <c r="F96" s="35">
+        <v>31</v>
       </c>
       <c r="G96" s="36">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H96" s="7"/>
       <c r="K96" s="36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L96" s="36">
-        <v>8</v>
-      </c>
-      <c r="M96" s="36">
         <v>10</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="44">
-        <v>1218</v>
+      <c r="M96" s="39">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A97" s="7">
+        <v>1212</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>180</v>
@@ -7127,29 +7132,29 @@
         <v>200</v>
       </c>
       <c r="E97" s="7"/>
-      <c r="F97" s="39">
+      <c r="F97" s="35">
+        <v>34</v>
+      </c>
+      <c r="G97" s="36">
         <v>27</v>
-      </c>
-      <c r="G97" s="36">
-        <v>13</v>
       </c>
       <c r="H97" s="7"/>
       <c r="K97" s="36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L97" s="36">
-        <v>17</v>
-      </c>
-      <c r="M97" s="36">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
-        <v>1219</v>
+        <v>24</v>
+      </c>
+      <c r="M97" s="39">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A98" s="7">
+        <v>1213</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>180</v>
@@ -7158,29 +7163,29 @@
         <v>200</v>
       </c>
       <c r="E98" s="7"/>
-      <c r="F98" s="39">
-        <v>29</v>
+      <c r="F98" s="35">
+        <v>36</v>
       </c>
       <c r="G98" s="36">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H98" s="7"/>
       <c r="K98" s="36">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L98" s="36">
-        <v>21</v>
-      </c>
-      <c r="M98" s="36">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="44">
-        <v>1220</v>
+        <v>28</v>
+      </c>
+      <c r="M98" s="39">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A99" s="6">
+        <v>1214</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>180</v>
@@ -7189,29 +7194,29 @@
         <v>200</v>
       </c>
       <c r="E99" s="7"/>
-      <c r="F99" s="39">
-        <v>25</v>
+      <c r="F99" s="35">
+        <v>34</v>
       </c>
       <c r="G99" s="36">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H99" s="7"/>
       <c r="K99" s="36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L99" s="36">
-        <v>11</v>
-      </c>
-      <c r="M99" s="36">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="M99" s="39">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>180</v>
@@ -7220,29 +7225,29 @@
         <v>200</v>
       </c>
       <c r="E100" s="7"/>
-      <c r="F100" s="39">
-        <v>32</v>
+      <c r="F100" s="35">
+        <v>37</v>
       </c>
       <c r="G100" s="36">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H100" s="7"/>
       <c r="K100" s="36">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L100" s="36">
-        <v>20</v>
-      </c>
-      <c r="M100" s="36">
+        <v>15</v>
+      </c>
+      <c r="M100" s="39">
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="44">
-        <v>1222</v>
+    <row r="101" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A101" s="7">
+        <v>1216</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>180</v>
@@ -7251,29 +7256,29 @@
         <v>200</v>
       </c>
       <c r="E101" s="7"/>
-      <c r="F101" s="39">
-        <v>28</v>
+      <c r="F101" s="35">
+        <v>31</v>
       </c>
       <c r="G101" s="36">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H101" s="7"/>
       <c r="K101" s="36">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L101" s="36">
         <v>14</v>
       </c>
-      <c r="M101" s="36">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M101" s="39">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>180</v>
@@ -7282,28 +7287,29 @@
         <v>200</v>
       </c>
       <c r="E102" s="7"/>
-      <c r="F102" s="36">
-        <v>35</v>
+      <c r="F102" s="39">
+        <v>28</v>
       </c>
       <c r="G102" s="36">
-        <v>37</v>
-      </c>
-      <c r="H102" s="36">
-        <v>35</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H102" s="7"/>
       <c r="K102" s="36">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="L102" s="36">
-        <v>29</v>
+        <v>8</v>
+      </c>
+      <c r="M102" s="36">
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="44">
-        <v>1224</v>
+      <c r="A103" s="7">
+        <v>1218</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>180</v>
@@ -7313,27 +7319,28 @@
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="39">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G103" s="36">
-        <v>30</v>
-      </c>
-      <c r="H103" s="36">
-        <v>30</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H103" s="7"/>
       <c r="K103" s="36">
         <v>32</v>
       </c>
       <c r="L103" s="36">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="M103" s="36">
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>180</v>
@@ -7343,27 +7350,28 @@
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="39">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G104" s="36">
-        <v>26</v>
-      </c>
-      <c r="H104" s="36">
-        <v>34</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H104" s="7"/>
       <c r="K104" s="36">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L104" s="36">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="M104" s="36">
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="44">
-        <v>1226</v>
+      <c r="A105" s="7">
+        <v>1220</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>180</v>
@@ -7373,27 +7381,28 @@
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="39">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G105" s="36">
-        <v>23</v>
-      </c>
-      <c r="H105" s="36">
-        <v>25</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H105" s="7"/>
       <c r="K105" s="36">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L105" s="36">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="M105" s="36">
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>180</v>
@@ -7403,27 +7412,28 @@
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="39">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G106" s="36">
+        <v>21</v>
+      </c>
+      <c r="H106" s="7"/>
+      <c r="K106" s="36">
         <v>25</v>
       </c>
-      <c r="H106" s="36">
-        <v>30</v>
-      </c>
-      <c r="K106" s="36">
-        <v>32</v>
-      </c>
       <c r="L106" s="36">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="M106" s="36">
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="44">
-        <v>1228</v>
+      <c r="A107" s="7">
+        <v>1222</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>180</v>
@@ -7433,27 +7443,28 @@
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="39">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G107" s="36">
-        <v>34</v>
-      </c>
-      <c r="H107" s="36">
-        <v>30</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H107" s="7"/>
       <c r="K107" s="36">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L107" s="36">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="M107" s="36">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>180</v>
@@ -7462,28 +7473,28 @@
         <v>200</v>
       </c>
       <c r="E108" s="7"/>
-      <c r="F108" s="40" t="s">
-        <v>263</v>
+      <c r="F108" s="36">
+        <v>35</v>
       </c>
       <c r="G108" s="36">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H108" s="36">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K108" s="36">
-        <v>26</v>
-      </c>
-      <c r="L108" s="42" t="s">
-        <v>263</v>
+        <v>32</v>
+      </c>
+      <c r="L108" s="36">
+        <v>29</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="44">
-        <v>1230</v>
+      <c r="A109" s="7">
+        <v>1224</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>180</v>
@@ -7493,27 +7504,27 @@
       </c>
       <c r="E109" s="7"/>
       <c r="F109" s="39">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G109" s="36">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H109" s="36">
+        <v>30</v>
+      </c>
+      <c r="K109" s="36">
         <v>32</v>
       </c>
-      <c r="K109" s="36">
-        <v>23</v>
-      </c>
       <c r="L109" s="36">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>180</v>
@@ -7522,28 +7533,28 @@
         <v>200</v>
       </c>
       <c r="E110" s="7"/>
-      <c r="F110" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="G110" s="42" t="s">
-        <v>263</v>
-      </c>
-      <c r="H110" s="42" t="s">
-        <v>263</v>
-      </c>
-      <c r="K110" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="L110" s="42" t="s">
-        <v>263</v>
+      <c r="F110" s="39">
+        <v>34</v>
+      </c>
+      <c r="G110" s="36">
+        <v>26</v>
+      </c>
+      <c r="H110" s="36">
+        <v>34</v>
+      </c>
+      <c r="K110" s="36">
+        <v>32</v>
+      </c>
+      <c r="L110" s="36">
+        <v>31</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="44">
-        <v>1232</v>
+      <c r="A111" s="7">
+        <v>1226</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>180</v>
@@ -7553,27 +7564,27 @@
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="39">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G111" s="36">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H111" s="36">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K111" s="36">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="L111" s="36">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>180</v>
@@ -7583,27 +7594,27 @@
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="39">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G112" s="36">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H112" s="36">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K112" s="36">
+        <v>32</v>
+      </c>
+      <c r="L112" s="36">
         <v>31</v>
       </c>
-      <c r="L112" s="36">
-        <v>22</v>
-      </c>
     </row>
     <row r="113" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="44">
-        <v>1234</v>
+      <c r="A113" s="7">
+        <v>1228</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>180</v>
@@ -7613,201 +7624,207 @@
       </c>
       <c r="E113" s="7"/>
       <c r="F113" s="39">
+        <v>36</v>
+      </c>
+      <c r="G113" s="36">
+        <v>34</v>
+      </c>
+      <c r="H113" s="36">
+        <v>30</v>
+      </c>
+      <c r="K113" s="36">
         <v>33</v>
       </c>
-      <c r="G113" s="36">
+      <c r="L113" s="36">
         <v>24</v>
       </c>
-      <c r="H113" s="36">
-        <v>31</v>
-      </c>
-      <c r="K113" s="36">
-        <v>20</v>
-      </c>
-      <c r="L113" s="36">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
-        <v>1201</v>
+        <v>1229</v>
       </c>
       <c r="B114" s="12" t="s">
         <v>259</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="D114" s="8">
         <v>200</v>
       </c>
-      <c r="F114" s="35">
-        <v>33</v>
-      </c>
-      <c r="G114" s="41">
-        <v>33</v>
-      </c>
-      <c r="K114" s="41">
-        <v>28</v>
-      </c>
-      <c r="L114" s="41">
-        <v>28</v>
-      </c>
-      <c r="M114" s="41">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="44">
-        <v>1202</v>
+      <c r="E114" s="7"/>
+      <c r="F114" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="G114" s="36">
+        <v>24</v>
+      </c>
+      <c r="H114" s="36">
+        <v>25</v>
+      </c>
+      <c r="K114" s="36">
+        <v>26</v>
+      </c>
+      <c r="L114" s="42" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="7">
+        <v>1230</v>
       </c>
       <c r="B115" s="12" t="s">
         <v>259</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="D115" s="8">
         <v>200</v>
       </c>
-      <c r="F115" s="36" t="s">
-        <v>291</v>
-      </c>
-      <c r="G115" s="36" t="s">
-        <v>291</v>
-      </c>
-      <c r="K115" s="36" t="s">
-        <v>291</v>
-      </c>
-      <c r="L115" s="36" t="s">
-        <v>291</v>
-      </c>
-      <c r="M115" s="36" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="E115" s="7"/>
+      <c r="F115" s="39">
+        <v>37</v>
+      </c>
+      <c r="G115" s="36">
+        <v>22</v>
+      </c>
+      <c r="H115" s="36">
+        <v>32</v>
+      </c>
+      <c r="K115" s="36">
+        <v>23</v>
+      </c>
+      <c r="L115" s="36">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
-        <v>1203</v>
+        <v>1231</v>
       </c>
       <c r="B116" s="12" t="s">
         <v>259</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="D116" s="8">
         <v>200</v>
       </c>
-      <c r="F116" s="35">
-        <v>33</v>
-      </c>
-      <c r="G116" s="36">
-        <v>29</v>
-      </c>
-      <c r="K116" s="36">
-        <v>36</v>
-      </c>
-      <c r="L116" s="36">
-        <v>25</v>
-      </c>
-      <c r="M116" s="39">
-        <v>25</v>
+      <c r="E116" s="7"/>
+      <c r="F116" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="G116" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="H116" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="K116" s="36" t="s">
+        <v>262</v>
+      </c>
+      <c r="L116" s="42" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="44">
-        <v>1204</v>
+      <c r="A117" s="7">
+        <v>1232</v>
       </c>
       <c r="B117" s="12" t="s">
         <v>259</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="D117" s="8">
         <v>200</v>
       </c>
-      <c r="F117" s="38">
-        <v>18</v>
+      <c r="E117" s="7"/>
+      <c r="F117" s="39">
+        <v>36</v>
       </c>
       <c r="G117" s="36">
-        <v>25</v>
+        <v>32</v>
+      </c>
+      <c r="H117" s="36">
+        <v>32</v>
       </c>
       <c r="K117" s="36">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="L117" s="36">
-        <v>19</v>
-      </c>
-      <c r="M117" s="39">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
-        <v>1205</v>
+        <v>1233</v>
       </c>
       <c r="B118" s="12" t="s">
         <v>259</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="D118" s="8">
         <v>200</v>
       </c>
-      <c r="F118" s="35">
-        <v>33</v>
+      <c r="E118" s="7"/>
+      <c r="F118" s="39">
+        <v>35</v>
       </c>
       <c r="G118" s="36">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="H118" s="36">
+        <v>34</v>
       </c>
       <c r="K118" s="36">
         <v>31</v>
       </c>
       <c r="L118" s="36">
-        <v>16</v>
-      </c>
-      <c r="M118" s="39">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A119" s="44">
-        <v>1206</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" s="7">
+        <v>1234</v>
       </c>
       <c r="B119" s="12" t="s">
         <v>259</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="D119" s="8">
         <v>200</v>
       </c>
-      <c r="F119" s="35">
-        <v>36</v>
+      <c r="E119" s="7"/>
+      <c r="F119" s="39">
+        <v>33</v>
       </c>
       <c r="G119" s="36">
-        <v>38</v>
+        <v>24</v>
+      </c>
+      <c r="H119" s="36">
+        <v>31</v>
       </c>
       <c r="K119" s="36">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="L119" s="36">
-        <v>31</v>
-      </c>
-      <c r="M119" s="39">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>18</v>
@@ -7815,28 +7832,28 @@
       <c r="D120" s="8">
         <v>200</v>
       </c>
-      <c r="F120" s="38">
-        <v>35</v>
-      </c>
-      <c r="G120" s="36">
+      <c r="F120" s="35">
         <v>33</v>
       </c>
-      <c r="K120" s="36">
-        <v>30</v>
-      </c>
-      <c r="L120" s="36">
+      <c r="G120" s="41">
+        <v>33</v>
+      </c>
+      <c r="K120" s="41">
         <v>28</v>
       </c>
-      <c r="M120" s="39">
+      <c r="L120" s="41">
         <v>28</v>
       </c>
-    </row>
-    <row r="121" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="44">
-        <v>1208</v>
+      <c r="M120" s="41">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="7">
+        <v>1202</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>18</v>
@@ -7844,28 +7861,28 @@
       <c r="D121" s="8">
         <v>200</v>
       </c>
-      <c r="F121" s="39">
-        <v>37</v>
-      </c>
-      <c r="G121" s="36">
-        <v>36</v>
-      </c>
-      <c r="K121" s="36">
-        <v>40</v>
-      </c>
-      <c r="L121" s="36">
-        <v>31</v>
-      </c>
-      <c r="M121" s="36">
-        <v>33</v>
+      <c r="F121" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="G121" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="K121" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="L121" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="M121" s="36" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>18</v>
@@ -7874,27 +7891,27 @@
         <v>200</v>
       </c>
       <c r="F122" s="35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G122" s="36">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K122" s="36">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L122" s="36">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M122" s="39">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="44">
-        <v>1210</v>
+      <c r="A123" s="7">
+        <v>1204</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>18</v>
@@ -7903,27 +7920,27 @@
         <v>200</v>
       </c>
       <c r="F123" s="38">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G123" s="36">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K123" s="36">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="L123" s="36">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M123" s="39">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>18</v>
@@ -7932,27 +7949,27 @@
         <v>200</v>
       </c>
       <c r="F124" s="35">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G124" s="36">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K124" s="36">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L124" s="36">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M124" s="39">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A125" s="44">
-        <v>1212</v>
+      <c r="A125" s="7">
+        <v>1206</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>18</v>
@@ -7961,27 +7978,27 @@
         <v>200</v>
       </c>
       <c r="F125" s="35">
+        <v>36</v>
+      </c>
+      <c r="G125" s="36">
         <v>38</v>
       </c>
-      <c r="G125" s="36">
-        <v>35</v>
-      </c>
       <c r="K125" s="36">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L125" s="36">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M125" s="39">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A126" s="44">
-        <v>1213</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>1207</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>18</v>
@@ -7989,28 +8006,28 @@
       <c r="D126" s="8">
         <v>200</v>
       </c>
-      <c r="F126" s="35">
+      <c r="F126" s="38">
+        <v>35</v>
+      </c>
+      <c r="G126" s="36">
         <v>33</v>
       </c>
-      <c r="G126" s="36">
-        <v>34</v>
-      </c>
       <c r="K126" s="36">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L126" s="36">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M126" s="39">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A127" s="6">
-        <v>1214</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A127" s="7">
+        <v>1208</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>18</v>
@@ -8018,28 +8035,28 @@
       <c r="D127" s="8">
         <v>200</v>
       </c>
-      <c r="F127" s="35">
-        <v>30</v>
+      <c r="F127" s="39">
+        <v>37</v>
       </c>
       <c r="G127" s="36">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K127" s="36">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L127" s="36">
-        <v>22</v>
-      </c>
-      <c r="M127" s="39">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="M127" s="36">
+        <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>18</v>
@@ -8048,27 +8065,27 @@
         <v>200</v>
       </c>
       <c r="F128" s="35">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G128" s="36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K128" s="36">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L128" s="36">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M128" s="39">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A129" s="44">
-        <v>1216</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A129" s="7">
+        <v>1210</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>18</v>
@@ -8076,28 +8093,28 @@
       <c r="D129" s="8">
         <v>200</v>
       </c>
-      <c r="F129" s="35">
+      <c r="F129" s="38">
+        <v>35</v>
+      </c>
+      <c r="G129" s="36">
+        <v>38</v>
+      </c>
+      <c r="K129" s="36">
+        <v>39</v>
+      </c>
+      <c r="L129" s="36">
+        <v>28</v>
+      </c>
+      <c r="M129" s="39">
         <v>33</v>
       </c>
-      <c r="G129" s="36">
-        <v>29</v>
-      </c>
-      <c r="K129" s="36">
-        <v>34</v>
-      </c>
-      <c r="L129" s="36">
-        <v>21</v>
-      </c>
-      <c r="M129" s="39">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>18</v>
@@ -8105,28 +8122,28 @@
       <c r="D130" s="8">
         <v>200</v>
       </c>
-      <c r="F130" s="39">
-        <v>27</v>
+      <c r="F130" s="35">
+        <v>34</v>
       </c>
       <c r="G130" s="36">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K130" s="36">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L130" s="36">
-        <v>15</v>
-      </c>
-      <c r="M130" s="36">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="44">
-        <v>1218</v>
+        <v>22</v>
+      </c>
+      <c r="M130" s="39">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A131" s="7">
+        <v>1212</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>18</v>
@@ -8134,28 +8151,28 @@
       <c r="D131" s="8">
         <v>200</v>
       </c>
-      <c r="F131" s="39">
+      <c r="F131" s="35">
+        <v>38</v>
+      </c>
+      <c r="G131" s="36">
+        <v>35</v>
+      </c>
+      <c r="K131" s="36">
+        <v>39</v>
+      </c>
+      <c r="L131" s="36">
         <v>27</v>
       </c>
-      <c r="G131" s="36">
-        <v>20</v>
-      </c>
-      <c r="K131" s="36">
+      <c r="M131" s="39">
         <v>36</v>
       </c>
-      <c r="L131" s="36">
-        <v>18</v>
-      </c>
-      <c r="M131" s="36">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" s="6">
-        <v>1219</v>
+    </row>
+    <row r="132" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A132" s="7">
+        <v>1213</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>18</v>
@@ -8163,28 +8180,28 @@
       <c r="D132" s="8">
         <v>200</v>
       </c>
-      <c r="F132" s="39">
-        <v>28</v>
+      <c r="F132" s="35">
+        <v>33</v>
       </c>
       <c r="G132" s="36">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K132" s="36">
         <v>39</v>
       </c>
       <c r="L132" s="36">
-        <v>25</v>
-      </c>
-      <c r="M132" s="36">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="44">
-        <v>1220</v>
+        <v>33</v>
+      </c>
+      <c r="M132" s="39">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A133" s="6">
+        <v>1214</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>18</v>
@@ -8192,28 +8209,28 @@
       <c r="D133" s="8">
         <v>200</v>
       </c>
-      <c r="F133" s="39">
+      <c r="F133" s="35">
         <v>30</v>
       </c>
       <c r="G133" s="36">
+        <v>28</v>
+      </c>
+      <c r="K133" s="36">
+        <v>25</v>
+      </c>
+      <c r="L133" s="36">
         <v>22</v>
       </c>
-      <c r="K133" s="36">
-        <v>14</v>
-      </c>
-      <c r="L133" s="36">
-        <v>14</v>
-      </c>
-      <c r="M133" s="36">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="134" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M133" s="39">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>18</v>
@@ -8221,28 +8238,28 @@
       <c r="D134" s="8">
         <v>200</v>
       </c>
-      <c r="F134" s="39">
-        <v>26</v>
+      <c r="F134" s="35">
+        <v>37</v>
       </c>
       <c r="G134" s="36">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K134" s="36">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L134" s="36">
-        <v>24</v>
-      </c>
-      <c r="M134" s="36">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A135" s="44">
-        <v>1222</v>
+        <v>21</v>
+      </c>
+      <c r="M134" s="39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A135" s="7">
+        <v>1216</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>18</v>
@@ -8250,28 +8267,28 @@
       <c r="D135" s="8">
         <v>200</v>
       </c>
-      <c r="F135" s="39">
+      <c r="F135" s="35">
+        <v>33</v>
+      </c>
+      <c r="G135" s="36">
         <v>29</v>
       </c>
-      <c r="G135" s="36">
-        <v>25</v>
-      </c>
       <c r="K135" s="36">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L135" s="36">
-        <v>16</v>
-      </c>
-      <c r="M135" s="36">
         <v>21</v>
+      </c>
+      <c r="M135" s="39">
+        <v>27</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>18</v>
@@ -8280,27 +8297,27 @@
         <v>200</v>
       </c>
       <c r="F136" s="39">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G136" s="36">
-        <v>36</v>
-      </c>
-      <c r="H136" s="36">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K136" s="36">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L136" s="36">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A137" s="44">
-        <v>1224</v>
+        <v>15</v>
+      </c>
+      <c r="M136" s="36">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A137" s="7">
+        <v>1218</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>18</v>
@@ -8308,28 +8325,28 @@
       <c r="D137" s="8">
         <v>200</v>
       </c>
-      <c r="F137" s="36">
-        <v>32</v>
+      <c r="F137" s="39">
+        <v>27</v>
       </c>
       <c r="G137" s="36">
+        <v>20</v>
+      </c>
+      <c r="K137" s="36">
         <v>36</v>
       </c>
-      <c r="H137" s="36">
-        <v>30</v>
-      </c>
-      <c r="K137" s="36">
-        <v>40</v>
-      </c>
       <c r="L137" s="36">
-        <v>27</v>
+        <v>18</v>
+      </c>
+      <c r="M137" s="36">
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>18</v>
@@ -8338,27 +8355,27 @@
         <v>200</v>
       </c>
       <c r="F138" s="39">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G138" s="36">
-        <v>0</v>
-      </c>
-      <c r="H138" s="36">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K138" s="36">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L138" s="36">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="M138" s="36">
+        <v>36</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="44">
-        <v>1226</v>
+      <c r="A139" s="7">
+        <v>1220</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>18</v>
@@ -8367,27 +8384,27 @@
         <v>200</v>
       </c>
       <c r="F139" s="39">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G139" s="36">
-        <v>34</v>
-      </c>
-      <c r="H139" s="36">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K139" s="36">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="L139" s="36">
-        <v>27</v>
+        <v>14</v>
+      </c>
+      <c r="M139" s="36">
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>18</v>
@@ -8396,27 +8413,27 @@
         <v>200</v>
       </c>
       <c r="F140" s="39">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G140" s="36">
-        <v>37</v>
-      </c>
-      <c r="H140" s="36">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K140" s="36">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L140" s="36">
-        <v>35</v>
+        <v>24</v>
+      </c>
+      <c r="M140" s="36">
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="44">
-        <v>1228</v>
+      <c r="A141" s="7">
+        <v>1222</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>18</v>
@@ -8425,27 +8442,27 @@
         <v>200</v>
       </c>
       <c r="F141" s="39">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G141" s="36">
-        <v>33</v>
-      </c>
-      <c r="H141" s="36">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K141" s="36">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L141" s="36">
-        <v>31</v>
+        <v>16</v>
+      </c>
+      <c r="M141" s="36">
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>18</v>
@@ -8454,27 +8471,27 @@
         <v>200</v>
       </c>
       <c r="F142" s="39">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G142" s="36">
         <v>36</v>
       </c>
       <c r="H142" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K142" s="36">
+        <v>40</v>
+      </c>
+      <c r="L142" s="36">
         <v>35</v>
       </c>
-      <c r="L142" s="36">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="44">
-        <v>1230</v>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" s="7">
+        <v>1224</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>18</v>
@@ -8482,28 +8499,28 @@
       <c r="D143" s="8">
         <v>200</v>
       </c>
-      <c r="F143" s="39">
+      <c r="F143" s="36">
         <v>32</v>
       </c>
       <c r="G143" s="36">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H143" s="36">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K143" s="36">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L143" s="36">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>18</v>
@@ -8512,27 +8529,27 @@
         <v>200</v>
       </c>
       <c r="F144" s="39">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G144" s="36">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H144" s="36">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K144" s="36">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L144" s="36">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="44">
-        <v>1232</v>
+      <c r="A145" s="7">
+        <v>1226</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>18</v>
@@ -8541,27 +8558,27 @@
         <v>200</v>
       </c>
       <c r="F145" s="39">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G145" s="36">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H145" s="36">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K145" s="36">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L145" s="36">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>18</v>
@@ -8570,27 +8587,27 @@
         <v>200</v>
       </c>
       <c r="F146" s="39">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G146" s="36">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H146" s="36">
+        <v>30</v>
+      </c>
+      <c r="K146" s="36">
+        <v>40</v>
+      </c>
+      <c r="L146" s="36">
         <v>35</v>
       </c>
-      <c r="K146" s="36">
-        <v>39</v>
-      </c>
-      <c r="L146" s="36">
-        <v>36</v>
-      </c>
     </row>
     <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" s="44">
-        <v>1234</v>
+      <c r="A147" s="7">
+        <v>1228</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>18</v>
@@ -8599,52 +8616,202 @@
         <v>200</v>
       </c>
       <c r="F147" s="39">
+        <v>34</v>
+      </c>
+      <c r="G147" s="36">
         <v>33</v>
       </c>
-      <c r="G147" s="36">
+      <c r="H147" s="36">
+        <v>30</v>
+      </c>
+      <c r="K147" s="36">
         <v>35</v>
       </c>
-      <c r="H147" s="36">
+      <c r="L147" s="36">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>1229</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D148" s="8">
+        <v>200</v>
+      </c>
+      <c r="F148" s="39">
+        <v>37</v>
+      </c>
+      <c r="G148" s="36">
+        <v>36</v>
+      </c>
+      <c r="H148" s="36">
         <v>29</v>
       </c>
-      <c r="K147" s="36">
+      <c r="K148" s="36">
+        <v>35</v>
+      </c>
+      <c r="L148" s="36">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A149" s="7">
+        <v>1230</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D149" s="8">
+        <v>200</v>
+      </c>
+      <c r="F149" s="39">
+        <v>32</v>
+      </c>
+      <c r="G149" s="36">
+        <v>33</v>
+      </c>
+      <c r="H149" s="36">
         <v>28</v>
       </c>
-      <c r="L147" s="36">
+      <c r="K149" s="36">
+        <v>39</v>
+      </c>
+      <c r="L149" s="36">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>1231</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D150" s="8">
+        <v>200</v>
+      </c>
+      <c r="F150" s="39">
+        <v>32</v>
+      </c>
+      <c r="G150" s="36">
+        <v>36</v>
+      </c>
+      <c r="H150" s="36">
+        <v>32</v>
+      </c>
+      <c r="K150" s="36">
+        <v>39</v>
+      </c>
+      <c r="L150" s="36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A151" s="7">
+        <v>1232</v>
+      </c>
+      <c r="B151" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D151" s="8">
+        <v>200</v>
+      </c>
+      <c r="F151" s="39">
+        <v>39</v>
+      </c>
+      <c r="G151" s="36">
+        <v>35</v>
+      </c>
+      <c r="H151" s="36">
+        <v>35</v>
+      </c>
+      <c r="K151" s="36">
+        <v>39</v>
+      </c>
+      <c r="L151" s="36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>1233</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D152" s="8">
+        <v>200</v>
+      </c>
+      <c r="F152" s="39">
+        <v>34</v>
+      </c>
+      <c r="G152" s="36">
+        <v>36</v>
+      </c>
+      <c r="H152" s="36">
+        <v>35</v>
+      </c>
+      <c r="K152" s="36">
+        <v>39</v>
+      </c>
+      <c r="L152" s="36">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A153" s="7">
+        <v>1234</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D153" s="8">
+        <v>200</v>
+      </c>
+      <c r="F153" s="39">
+        <v>33</v>
+      </c>
+      <c r="G153" s="36">
+        <v>35</v>
+      </c>
+      <c r="H153" s="36">
+        <v>29</v>
+      </c>
+      <c r="K153" s="36">
+        <v>28</v>
+      </c>
+      <c r="L153" s="36">
         <v>21</v>
       </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A148" s="6"/>
-      <c r="B148" s="12"/>
-      <c r="C148" s="8"/>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="44"/>
-      <c r="B149" s="12"/>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A150" s="6"/>
-      <c r="B150" s="12"/>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A151" s="44"/>
-      <c r="B151" s="12"/>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A152" s="6"/>
-      <c r="B152" s="12"/>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" s="44"/>
-      <c r="B153" s="12"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="12"/>
+      <c r="C154" s="8"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A155" s="44"/>
+      <c r="A155" s="7"/>
       <c r="B155" s="12"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -8652,7 +8819,7 @@
       <c r="B156" s="12"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" s="44"/>
+      <c r="A157" s="7"/>
       <c r="B157" s="12"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -8660,15 +8827,15 @@
       <c r="B158" s="12"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" s="44"/>
+      <c r="A159" s="7"/>
       <c r="B159" s="12"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A160" s="44"/>
+      <c r="A160" s="6"/>
       <c r="B160" s="12"/>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" s="6"/>
+      <c r="A161" s="7"/>
       <c r="B161" s="12"/>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -8676,7 +8843,7 @@
       <c r="B162" s="12"/>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="44"/>
+      <c r="A163" s="7"/>
       <c r="B163" s="12"/>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -8684,15 +8851,15 @@
       <c r="B164" s="12"/>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="44"/>
+      <c r="A165" s="7"/>
       <c r="B165" s="12"/>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" s="6"/>
+      <c r="A166" s="7"/>
       <c r="B166" s="12"/>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" s="44"/>
+      <c r="A167" s="6"/>
       <c r="B167" s="12"/>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -8700,7 +8867,7 @@
       <c r="B168" s="12"/>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" s="44"/>
+      <c r="A169" s="7"/>
       <c r="B169" s="12"/>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -8708,7 +8875,7 @@
       <c r="B170" s="12"/>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" s="44"/>
+      <c r="A171" s="7"/>
       <c r="B171" s="12"/>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -8716,7 +8883,7 @@
       <c r="B172" s="12"/>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" s="44"/>
+      <c r="A173" s="7"/>
       <c r="B173" s="12"/>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -8724,7 +8891,7 @@
       <c r="B174" s="12"/>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" s="44"/>
+      <c r="A175" s="7"/>
       <c r="B175" s="12"/>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -8732,7 +8899,7 @@
       <c r="B176" s="12"/>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177" s="44"/>
+      <c r="A177" s="7"/>
       <c r="B177" s="12"/>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -8740,7 +8907,7 @@
       <c r="B178" s="12"/>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" s="44"/>
+      <c r="A179" s="7"/>
       <c r="B179" s="12"/>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -8748,117 +8915,91 @@
       <c r="B180" s="12"/>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" s="44"/>
+      <c r="A181" s="7"/>
       <c r="B181" s="12"/>
     </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="6"/>
+      <c r="B182" s="12"/>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="7"/>
+      <c r="B183" s="12"/>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" s="6"/>
+      <c r="B184" s="12"/>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" s="7"/>
+      <c r="B185" s="12"/>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" s="6"/>
+      <c r="B186" s="12"/>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" s="7"/>
+      <c r="B187" s="12"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F81 F87">
-    <cfRule type="cellIs" dxfId="21" priority="22" operator="lessThan">
+  <conditionalFormatting sqref="F87 F93">
+    <cfRule type="cellIs" dxfId="11" priority="22" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F96:F113">
-    <cfRule type="cellIs" dxfId="20" priority="21" operator="lessThan">
+  <conditionalFormatting sqref="F102:F119">
+    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G81:G95">
-    <cfRule type="cellIs" dxfId="19" priority="20" operator="lessThan">
-      <formula>13.2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G96:G113">
-    <cfRule type="cellIs" dxfId="18" priority="19" operator="lessThan">
-      <formula>13.2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K81">
-    <cfRule type="cellIs" dxfId="17" priority="18" operator="lessThan">
-      <formula>13.2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K82:K113">
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
-      <formula>13.2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L81 L87">
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="lessThan">
-      <formula>13.2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L82:L113">
-    <cfRule type="cellIs" dxfId="14" priority="15" operator="lessThan">
-      <formula>13.2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M81 M87">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
-      <formula>13.2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M82:M101">
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="lessThan">
-      <formula>13.2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H102:H113">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="lessThan">
-      <formula>13.2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F130:F147">
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="lessThan">
-      <formula>13.2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F115 F121">
+  <conditionalFormatting sqref="F121 F127">
     <cfRule type="cellIs" dxfId="9" priority="11" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G130:G147">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="lessThan">
+  <conditionalFormatting sqref="F136:F153">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G115:G129">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="lessThan">
+  <conditionalFormatting sqref="G87:G119">
+    <cfRule type="cellIs" dxfId="7" priority="19" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M130:M135">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="G121:G153">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M115:M129">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
+  <conditionalFormatting sqref="H108:H119">
+    <cfRule type="cellIs" dxfId="5" priority="12" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H136:H147">
+  <conditionalFormatting sqref="H142:H153">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K130:K147">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="K87:L119">
+    <cfRule type="cellIs" dxfId="3" priority="15" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K115:K129">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+  <conditionalFormatting sqref="K121:L153">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L130:L147">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="M87:M107">
+    <cfRule type="cellIs" dxfId="1" priority="13" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L115:L129">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="M121:M141">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="lessThan">
       <formula>13.2</formula>
     </cfRule>
   </conditionalFormatting>
